--- a/docs/内娱图库_海蒂与爷爷_朱远亮_18144610287/StarPicture_测试用例.xlsx
+++ b/docs/内娱图库_海蒂与爷爷_朱远亮_18144610287/StarPicture_测试用例.xlsx
@@ -8,10 +8,9 @@
   </bookViews>
   <sheets>
     <sheet name="测试用例汇总" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="汇总统计" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'测试用例汇总'!$A$1:$M$114</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'测试用例汇总'!$A$1:$M$147</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -20,7 +19,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="4">
+  <fonts count="3">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -35,10 +34,6 @@
     </font>
     <font>
       <b val="1"/>
-    </font>
-    <font>
-      <b val="1"/>
-      <color rgb="00FFFFFF"/>
     </font>
   </fonts>
   <fills count="3">
@@ -80,7 +75,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -93,9 +88,6 @@
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -462,7 +454,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M114"/>
+  <dimension ref="A1:M147"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -573,7 +565,7 @@
       </c>
       <c r="F2" s="4" t="inlineStr">
         <is>
-          <t>注册_账号密码正确</t>
+          <t>注册_正常</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr">
@@ -583,22 +575,22 @@
       </c>
       <c r="H2" s="2" t="inlineStr">
         <is>
-          <t>1. POST /user/register userAccount=Zyl_New01 userPassword=12345678 checkPassword=12345678</t>
+          <t>POST /user/register userAccount=Zyl_New01 userPassword=12345678 checkPassword=12345678</t>
         </is>
       </c>
       <c r="I2" s="2" t="inlineStr">
         <is>
-          <t>返回code=0, userId&gt;0</t>
-        </is>
-      </c>
-      <c r="J2" s="2" t="n"/>
-      <c r="K2" s="2" t="n"/>
+          <t>code=0, userId&gt;0</t>
+        </is>
+      </c>
+      <c r="J2" s="2" t="inlineStr"/>
+      <c r="K2" s="2" t="inlineStr"/>
       <c r="L2" s="2" t="inlineStr">
         <is>
           <t>朱远亮</t>
         </is>
       </c>
-      <c r="M2" s="2" t="n"/>
+      <c r="M2" s="2" t="inlineStr"/>
     </row>
     <row r="3" ht="80" customHeight="1">
       <c r="A3" s="2" t="inlineStr">
@@ -631,27 +623,27 @@
       </c>
       <c r="G3" s="2" t="inlineStr">
         <is>
-          <t>TC_New01 已存在</t>
+          <t>TC-New01 已存在</t>
         </is>
       </c>
       <c r="H3" s="2" t="inlineStr">
         <is>
-          <t>1. 重复 TC-UR-001</t>
+          <t>重复注册</t>
         </is>
       </c>
       <c r="I3" s="2" t="inlineStr">
         <is>
-          <t>返回code=40001 提示账号重复</t>
-        </is>
-      </c>
-      <c r="J3" s="2" t="n"/>
-      <c r="K3" s="2" t="n"/>
+          <t>code=40001</t>
+        </is>
+      </c>
+      <c r="J3" s="2" t="inlineStr"/>
+      <c r="K3" s="2" t="inlineStr"/>
       <c r="L3" s="2" t="inlineStr">
         <is>
           <t>朱远亮</t>
         </is>
       </c>
-      <c r="M3" s="2" t="n"/>
+      <c r="M3" s="2" t="inlineStr"/>
     </row>
     <row r="4" ht="80" customHeight="1">
       <c r="A4" s="2" t="inlineStr">
@@ -675,7 +667,7 @@
         </is>
       </c>
       <c r="E4" s="3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F4" s="4" t="inlineStr">
         <is>
@@ -684,32 +676,32 @@
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>无账号</t>
+          <t>无</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>1. userPassword=12345678 checkPassword=87654321</t>
+          <t>userPassword!=checkPassword</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>返回code=40001</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="n"/>
-      <c r="K4" s="2" t="n"/>
+          <t>code=40001</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr"/>
+      <c r="K4" s="2" t="inlineStr"/>
       <c r="L4" s="2" t="inlineStr">
         <is>
           <t>朱远亮</t>
         </is>
       </c>
-      <c r="M4" s="2" t="n"/>
+      <c r="M4" s="2" t="inlineStr"/>
     </row>
     <row r="5" ht="80" customHeight="1">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>TC-UR-004</t>
+          <t>TC-UL-001</t>
         </is>
       </c>
       <c r="B5" s="2" t="inlineStr">
@@ -719,7 +711,7 @@
       </c>
       <c r="C5" s="3" t="inlineStr">
         <is>
-          <t>/用户注册</t>
+          <t>/用户登录</t>
         </is>
       </c>
       <c r="D5" s="3" t="inlineStr">
@@ -728,41 +720,41 @@
         </is>
       </c>
       <c r="E5" s="3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F5" s="4" t="inlineStr">
         <is>
-          <t>注册_账号为空</t>
+          <t>登录_正常</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>无账号</t>
+          <t>testuser01 已存在</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>1. userAccount=''</t>
+          <t>POST /user/login userAccount=testuser01 userPassword=12345678</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>返回code=40001</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="n"/>
-      <c r="K5" s="2" t="n"/>
+          <t>code=0, Set-Cookie</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr"/>
+      <c r="K5" s="2" t="inlineStr"/>
       <c r="L5" s="2" t="inlineStr">
         <is>
           <t>朱远亮</t>
         </is>
       </c>
-      <c r="M5" s="2" t="n"/>
+      <c r="M5" s="2" t="inlineStr"/>
     </row>
     <row r="6" ht="80" customHeight="1">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>TC-UR-005</t>
+          <t>TC-UL-002</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
@@ -772,7 +764,7 @@
       </c>
       <c r="C6" s="3" t="inlineStr">
         <is>
-          <t>/用户注册</t>
+          <t>/用户登录</t>
         </is>
       </c>
       <c r="D6" s="3" t="inlineStr">
@@ -781,41 +773,41 @@
         </is>
       </c>
       <c r="E6" s="3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F6" s="4" t="inlineStr">
         <is>
-          <t>注册_账号长度不足4</t>
+          <t>登录_密码错误</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>无账号</t>
+          <t>testuser01</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>1. userAccount='abc'(3字符)</t>
+          <t>wrongPassword</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>返回code=40001 提示账号长度不足</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="n"/>
-      <c r="K6" s="2" t="n"/>
+          <t>code=40001</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr"/>
+      <c r="K6" s="2" t="inlineStr"/>
       <c r="L6" s="2" t="inlineStr">
         <is>
           <t>朱远亮</t>
         </is>
       </c>
-      <c r="M6" s="2" t="n"/>
+      <c r="M6" s="2" t="inlineStr"/>
     </row>
     <row r="7" ht="80" customHeight="1">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>TC-UL-001</t>
+          <t>TC-UL-003</t>
         </is>
       </c>
       <c r="B7" s="2" t="inlineStr">
@@ -838,37 +830,37 @@
       </c>
       <c r="F7" s="4" t="inlineStr">
         <is>
-          <t>登录_账号密码正确</t>
+          <t>登录_账号不存在</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>testuser01 已存在</t>
+          <t>无</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>1. POST /user/login userAccount=testuser01 userPassword=12345678</t>
+          <t>userAccount=notexist</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>返回code=0, Set-Cookie 含登录态</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="n"/>
-      <c r="K7" s="2" t="n"/>
+          <t>code=40001</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr"/>
+      <c r="K7" s="2" t="inlineStr"/>
       <c r="L7" s="2" t="inlineStr">
         <is>
           <t>朱远亮</t>
         </is>
       </c>
-      <c r="M7" s="2" t="n"/>
+      <c r="M7" s="2" t="inlineStr"/>
     </row>
     <row r="8" ht="80" customHeight="1">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>TC-UL-002</t>
+          <t>TC-GC-001</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
@@ -878,7 +870,7 @@
       </c>
       <c r="C8" s="3" t="inlineStr">
         <is>
-          <t>/用户登录</t>
+          <t>/获取当前用户</t>
         </is>
       </c>
       <c r="D8" s="3" t="inlineStr">
@@ -891,37 +883,37 @@
       </c>
       <c r="F8" s="4" t="inlineStr">
         <is>
-          <t>登录_密码错误</t>
+          <t>获取_已登录</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>testuser01 已存在</t>
+          <t>已登录 Cookie</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>1. password=wrongpass</t>
+          <t>GET /user/get/login</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>返回code=40001</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="n"/>
-      <c r="K8" s="2" t="n"/>
+          <t>code=0, 用户信息</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr"/>
+      <c r="K8" s="2" t="inlineStr"/>
       <c r="L8" s="2" t="inlineStr">
         <is>
           <t>朱远亮</t>
         </is>
       </c>
-      <c r="M8" s="2" t="n"/>
+      <c r="M8" s="2" t="inlineStr"/>
     </row>
     <row r="9" ht="80" customHeight="1">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>TC-UL-003</t>
+          <t>TC-GC-002</t>
         </is>
       </c>
       <c r="B9" s="2" t="inlineStr">
@@ -931,7 +923,7 @@
       </c>
       <c r="C9" s="3" t="inlineStr">
         <is>
-          <t>/用户登录</t>
+          <t>/获取当前用户</t>
         </is>
       </c>
       <c r="D9" s="3" t="inlineStr">
@@ -940,41 +932,41 @@
         </is>
       </c>
       <c r="E9" s="3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F9" s="4" t="inlineStr">
         <is>
-          <t>登录_账号不存在</t>
+          <t>获取_未登录</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>无</t>
+          <t>无 Cookie</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>1. userAccount=testuser99</t>
+          <t>GET /user/get/login</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>返回code=40001</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="n"/>
-      <c r="K9" s="2" t="n"/>
+          <t>code=40100</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr"/>
+      <c r="K9" s="2" t="inlineStr"/>
       <c r="L9" s="2" t="inlineStr">
         <is>
           <t>朱远亮</t>
         </is>
       </c>
-      <c r="M9" s="2" t="n"/>
+      <c r="M9" s="2" t="inlineStr"/>
     </row>
     <row r="10" ht="80" customHeight="1">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>TC-UL-004</t>
+          <t>TC-UM-001</t>
         </is>
       </c>
       <c r="B10" s="2" t="inlineStr">
@@ -984,7 +976,7 @@
       </c>
       <c r="C10" s="3" t="inlineStr">
         <is>
-          <t>/用户登录</t>
+          <t>/更新我的信息</t>
         </is>
       </c>
       <c r="D10" s="3" t="inlineStr">
@@ -993,41 +985,41 @@
         </is>
       </c>
       <c r="E10" s="3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F10" s="4" t="inlineStr">
         <is>
-          <t>登录_账号密码都为空</t>
+          <t>更新_正常昵称</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>无</t>
+          <t>已登录</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>1. 空 body</t>
+          <t>POST /user/update/my userName='新名'</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>返回code=40001</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="n"/>
-      <c r="K10" s="2" t="n"/>
+          <t>code=0</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr"/>
+      <c r="K10" s="2" t="inlineStr"/>
       <c r="L10" s="2" t="inlineStr">
         <is>
           <t>朱远亮</t>
         </is>
       </c>
-      <c r="M10" s="2" t="n"/>
+      <c r="M10" s="2" t="inlineStr"/>
     </row>
     <row r="11" ht="80" customHeight="1">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>TC-UL-005</t>
+          <t>TC-UM-002</t>
         </is>
       </c>
       <c r="B11" s="2" t="inlineStr">
@@ -1037,7 +1029,7 @@
       </c>
       <c r="C11" s="3" t="inlineStr">
         <is>
-          <t>/用户登录</t>
+          <t>/更新我的信息</t>
         </is>
       </c>
       <c r="D11" s="3" t="inlineStr">
@@ -1046,41 +1038,41 @@
         </is>
       </c>
       <c r="E11" s="3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F11" s="4" t="inlineStr">
         <is>
-          <t>登录_密码小于8字符</t>
+          <t>更新_昵称为空</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>无</t>
+          <t>已登录</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>1. password='1234567'</t>
+          <t>userName=''</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>返回code=40001</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="n"/>
-      <c r="K11" s="2" t="n"/>
+          <t>code=40001</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr"/>
+      <c r="K11" s="2" t="inlineStr"/>
       <c r="L11" s="2" t="inlineStr">
         <is>
           <t>朱远亮</t>
         </is>
       </c>
-      <c r="M11" s="2" t="n"/>
+      <c r="M11" s="2" t="inlineStr"/>
     </row>
     <row r="12" ht="80" customHeight="1">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>TC-PERF-001</t>
+          <t>TC-UM-003</t>
         </is>
       </c>
       <c r="B12" s="2" t="inlineStr">
@@ -1090,51 +1082,50 @@
       </c>
       <c r="C12" s="3" t="inlineStr">
         <is>
-          <t>/用户登录</t>
+          <t>/更新我的信息</t>
         </is>
       </c>
       <c r="D12" s="3" t="inlineStr">
         <is>
-          <t>性能测试</t>
+          <t>功能测试</t>
         </is>
       </c>
       <c r="E12" s="3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F12" s="4" t="inlineStr">
         <is>
-          <t>登录_50并发</t>
+          <t>更新_未登录</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>已安装 JMeter</t>
+          <t>无</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>1. JMeter 50 线程 5s 内启动
-2. POST /user/login 正确账号密码</t>
+          <t>POST /user/update/my</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>P95 &lt; 500ms, 错误率 &lt; 1%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="n"/>
-      <c r="K12" s="2" t="n"/>
+          <t>code=40100</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr"/>
+      <c r="K12" s="2" t="inlineStr"/>
       <c r="L12" s="2" t="inlineStr">
         <is>
           <t>朱远亮</t>
         </is>
       </c>
-      <c r="M12" s="2" t="n"/>
+      <c r="M12" s="2" t="inlineStr"/>
     </row>
     <row r="13" ht="80" customHeight="1">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>TC-API-001</t>
+          <t>TC-UA-001</t>
         </is>
       </c>
       <c r="B13" s="2" t="inlineStr">
@@ -1144,51 +1135,50 @@
       </c>
       <c r="C13" s="3" t="inlineStr">
         <is>
-          <t>/用户注册</t>
+          <t>/管理员新增用户</t>
         </is>
       </c>
       <c r="D13" s="3" t="inlineStr">
         <is>
-          <t>接口测试</t>
+          <t>功能测试</t>
         </is>
       </c>
       <c r="E13" s="3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F13" s="4" t="inlineStr">
         <is>
-          <t>注册_Content-Type错误</t>
+          <t>新增_正常</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>无账号</t>
+          <t>admin 已登录</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>1. Content-Type=application/xml
-2. POST /user/register body=XML</t>
+          <t>POST /user/add userAccount=Zyl_Admin01</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>返回 415</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="n"/>
-      <c r="K13" s="2" t="n"/>
+          <t>code=0</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr"/>
+      <c r="K13" s="2" t="inlineStr"/>
       <c r="L13" s="2" t="inlineStr">
         <is>
           <t>朱远亮</t>
         </is>
       </c>
-      <c r="M13" s="2" t="n"/>
+      <c r="M13" s="2" t="inlineStr"/>
     </row>
     <row r="14" ht="80" customHeight="1">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>TC-SEC-001</t>
+          <t>TC-UA-002</t>
         </is>
       </c>
       <c r="B14" s="2" t="inlineStr">
@@ -1198,12 +1188,12 @@
       </c>
       <c r="C14" s="3" t="inlineStr">
         <is>
-          <t>/用户登录</t>
+          <t>/管理员新增用户</t>
         </is>
       </c>
       <c r="D14" s="3" t="inlineStr">
         <is>
-          <t>安全测试</t>
+          <t>功能测试</t>
         </is>
       </c>
       <c r="E14" s="3" t="n">
@@ -1211,38 +1201,37 @@
       </c>
       <c r="F14" s="4" t="inlineStr">
         <is>
-          <t>登录_SQL注入</t>
+          <t>新增_普通用户越权</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>testuser01 已存在</t>
+          <t>testuser01</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>1. password = "' OR 1=1 --"
-2. POST /user/login</t>
+          <t>POST /user/add</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>返回code=40001 拒绝登录</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="n"/>
-      <c r="K14" s="2" t="n"/>
+          <t>code=40300</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr"/>
+      <c r="K14" s="2" t="inlineStr"/>
       <c r="L14" s="2" t="inlineStr">
         <is>
           <t>朱远亮</t>
         </is>
       </c>
-      <c r="M14" s="2" t="n"/>
+      <c r="M14" s="2" t="inlineStr"/>
     </row>
     <row r="15" ht="80" customHeight="1">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>TC-UR-006</t>
+          <t>TC-UA-003</t>
         </is>
       </c>
       <c r="B15" s="2" t="inlineStr">
@@ -1252,7 +1241,7 @@
       </c>
       <c r="C15" s="3" t="inlineStr">
         <is>
-          <t>/用户注册</t>
+          <t>/管理员新增用户</t>
         </is>
       </c>
       <c r="D15" s="3" t="inlineStr">
@@ -1261,41 +1250,41 @@
         </is>
       </c>
       <c r="E15" s="3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F15" s="4" t="inlineStr">
         <is>
-          <t>注册_账号长度边界20</t>
+          <t>新增_未登录</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>无账号</t>
+          <t>无</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>1. userAccount=20字符</t>
+          <t>POST /user/add</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>返回code=0</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="n"/>
-      <c r="K15" s="2" t="n"/>
+          <t>code=40100</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr"/>
+      <c r="K15" s="2" t="inlineStr"/>
       <c r="L15" s="2" t="inlineStr">
         <is>
           <t>朱远亮</t>
         </is>
       </c>
-      <c r="M15" s="2" t="n"/>
+      <c r="M15" s="2" t="inlineStr"/>
     </row>
     <row r="16" ht="80" customHeight="1">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>TC-UR-007</t>
+          <t>TC-UG-001</t>
         </is>
       </c>
       <c r="B16" s="2" t="inlineStr">
@@ -1305,7 +1294,7 @@
       </c>
       <c r="C16" s="3" t="inlineStr">
         <is>
-          <t>/用户注册</t>
+          <t>/管理员获取用户</t>
         </is>
       </c>
       <c r="D16" s="3" t="inlineStr">
@@ -1314,41 +1303,41 @@
         </is>
       </c>
       <c r="E16" s="3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F16" s="4" t="inlineStr">
         <is>
-          <t>注册_账号含特殊字符</t>
+          <t>按id获取_正常</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>无账号</t>
+          <t>admin</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>1. userAccount='test@user.cn'</t>
+          <t>GET /user/get?id=1</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>返回code=40001</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="n"/>
-      <c r="K16" s="2" t="n"/>
+          <t>code=0, 用户信息</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr"/>
+      <c r="K16" s="2" t="inlineStr"/>
       <c r="L16" s="2" t="inlineStr">
         <is>
           <t>朱远亮</t>
         </is>
       </c>
-      <c r="M16" s="2" t="n"/>
+      <c r="M16" s="2" t="inlineStr"/>
     </row>
     <row r="17" ht="80" customHeight="1">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>TC-UR-008</t>
+          <t>TC-UG-002</t>
         </is>
       </c>
       <c r="B17" s="2" t="inlineStr">
@@ -1358,7 +1347,7 @@
       </c>
       <c r="C17" s="3" t="inlineStr">
         <is>
-          <t>/用户注册</t>
+          <t>/管理员获取用户</t>
         </is>
       </c>
       <c r="D17" s="3" t="inlineStr">
@@ -1367,41 +1356,41 @@
         </is>
       </c>
       <c r="E17" s="3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F17" s="4" t="inlineStr">
         <is>
-          <t>注册_纯数字账号</t>
+          <t>按id获取_不存在</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>无账号</t>
+          <t>admin</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>1. userAccount='123456'</t>
+          <t>GET /user/get?id=999999</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>返回code=40001 纯数字不允许</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="n"/>
-      <c r="K17" s="2" t="n"/>
+          <t>code=40001</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr"/>
+      <c r="K17" s="2" t="inlineStr"/>
       <c r="L17" s="2" t="inlineStr">
         <is>
           <t>朱远亮</t>
         </is>
       </c>
-      <c r="M17" s="2" t="n"/>
+      <c r="M17" s="2" t="inlineStr"/>
     </row>
     <row r="18" ht="80" customHeight="1">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>TC-UR-009</t>
+          <t>TC-UV-001</t>
         </is>
       </c>
       <c r="B18" s="2" t="inlineStr">
@@ -1411,7 +1400,7 @@
       </c>
       <c r="C18" s="3" t="inlineStr">
         <is>
-          <t>/用户注册</t>
+          <t>/管理员获取VO</t>
         </is>
       </c>
       <c r="D18" s="3" t="inlineStr">
@@ -1420,41 +1409,41 @@
         </is>
       </c>
       <c r="E18" s="3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F18" s="4" t="inlineStr">
         <is>
-          <t>注册_密码含中文</t>
+          <t>获取VO_正常</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>无账号</t>
+          <t>admin</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>1. userPassword='密码12345678'</t>
+          <t>GET /user/get/vo?id=1</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>返回code=40001</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="n"/>
-      <c r="K18" s="2" t="n"/>
+          <t>code=0</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr"/>
+      <c r="K18" s="2" t="inlineStr"/>
       <c r="L18" s="2" t="inlineStr">
         <is>
           <t>朱远亮</t>
         </is>
       </c>
-      <c r="M18" s="2" t="n"/>
+      <c r="M18" s="2" t="inlineStr"/>
     </row>
     <row r="19" ht="80" customHeight="1">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>TC-UR-010</t>
+          <t>TC-UV-002</t>
         </is>
       </c>
       <c r="B19" s="2" t="inlineStr">
@@ -1464,7 +1453,7 @@
       </c>
       <c r="C19" s="3" t="inlineStr">
         <is>
-          <t>/用户注册</t>
+          <t>/管理员获取VO</t>
         </is>
       </c>
       <c r="D19" s="3" t="inlineStr">
@@ -1473,41 +1462,41 @@
         </is>
       </c>
       <c r="E19" s="3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F19" s="4" t="inlineStr">
         <is>
-          <t>注册_账号含emoji</t>
+          <t>获取VO_普通用户越权</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>无账号</t>
+          <t>testuser01</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>1. userAccount='test😀01'</t>
+          <t>GET /user/get/vo?id=1</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>返回code=40001</t>
-        </is>
-      </c>
-      <c r="J19" s="2" t="n"/>
-      <c r="K19" s="2" t="n"/>
+          <t>code=40300</t>
+        </is>
+      </c>
+      <c r="J19" s="2" t="inlineStr"/>
+      <c r="K19" s="2" t="inlineStr"/>
       <c r="L19" s="2" t="inlineStr">
         <is>
           <t>朱远亮</t>
         </is>
       </c>
-      <c r="M19" s="2" t="n"/>
+      <c r="M19" s="2" t="inlineStr"/>
     </row>
     <row r="20" ht="80" customHeight="1">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>TC-UL-006</t>
+          <t>TC-UD-001</t>
         </is>
       </c>
       <c r="B20" s="2" t="inlineStr">
@@ -1517,7 +1506,7 @@
       </c>
       <c r="C20" s="3" t="inlineStr">
         <is>
-          <t>/用户登录</t>
+          <t>/管理员删除用户</t>
         </is>
       </c>
       <c r="D20" s="3" t="inlineStr">
@@ -1530,39 +1519,37 @@
       </c>
       <c r="F20" s="4" t="inlineStr">
         <is>
-          <t>登录_退出后Cookie失效</t>
+          <t>删除_正常</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>testuser01 已登录</t>
+          <t>admin</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>1. 先登录拿Cookie
-2. POST /user/logout
-3. 用旧Cookie访问 /user/get/login</t>
+          <t>POST /user/delete id=新用户id</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>返回code=40100</t>
-        </is>
-      </c>
-      <c r="J20" s="2" t="n"/>
-      <c r="K20" s="2" t="n"/>
+          <t>code=0, isDelete=1</t>
+        </is>
+      </c>
+      <c r="J20" s="2" t="inlineStr"/>
+      <c r="K20" s="2" t="inlineStr"/>
       <c r="L20" s="2" t="inlineStr">
         <is>
           <t>朱远亮</t>
         </is>
       </c>
-      <c r="M20" s="2" t="n"/>
+      <c r="M20" s="2" t="inlineStr"/>
     </row>
     <row r="21" ht="80" customHeight="1">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>TC-UL-007</t>
+          <t>TC-UD-002</t>
         </is>
       </c>
       <c r="B21" s="2" t="inlineStr">
@@ -1572,7 +1559,7 @@
       </c>
       <c r="C21" s="3" t="inlineStr">
         <is>
-          <t>/用户登录</t>
+          <t>/管理员删除用户</t>
         </is>
       </c>
       <c r="D21" s="3" t="inlineStr">
@@ -1581,41 +1568,41 @@
         </is>
       </c>
       <c r="E21" s="3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F21" s="4" t="inlineStr">
         <is>
-          <t>登录_连续5次密码错</t>
+          <t>删除_普通用户越权</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>testuser01 已存在</t>
+          <t>testuser01</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>1. 连续5次错误密码</t>
+          <t>POST /user/delete</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>返回5次code=40001</t>
-        </is>
-      </c>
-      <c r="J21" s="2" t="n"/>
-      <c r="K21" s="2" t="n"/>
+          <t>code=40300</t>
+        </is>
+      </c>
+      <c r="J21" s="2" t="inlineStr"/>
+      <c r="K21" s="2" t="inlineStr"/>
       <c r="L21" s="2" t="inlineStr">
         <is>
           <t>朱远亮</t>
         </is>
       </c>
-      <c r="M21" s="2" t="n"/>
+      <c r="M21" s="2" t="inlineStr"/>
     </row>
     <row r="22" ht="80" customHeight="1">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>TC-UL-008</t>
+          <t>TC-UU-001</t>
         </is>
       </c>
       <c r="B22" s="2" t="inlineStr">
@@ -1625,51 +1612,50 @@
       </c>
       <c r="C22" s="3" t="inlineStr">
         <is>
-          <t>/用户登录</t>
+          <t>/管理员更新用户</t>
         </is>
       </c>
       <c r="D22" s="3" t="inlineStr">
         <is>
-          <t>接口测试</t>
+          <t>功能测试</t>
         </is>
       </c>
       <c r="E22" s="3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F22" s="4" t="inlineStr">
         <is>
-          <t>登录_缺Content-Type</t>
+          <t>更新_正常昵称</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>无</t>
+          <t>admin</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>1. 不设置Content-Type
-2. POST /user/login</t>
+          <t>POST /user/update id=新id userName='改名'</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>返回415或服务端解析</t>
-        </is>
-      </c>
-      <c r="J22" s="2" t="n"/>
-      <c r="K22" s="2" t="n"/>
+          <t>code=0</t>
+        </is>
+      </c>
+      <c r="J22" s="2" t="inlineStr"/>
+      <c r="K22" s="2" t="inlineStr"/>
       <c r="L22" s="2" t="inlineStr">
         <is>
           <t>朱远亮</t>
         </is>
       </c>
-      <c r="M22" s="2" t="n"/>
+      <c r="M22" s="2" t="inlineStr"/>
     </row>
     <row r="23" ht="80" customHeight="1">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>TC-UL-009</t>
+          <t>TC-UU-002</t>
         </is>
       </c>
       <c r="B23" s="2" t="inlineStr">
@@ -1679,7 +1665,7 @@
       </c>
       <c r="C23" s="3" t="inlineStr">
         <is>
-          <t>/用户登录</t>
+          <t>/管理员更新用户</t>
         </is>
       </c>
       <c r="D23" s="3" t="inlineStr">
@@ -1688,41 +1674,41 @@
         </is>
       </c>
       <c r="E23" s="3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F23" s="4" t="inlineStr">
         <is>
-          <t>登录_密码仅大小写不同</t>
+          <t>更新_普通用户越权</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>testuser01 已存在</t>
+          <t>testuser01</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>1. password='12345678A' (实际是小写)</t>
+          <t>POST /user/update</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>返回code=40001</t>
-        </is>
-      </c>
-      <c r="J23" s="2" t="n"/>
-      <c r="K23" s="2" t="n"/>
+          <t>code=40300</t>
+        </is>
+      </c>
+      <c r="J23" s="2" t="inlineStr"/>
+      <c r="K23" s="2" t="inlineStr"/>
       <c r="L23" s="2" t="inlineStr">
         <is>
           <t>朱远亮</t>
         </is>
       </c>
-      <c r="M23" s="2" t="n"/>
+      <c r="M23" s="2" t="inlineStr"/>
     </row>
     <row r="24" ht="80" customHeight="1">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>TC-UL-010</t>
+          <t>TC-LP-001</t>
         </is>
       </c>
       <c r="B24" s="2" t="inlineStr">
@@ -1732,7 +1718,7 @@
       </c>
       <c r="C24" s="3" t="inlineStr">
         <is>
-          <t>/用户登录</t>
+          <t>/管理员分页查询</t>
         </is>
       </c>
       <c r="D24" s="3" t="inlineStr">
@@ -1741,41 +1727,41 @@
         </is>
       </c>
       <c r="E24" s="3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F24" s="4" t="inlineStr">
         <is>
-          <t>登录_密码含空格</t>
+          <t>分页查询_正常</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>testuser01 已存在</t>
+          <t>admin</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>1. password=' 12345678 '</t>
+          <t>POST /user/list/page/vo current=1 pageSize=10</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>返回code=40001</t>
-        </is>
-      </c>
-      <c r="J24" s="2" t="n"/>
-      <c r="K24" s="2" t="n"/>
+          <t>code=0, records列表</t>
+        </is>
+      </c>
+      <c r="J24" s="2" t="inlineStr"/>
+      <c r="K24" s="2" t="inlineStr"/>
       <c r="L24" s="2" t="inlineStr">
         <is>
           <t>朱远亮</t>
         </is>
       </c>
-      <c r="M24" s="2" t="n"/>
+      <c r="M24" s="2" t="inlineStr"/>
     </row>
     <row r="25" ht="80" customHeight="1">
       <c r="A25" s="2" t="inlineStr">
         <is>
-          <t>TC-UA-001</t>
+          <t>TC-LP-002</t>
         </is>
       </c>
       <c r="B25" s="2" t="inlineStr">
@@ -1785,7 +1771,7 @@
       </c>
       <c r="C25" s="3" t="inlineStr">
         <is>
-          <t>/用户管理</t>
+          <t>/管理员分页查询</t>
         </is>
       </c>
       <c r="D25" s="3" t="inlineStr">
@@ -1794,41 +1780,41 @@
         </is>
       </c>
       <c r="E25" s="3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F25" s="4" t="inlineStr">
         <is>
-          <t>管理员查询用户列表</t>
+          <t>分页查询_普通用户越权</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>admin 已登录</t>
+          <t>testuser01</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>1. POST /user/list/page/vo current=1 pageSize=10</t>
+          <t>POST /user/list/page/vo</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>返回code=0, records含用户列表</t>
-        </is>
-      </c>
-      <c r="J25" s="2" t="n"/>
-      <c r="K25" s="2" t="n"/>
+          <t>code=40300</t>
+        </is>
+      </c>
+      <c r="J25" s="2" t="inlineStr"/>
+      <c r="K25" s="2" t="inlineStr"/>
       <c r="L25" s="2" t="inlineStr">
         <is>
           <t>朱远亮</t>
         </is>
       </c>
-      <c r="M25" s="2" t="n"/>
+      <c r="M25" s="2" t="inlineStr"/>
     </row>
     <row r="26" ht="80" customHeight="1">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>TC-UA-002</t>
+          <t>TC-LO-001</t>
         </is>
       </c>
       <c r="B26" s="2" t="inlineStr">
@@ -1838,7 +1824,7 @@
       </c>
       <c r="C26" s="3" t="inlineStr">
         <is>
-          <t>/用户管理</t>
+          <t>/用户注销</t>
         </is>
       </c>
       <c r="D26" s="3" t="inlineStr">
@@ -1847,41 +1833,41 @@
         </is>
       </c>
       <c r="E26" s="3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F26" s="4" t="inlineStr">
         <is>
-          <t>管理员按昵称搜索</t>
+          <t>注销_正常</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>admin 已登录</t>
+          <t>已登录</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>1. POST /user/list/page/vo userName='test'</t>
+          <t>POST /user/logout</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>返回code=0 含test的记录</t>
-        </is>
-      </c>
-      <c r="J26" s="2" t="n"/>
-      <c r="K26" s="2" t="n"/>
+          <t>code=0</t>
+        </is>
+      </c>
+      <c r="J26" s="2" t="inlineStr"/>
+      <c r="K26" s="2" t="inlineStr"/>
       <c r="L26" s="2" t="inlineStr">
         <is>
           <t>朱远亮</t>
         </is>
       </c>
-      <c r="M26" s="2" t="n"/>
+      <c r="M26" s="2" t="inlineStr"/>
     </row>
     <row r="27" ht="80" customHeight="1">
       <c r="A27" s="2" t="inlineStr">
         <is>
-          <t>TC-UA-003</t>
+          <t>TC-LO-002</t>
         </is>
       </c>
       <c r="B27" s="2" t="inlineStr">
@@ -1891,12 +1877,12 @@
       </c>
       <c r="C27" s="3" t="inlineStr">
         <is>
-          <t>/用户管理</t>
+          <t>/用户注销</t>
         </is>
       </c>
       <c r="D27" s="3" t="inlineStr">
         <is>
-          <t>安全测试</t>
+          <t>功能测试</t>
         </is>
       </c>
       <c r="E27" s="3" t="n">
@@ -1904,37 +1890,37 @@
       </c>
       <c r="F27" s="4" t="inlineStr">
         <is>
-          <t>普通用户越权调用</t>
+          <t>注销_未登录</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>testuser01 已登录</t>
+          <t>无</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>1. POST /user/list/page/vo</t>
+          <t>POST /user/logout</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>返回code=40300</t>
-        </is>
-      </c>
-      <c r="J27" s="2" t="n"/>
-      <c r="K27" s="2" t="n"/>
+          <t>code=40100</t>
+        </is>
+      </c>
+      <c r="J27" s="2" t="inlineStr"/>
+      <c r="K27" s="2" t="inlineStr"/>
       <c r="L27" s="2" t="inlineStr">
         <is>
           <t>朱远亮</t>
         </is>
       </c>
-      <c r="M27" s="2" t="n"/>
+      <c r="M27" s="2" t="inlineStr"/>
     </row>
     <row r="28" ht="80" customHeight="1">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>TC-PERF-002</t>
+          <t>TC-PERF-001</t>
         </is>
       </c>
       <c r="B28" s="2" t="inlineStr">
@@ -1944,7 +1930,7 @@
       </c>
       <c r="C28" s="3" t="inlineStr">
         <is>
-          <t>/用户注册</t>
+          <t>/用户登录</t>
         </is>
       </c>
       <c r="D28" s="3" t="inlineStr">
@@ -1957,38 +1943,37 @@
       </c>
       <c r="F28" s="4" t="inlineStr">
         <is>
-          <t>注册_20并发</t>
+          <t>登录_50并发</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t>已安装 JMeter</t>
+          <t>JMeter</t>
         </is>
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>1. JMeter 20 线程 5s 内启动
-2. POST /user/register</t>
+          <t>50线程 POST /user/login</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>P95 &lt; 800ms, 错误率 &lt; 1%</t>
-        </is>
-      </c>
-      <c r="J28" s="2" t="n"/>
-      <c r="K28" s="2" t="n"/>
+          <t>P95&lt;500ms</t>
+        </is>
+      </c>
+      <c r="J28" s="2" t="inlineStr"/>
+      <c r="K28" s="2" t="inlineStr"/>
       <c r="L28" s="2" t="inlineStr">
         <is>
           <t>朱远亮</t>
         </is>
       </c>
-      <c r="M28" s="2" t="n"/>
+      <c r="M28" s="2" t="inlineStr"/>
     </row>
     <row r="29" ht="80" customHeight="1">
       <c r="A29" s="2" t="inlineStr">
         <is>
-          <t>TC-API-002</t>
+          <t>TC-API-001</t>
         </is>
       </c>
       <c r="B29" s="2" t="inlineStr">
@@ -2011,37 +1996,37 @@
       </c>
       <c r="F29" s="4" t="inlineStr">
         <is>
-          <t>注册_缺userAccount字段</t>
+          <t>注册_Content-Type错误</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>无账号</t>
+          <t>无</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>1. body 只有 userPassword 和 checkPassword</t>
+          <t>Content-Type=application/xml</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>返回code=40001</t>
-        </is>
-      </c>
-      <c r="J29" s="2" t="n"/>
-      <c r="K29" s="2" t="n"/>
+          <t>415</t>
+        </is>
+      </c>
+      <c r="J29" s="2" t="inlineStr"/>
+      <c r="K29" s="2" t="inlineStr"/>
       <c r="L29" s="2" t="inlineStr">
         <is>
           <t>朱远亮</t>
         </is>
       </c>
-      <c r="M29" s="2" t="n"/>
+      <c r="M29" s="2" t="inlineStr"/>
     </row>
     <row r="30" ht="80" customHeight="1">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>TC-PU-001</t>
+          <t>TC-SEC-001</t>
         </is>
       </c>
       <c r="B30" s="2" t="inlineStr">
@@ -2051,12 +2036,12 @@
       </c>
       <c r="C30" s="3" t="inlineStr">
         <is>
-          <t>/图片上传</t>
+          <t>/用户登录</t>
         </is>
       </c>
       <c r="D30" s="3" t="inlineStr">
         <is>
-          <t>功能测试</t>
+          <t>安全测试</t>
         </is>
       </c>
       <c r="E30" s="3" t="n">
@@ -2064,37 +2049,37 @@
       </c>
       <c r="F30" s="4" t="inlineStr">
         <is>
-          <t>本地上传_jpg_2MB</t>
+          <t>SQL注入_登录</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>testuser01 已登录</t>
+          <t>testuser01</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>1. POST /file/upload file=2MB_jpg</t>
+          <t>password="' OR 1=1 --"</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>返回code=0, url 字段为可访问图片链接</t>
-        </is>
-      </c>
-      <c r="J30" s="2" t="n"/>
-      <c r="K30" s="2" t="n"/>
+          <t>code=40001</t>
+        </is>
+      </c>
+      <c r="J30" s="2" t="inlineStr"/>
+      <c r="K30" s="2" t="inlineStr"/>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>李冠燃</t>
-        </is>
-      </c>
-      <c r="M30" s="2" t="n"/>
+          <t>朱远亮</t>
+        </is>
+      </c>
+      <c r="M30" s="2" t="inlineStr"/>
     </row>
     <row r="31" ht="80" customHeight="1">
       <c r="A31" s="2" t="inlineStr">
         <is>
-          <t>TC-PU-002</t>
+          <t>TC-SEC-002</t>
         </is>
       </c>
       <c r="B31" s="2" t="inlineStr">
@@ -2104,12 +2089,12 @@
       </c>
       <c r="C31" s="3" t="inlineStr">
         <is>
-          <t>/图片上传</t>
+          <t>/管理员</t>
         </is>
       </c>
       <c r="D31" s="3" t="inlineStr">
         <is>
-          <t>功能测试</t>
+          <t>安全测试</t>
         </is>
       </c>
       <c r="E31" s="3" t="n">
@@ -2117,37 +2102,37 @@
       </c>
       <c r="F31" s="4" t="inlineStr">
         <is>
-          <t>本地上传_png</t>
+          <t>越权_普通用户改userRole</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>testuser01 已登录</t>
+          <t>testuser01</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>1. POST /file/upload file=1MB_png</t>
+          <t>POST /user/update role='admin'</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>返回code=0, picFormat=png</t>
-        </is>
-      </c>
-      <c r="J31" s="2" t="n"/>
-      <c r="K31" s="2" t="n"/>
+          <t>code=40300</t>
+        </is>
+      </c>
+      <c r="J31" s="2" t="inlineStr"/>
+      <c r="K31" s="2" t="inlineStr"/>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>李冠燃</t>
-        </is>
-      </c>
-      <c r="M31" s="2" t="n"/>
+          <t>朱远亮</t>
+        </is>
+      </c>
+      <c r="M31" s="2" t="inlineStr"/>
     </row>
     <row r="32" ht="80" customHeight="1">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>TC-PU-003</t>
+          <t>TC-PD-001</t>
         </is>
       </c>
       <c r="B32" s="2" t="inlineStr">
@@ -2157,7 +2142,7 @@
       </c>
       <c r="C32" s="3" t="inlineStr">
         <is>
-          <t>/图片上传</t>
+          <t>/图片删除</t>
         </is>
       </c>
       <c r="D32" s="3" t="inlineStr">
@@ -2170,37 +2155,37 @@
       </c>
       <c r="F32" s="4" t="inlineStr">
         <is>
-          <t>本地上传_超过2MB_应失败</t>
+          <t>删除_自己的图片</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
         <is>
-          <t>testuser01 已登录</t>
+          <t>testuser01有图片</t>
         </is>
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>1. POST /file/upload file=5MB_jpg</t>
+          <t>POST /picture/delete id=我的图片</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>返回code=40001</t>
-        </is>
-      </c>
-      <c r="J32" s="2" t="n"/>
-      <c r="K32" s="2" t="n"/>
+          <t>code=0, isDelete=1</t>
+        </is>
+      </c>
+      <c r="J32" s="2" t="inlineStr"/>
+      <c r="K32" s="2" t="inlineStr"/>
       <c r="L32" s="2" t="inlineStr">
         <is>
           <t>李冠燃</t>
         </is>
       </c>
-      <c r="M32" s="2" t="n"/>
+      <c r="M32" s="2" t="inlineStr"/>
     </row>
     <row r="33" ht="80" customHeight="1">
       <c r="A33" s="2" t="inlineStr">
         <is>
-          <t>TC-PU-004</t>
+          <t>TC-PD-002</t>
         </is>
       </c>
       <c r="B33" s="2" t="inlineStr">
@@ -2210,7 +2195,7 @@
       </c>
       <c r="C33" s="3" t="inlineStr">
         <is>
-          <t>/图片上传</t>
+          <t>/图片删除</t>
         </is>
       </c>
       <c r="D33" s="3" t="inlineStr">
@@ -2219,41 +2204,41 @@
         </is>
       </c>
       <c r="E33" s="3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F33" s="4" t="inlineStr">
         <is>
-          <t>本地上传_非图片_应失败</t>
+          <t>删除_别人的图片_越权</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>testuser01 已登录</t>
+          <t>testuser02</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>1. POST /file/upload file=test.pdf</t>
+          <t>POST /picture/delete id=别人图片</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>返回code=40001</t>
-        </is>
-      </c>
-      <c r="J33" s="2" t="n"/>
-      <c r="K33" s="2" t="n"/>
+          <t>code=40300</t>
+        </is>
+      </c>
+      <c r="J33" s="2" t="inlineStr"/>
+      <c r="K33" s="2" t="inlineStr"/>
       <c r="L33" s="2" t="inlineStr">
         <is>
           <t>李冠燃</t>
         </is>
       </c>
-      <c r="M33" s="2" t="n"/>
+      <c r="M33" s="2" t="inlineStr"/>
     </row>
     <row r="34" ht="80" customHeight="1">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>TC-PU-005</t>
+          <t>TC-PD-003</t>
         </is>
       </c>
       <c r="B34" s="2" t="inlineStr">
@@ -2263,7 +2248,7 @@
       </c>
       <c r="C34" s="3" t="inlineStr">
         <is>
-          <t>/图片上传</t>
+          <t>/图片删除</t>
         </is>
       </c>
       <c r="D34" s="3" t="inlineStr">
@@ -2272,41 +2257,41 @@
         </is>
       </c>
       <c r="E34" s="3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F34" s="4" t="inlineStr">
         <is>
-          <t>本地上传_空文件_应失败</t>
+          <t>删除_不存在的图片</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
         <is>
-          <t>testuser01 已登录</t>
+          <t>admin</t>
         </is>
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>1. POST /file/upload file=0byte</t>
+          <t>POST /picture/delete id=999999</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>返回code=40001</t>
-        </is>
-      </c>
-      <c r="J34" s="2" t="n"/>
-      <c r="K34" s="2" t="n"/>
+          <t>code=40001</t>
+        </is>
+      </c>
+      <c r="J34" s="2" t="inlineStr"/>
+      <c r="K34" s="2" t="inlineStr"/>
       <c r="L34" s="2" t="inlineStr">
         <is>
           <t>李冠燃</t>
         </is>
       </c>
-      <c r="M34" s="2" t="n"/>
+      <c r="M34" s="2" t="inlineStr"/>
     </row>
     <row r="35" ht="80" customHeight="1">
       <c r="A35" s="2" t="inlineStr">
         <is>
-          <t>TC-PX-001</t>
+          <t>TC-PG-001</t>
         </is>
       </c>
       <c r="B35" s="2" t="inlineStr">
@@ -2316,7 +2301,7 @@
       </c>
       <c r="C35" s="3" t="inlineStr">
         <is>
-          <t>/图片搜索</t>
+          <t>/图片查询</t>
         </is>
       </c>
       <c r="D35" s="3" t="inlineStr">
@@ -2329,7 +2314,7 @@
       </c>
       <c r="F35" s="4" t="inlineStr">
         <is>
-          <t>关键字搜图_有结果</t>
+          <t>按id查询_正常</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
@@ -2339,27 +2324,27 @@
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>1. POST /picture/search/picture text='猫'</t>
+          <t>GET /picture/get?id=1</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>返回含'猫'的图片列表</t>
-        </is>
-      </c>
-      <c r="J35" s="2" t="n"/>
-      <c r="K35" s="2" t="n"/>
+          <t>code=0</t>
+        </is>
+      </c>
+      <c r="J35" s="2" t="inlineStr"/>
+      <c r="K35" s="2" t="inlineStr"/>
       <c r="L35" s="2" t="inlineStr">
         <is>
           <t>李冠燃</t>
         </is>
       </c>
-      <c r="M35" s="2" t="n"/>
+      <c r="M35" s="2" t="inlineStr"/>
     </row>
     <row r="36" ht="80" customHeight="1">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>TC-PX-002</t>
+          <t>TC-PG-002</t>
         </is>
       </c>
       <c r="B36" s="2" t="inlineStr">
@@ -2369,7 +2354,7 @@
       </c>
       <c r="C36" s="3" t="inlineStr">
         <is>
-          <t>/图片搜索</t>
+          <t>/图片查询</t>
         </is>
       </c>
       <c r="D36" s="3" t="inlineStr">
@@ -2382,7 +2367,7 @@
       </c>
       <c r="F36" s="4" t="inlineStr">
         <is>
-          <t>关键字搜图_无结果</t>
+          <t>按id查询_不存在</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -2392,27 +2377,27 @@
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>1. POST /picture/search/picture text='xyz999'</t>
+          <t>GET /picture/get?id=999999</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>返回空列表</t>
-        </is>
-      </c>
-      <c r="J36" s="2" t="n"/>
-      <c r="K36" s="2" t="n"/>
+          <t>code=40001</t>
+        </is>
+      </c>
+      <c r="J36" s="2" t="inlineStr"/>
+      <c r="K36" s="2" t="inlineStr"/>
       <c r="L36" s="2" t="inlineStr">
         <is>
           <t>李冠燃</t>
         </is>
       </c>
-      <c r="M36" s="2" t="n"/>
+      <c r="M36" s="2" t="inlineStr"/>
     </row>
     <row r="37" ht="80" customHeight="1">
       <c r="A37" s="2" t="inlineStr">
         <is>
-          <t>TC-PX-003</t>
+          <t>TC-PV-001</t>
         </is>
       </c>
       <c r="B37" s="2" t="inlineStr">
@@ -2422,7 +2407,7 @@
       </c>
       <c r="C37" s="3" t="inlineStr">
         <is>
-          <t>/图片搜索</t>
+          <t>/图片VO查询</t>
         </is>
       </c>
       <c r="D37" s="3" t="inlineStr">
@@ -2431,41 +2416,41 @@
         </is>
       </c>
       <c r="E37" s="3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F37" s="4" t="inlineStr">
         <is>
-          <t>关键字搜图_空文本</t>
+          <t>查询VO_正常</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>testuser01 已登录</t>
+          <t>已有图片</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>1. POST /picture/search/picture text=''</t>
+          <t>GET /picture/get/vo?id=1</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>返回code=40001 或全部图片</t>
-        </is>
-      </c>
-      <c r="J37" s="2" t="n"/>
-      <c r="K37" s="2" t="n"/>
+          <t>code=0, PictureVO</t>
+        </is>
+      </c>
+      <c r="J37" s="2" t="inlineStr"/>
+      <c r="K37" s="2" t="inlineStr"/>
       <c r="L37" s="2" t="inlineStr">
         <is>
           <t>李冠燃</t>
         </is>
       </c>
-      <c r="M37" s="2" t="n"/>
+      <c r="M37" s="2" t="inlineStr"/>
     </row>
     <row r="38" ht="80" customHeight="1">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>TC-PX-004</t>
+          <t>TC-PV-002</t>
         </is>
       </c>
       <c r="B38" s="2" t="inlineStr">
@@ -2475,7 +2460,7 @@
       </c>
       <c r="C38" s="3" t="inlineStr">
         <is>
-          <t>/图片搜索</t>
+          <t>/图片VO查询</t>
         </is>
       </c>
       <c r="D38" s="3" t="inlineStr">
@@ -2484,41 +2469,41 @@
         </is>
       </c>
       <c r="E38" s="3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F38" s="4" t="inlineStr">
         <is>
-          <t>关键字搜图_超长</t>
+          <t>查询VO_未登录</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
         <is>
-          <t>testuser01 已登录</t>
+          <t>无</t>
         </is>
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>1. text=1000字符</t>
+          <t>GET /picture/get/vo?id=1</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>返回code=40001</t>
-        </is>
-      </c>
-      <c r="J38" s="2" t="n"/>
-      <c r="K38" s="2" t="n"/>
+          <t>code=40100</t>
+        </is>
+      </c>
+      <c r="J38" s="2" t="inlineStr"/>
+      <c r="K38" s="2" t="inlineStr"/>
       <c r="L38" s="2" t="inlineStr">
         <is>
           <t>李冠燃</t>
         </is>
       </c>
-      <c r="M38" s="2" t="n"/>
+      <c r="M38" s="2" t="inlineStr"/>
     </row>
     <row r="39" ht="80" customHeight="1">
       <c r="A39" s="2" t="inlineStr">
         <is>
-          <t>TC-PX-005</t>
+          <t>TC-PE-001</t>
         </is>
       </c>
       <c r="B39" s="2" t="inlineStr">
@@ -2528,7 +2513,7 @@
       </c>
       <c r="C39" s="3" t="inlineStr">
         <is>
-          <t>/图片搜索</t>
+          <t>/图片编辑</t>
         </is>
       </c>
       <c r="D39" s="3" t="inlineStr">
@@ -2537,41 +2522,41 @@
         </is>
       </c>
       <c r="E39" s="3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F39" s="4" t="inlineStr">
         <is>
-          <t>关键字搜图_未登录</t>
+          <t>编辑_名称正常</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
         <is>
-          <t>无</t>
+          <t>testuser01有图片</t>
         </is>
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t>1. POST /picture/search/picture</t>
+          <t>POST /picture/edit id=1 name='新名'</t>
         </is>
       </c>
       <c r="I39" s="2" t="inlineStr">
         <is>
-          <t>返回code=40100</t>
-        </is>
-      </c>
-      <c r="J39" s="2" t="n"/>
-      <c r="K39" s="2" t="n"/>
+          <t>code=0</t>
+        </is>
+      </c>
+      <c r="J39" s="2" t="inlineStr"/>
+      <c r="K39" s="2" t="inlineStr"/>
       <c r="L39" s="2" t="inlineStr">
         <is>
           <t>李冠燃</t>
         </is>
       </c>
-      <c r="M39" s="2" t="n"/>
+      <c r="M39" s="2" t="inlineStr"/>
     </row>
     <row r="40" ht="80" customHeight="1">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>TC-PERF-001</t>
+          <t>TC-PE-002</t>
         </is>
       </c>
       <c r="B40" s="2" t="inlineStr">
@@ -2581,50 +2566,50 @@
       </c>
       <c r="C40" s="3" t="inlineStr">
         <is>
-          <t>/图片上传</t>
+          <t>/图片编辑</t>
         </is>
       </c>
       <c r="D40" s="3" t="inlineStr">
         <is>
-          <t>性能测试</t>
+          <t>功能测试</t>
         </is>
       </c>
       <c r="E40" s="3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F40" s="4" t="inlineStr">
         <is>
-          <t>上传_20并发</t>
+          <t>编辑_越权</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
         <is>
-          <t>已安装 JMeter</t>
+          <t>testuser02</t>
         </is>
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t>1. JMeter 20 线程上传 2MB jpg</t>
+          <t>POST /picture/edit id=别人图片</t>
         </is>
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t>P95 &lt; 3s, 错误率 &lt; 5%</t>
-        </is>
-      </c>
-      <c r="J40" s="2" t="n"/>
-      <c r="K40" s="2" t="n"/>
+          <t>code=40300</t>
+        </is>
+      </c>
+      <c r="J40" s="2" t="inlineStr"/>
+      <c r="K40" s="2" t="inlineStr"/>
       <c r="L40" s="2" t="inlineStr">
         <is>
           <t>李冠燃</t>
         </is>
       </c>
-      <c r="M40" s="2" t="n"/>
+      <c r="M40" s="2" t="inlineStr"/>
     </row>
     <row r="41" ht="80" customHeight="1">
       <c r="A41" s="2" t="inlineStr">
         <is>
-          <t>TC-API-001</t>
+          <t>TC-PE-003</t>
         </is>
       </c>
       <c r="B41" s="2" t="inlineStr">
@@ -2634,50 +2619,50 @@
       </c>
       <c r="C41" s="3" t="inlineStr">
         <is>
-          <t>/图片上传</t>
+          <t>/图片编辑</t>
         </is>
       </c>
       <c r="D41" s="3" t="inlineStr">
         <is>
-          <t>接口测试</t>
+          <t>功能测试</t>
         </is>
       </c>
       <c r="E41" s="3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F41" s="4" t="inlineStr">
         <is>
-          <t>上传_缺multipart边界</t>
+          <t>编辑_不存在</t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr">
         <is>
-          <t>testuser01 已登录</t>
+          <t>admin</t>
         </is>
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
-          <t>1. 发送不完整 multipart 请求</t>
+          <t>POST /picture/edit id=999999</t>
         </is>
       </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t>返回 400 或 415</t>
-        </is>
-      </c>
-      <c r="J41" s="2" t="n"/>
-      <c r="K41" s="2" t="n"/>
+          <t>code=40001</t>
+        </is>
+      </c>
+      <c r="J41" s="2" t="inlineStr"/>
+      <c r="K41" s="2" t="inlineStr"/>
       <c r="L41" s="2" t="inlineStr">
         <is>
           <t>李冠燃</t>
         </is>
       </c>
-      <c r="M41" s="2" t="n"/>
+      <c r="M41" s="2" t="inlineStr"/>
     </row>
     <row r="42" ht="80" customHeight="1">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>TC-SEC-001</t>
+          <t>TC-EB-001</t>
         </is>
       </c>
       <c r="B42" s="2" t="inlineStr">
@@ -2687,12 +2672,12 @@
       </c>
       <c r="C42" s="3" t="inlineStr">
         <is>
-          <t>/图片上传</t>
+          <t>/图片批量编辑</t>
         </is>
       </c>
       <c r="D42" s="3" t="inlineStr">
         <is>
-          <t>安全测试</t>
+          <t>功能测试</t>
         </is>
       </c>
       <c r="E42" s="3" t="n">
@@ -2700,37 +2685,37 @@
       </c>
       <c r="F42" s="4" t="inlineStr">
         <is>
-          <t>上传_伪PHP木马</t>
+          <t>批量编辑_正常</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
         <is>
-          <t>testuser01 已登录</t>
+          <t>testuser01有多张</t>
         </is>
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t>1. file=1.jpg 内容为 &lt;?php system($_GET['c']);?&gt;</t>
+          <t>POST /picture/edit/batch ids=[1,2,3] category='风景'</t>
         </is>
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t>返回code=40001</t>
-        </is>
-      </c>
-      <c r="J42" s="2" t="n"/>
-      <c r="K42" s="2" t="n"/>
+          <t>code=0</t>
+        </is>
+      </c>
+      <c r="J42" s="2" t="inlineStr"/>
+      <c r="K42" s="2" t="inlineStr"/>
       <c r="L42" s="2" t="inlineStr">
         <is>
           <t>李冠燃</t>
         </is>
       </c>
-      <c r="M42" s="2" t="n"/>
+      <c r="M42" s="2" t="inlineStr"/>
     </row>
     <row r="43" ht="80" customHeight="1">
       <c r="A43" s="2" t="inlineStr">
         <is>
-          <t>TC-PU-006</t>
+          <t>TC-EB-002</t>
         </is>
       </c>
       <c r="B43" s="2" t="inlineStr">
@@ -2740,7 +2725,7 @@
       </c>
       <c r="C43" s="3" t="inlineStr">
         <is>
-          <t>/图片上传</t>
+          <t>/图片批量编辑</t>
         </is>
       </c>
       <c r="D43" s="3" t="inlineStr">
@@ -2749,41 +2734,41 @@
         </is>
       </c>
       <c r="E43" s="3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F43" s="4" t="inlineStr">
         <is>
-          <t>上传_bmp格式</t>
+          <t>批量编辑_越权</t>
         </is>
       </c>
       <c r="G43" s="2" t="inlineStr">
         <is>
-          <t>testuser01 已登录</t>
+          <t>testuser02</t>
         </is>
       </c>
       <c r="H43" s="2" t="inlineStr">
         <is>
-          <t>1. POST /file/upload file=1MB_bmp</t>
+          <t>POST /picture/edit/batch ids=[别人图片]</t>
         </is>
       </c>
       <c r="I43" s="2" t="inlineStr">
         <is>
-          <t>返回code=0 picFormat=bmp</t>
-        </is>
-      </c>
-      <c r="J43" s="2" t="n"/>
-      <c r="K43" s="2" t="n"/>
+          <t>code=40300</t>
+        </is>
+      </c>
+      <c r="J43" s="2" t="inlineStr"/>
+      <c r="K43" s="2" t="inlineStr"/>
       <c r="L43" s="2" t="inlineStr">
         <is>
           <t>李冠燃</t>
         </is>
       </c>
-      <c r="M43" s="2" t="n"/>
+      <c r="M43" s="2" t="inlineStr"/>
     </row>
     <row r="44" ht="80" customHeight="1">
       <c r="A44" s="2" t="inlineStr">
         <is>
-          <t>TC-PU-007</t>
+          <t>TC-PU-001</t>
         </is>
       </c>
       <c r="B44" s="2" t="inlineStr">
@@ -2793,7 +2778,7 @@
       </c>
       <c r="C44" s="3" t="inlineStr">
         <is>
-          <t>/图片上传</t>
+          <t>/图片更新</t>
         </is>
       </c>
       <c r="D44" s="3" t="inlineStr">
@@ -2802,41 +2787,41 @@
         </is>
       </c>
       <c r="E44" s="3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F44" s="4" t="inlineStr">
         <is>
-          <t>上传_gif格式</t>
+          <t>更新_正常</t>
         </is>
       </c>
       <c r="G44" s="2" t="inlineStr">
         <is>
-          <t>testuser01 已登录</t>
+          <t>admin</t>
         </is>
       </c>
       <c r="H44" s="2" t="inlineStr">
         <is>
-          <t>1. POST /file/upload file=1MB_gif</t>
+          <t>POST /picture/update id=1 name='更新名'</t>
         </is>
       </c>
       <c r="I44" s="2" t="inlineStr">
         <is>
-          <t>返回code=0 picFormat=gif</t>
-        </is>
-      </c>
-      <c r="J44" s="2" t="n"/>
-      <c r="K44" s="2" t="n"/>
+          <t>code=0</t>
+        </is>
+      </c>
+      <c r="J44" s="2" t="inlineStr"/>
+      <c r="K44" s="2" t="inlineStr"/>
       <c r="L44" s="2" t="inlineStr">
         <is>
           <t>李冠燃</t>
         </is>
       </c>
-      <c r="M44" s="2" t="n"/>
+      <c r="M44" s="2" t="inlineStr"/>
     </row>
     <row r="45" ht="80" customHeight="1">
       <c r="A45" s="2" t="inlineStr">
         <is>
-          <t>TC-PU-008</t>
+          <t>TC-PU-002</t>
         </is>
       </c>
       <c r="B45" s="2" t="inlineStr">
@@ -2846,7 +2831,7 @@
       </c>
       <c r="C45" s="3" t="inlineStr">
         <is>
-          <t>/图片上传</t>
+          <t>/图片更新</t>
         </is>
       </c>
       <c r="D45" s="3" t="inlineStr">
@@ -2855,41 +2840,41 @@
         </is>
       </c>
       <c r="E45" s="3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F45" s="4" t="inlineStr">
         <is>
-          <t>上传_webp格式</t>
+          <t>更新_普通用户越权</t>
         </is>
       </c>
       <c r="G45" s="2" t="inlineStr">
         <is>
-          <t>testuser01 已登录</t>
+          <t>testuser01</t>
         </is>
       </c>
       <c r="H45" s="2" t="inlineStr">
         <is>
-          <t>1. POST /file/upload file=1MB_webp</t>
+          <t>POST /picture/update</t>
         </is>
       </c>
       <c r="I45" s="2" t="inlineStr">
         <is>
-          <t>返回code=0 picFormat=webp</t>
-        </is>
-      </c>
-      <c r="J45" s="2" t="n"/>
-      <c r="K45" s="2" t="n"/>
+          <t>code=40300</t>
+        </is>
+      </c>
+      <c r="J45" s="2" t="inlineStr"/>
+      <c r="K45" s="2" t="inlineStr"/>
       <c r="L45" s="2" t="inlineStr">
         <is>
           <t>李冠燃</t>
         </is>
       </c>
-      <c r="M45" s="2" t="n"/>
+      <c r="M45" s="2" t="inlineStr"/>
     </row>
     <row r="46" ht="80" customHeight="1">
       <c r="A46" s="2" t="inlineStr">
         <is>
-          <t>TC-PU-009</t>
+          <t>TC-PL-001</t>
         </is>
       </c>
       <c r="B46" s="2" t="inlineStr">
@@ -2899,7 +2884,7 @@
       </c>
       <c r="C46" s="3" t="inlineStr">
         <is>
-          <t>/图片上传</t>
+          <t>/图片分页</t>
         </is>
       </c>
       <c r="D46" s="3" t="inlineStr">
@@ -2908,41 +2893,41 @@
         </is>
       </c>
       <c r="E46" s="3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F46" s="4" t="inlineStr">
         <is>
-          <t>上传_文件名含中文</t>
+          <t>分页查询_默认</t>
         </is>
       </c>
       <c r="G46" s="2" t="inlineStr">
         <is>
-          <t>testuser01 已登录</t>
+          <t>admin</t>
         </is>
       </c>
       <c r="H46" s="2" t="inlineStr">
         <is>
-          <t>1. POST /file/upload file=中文图片.jpg</t>
+          <t>POST /picture/list/page current=1 pageSize=10</t>
         </is>
       </c>
       <c r="I46" s="2" t="inlineStr">
         <is>
-          <t>返回code=0 url 正确编码</t>
-        </is>
-      </c>
-      <c r="J46" s="2" t="n"/>
-      <c r="K46" s="2" t="n"/>
+          <t>code=0, records</t>
+        </is>
+      </c>
+      <c r="J46" s="2" t="inlineStr"/>
+      <c r="K46" s="2" t="inlineStr"/>
       <c r="L46" s="2" t="inlineStr">
         <is>
           <t>李冠燃</t>
         </is>
       </c>
-      <c r="M46" s="2" t="n"/>
+      <c r="M46" s="2" t="inlineStr"/>
     </row>
     <row r="47" ht="80" customHeight="1">
       <c r="A47" s="2" t="inlineStr">
         <is>
-          <t>TC-PU-010</t>
+          <t>TC-PL-002</t>
         </is>
       </c>
       <c r="B47" s="2" t="inlineStr">
@@ -2952,7 +2937,7 @@
       </c>
       <c r="C47" s="3" t="inlineStr">
         <is>
-          <t>/图片上传</t>
+          <t>/图片分页</t>
         </is>
       </c>
       <c r="D47" s="3" t="inlineStr">
@@ -2961,41 +2946,41 @@
         </is>
       </c>
       <c r="E47" s="3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F47" s="4" t="inlineStr">
         <is>
-          <t>上传_文件名含特殊字符</t>
+          <t>分页查询_普通用户</t>
         </is>
       </c>
       <c r="G47" s="2" t="inlineStr">
         <is>
-          <t>testuser01 已登录</t>
+          <t>testuser01</t>
         </is>
       </c>
       <c r="H47" s="2" t="inlineStr">
         <is>
-          <t>1. POST /file/upload file='im$g.jpg'</t>
+          <t>POST /picture/list/page</t>
         </is>
       </c>
       <c r="I47" s="2" t="inlineStr">
         <is>
-          <t>返回code=0 url 已转义</t>
-        </is>
-      </c>
-      <c r="J47" s="2" t="n"/>
-      <c r="K47" s="2" t="n"/>
+          <t>code=40100或code=0</t>
+        </is>
+      </c>
+      <c r="J47" s="2" t="inlineStr"/>
+      <c r="K47" s="2" t="inlineStr"/>
       <c r="L47" s="2" t="inlineStr">
         <is>
           <t>李冠燃</t>
         </is>
       </c>
-      <c r="M47" s="2" t="n"/>
+      <c r="M47" s="2" t="inlineStr"/>
     </row>
     <row r="48" ht="80" customHeight="1">
       <c r="A48" s="2" t="inlineStr">
         <is>
-          <t>TC-PX-006</t>
+          <t>TC-PL-003</t>
         </is>
       </c>
       <c r="B48" s="2" t="inlineStr">
@@ -3005,7 +2990,7 @@
       </c>
       <c r="C48" s="3" t="inlineStr">
         <is>
-          <t>/图片搜索</t>
+          <t>/图片分页</t>
         </is>
       </c>
       <c r="D48" s="3" t="inlineStr">
@@ -3018,37 +3003,37 @@
       </c>
       <c r="F48" s="4" t="inlineStr">
         <is>
-          <t>搜图_精确匹配</t>
+          <t>分页查询_空页</t>
         </is>
       </c>
       <c r="G48" s="2" t="inlineStr">
         <is>
-          <t>已有图片</t>
+          <t>admin</t>
         </is>
       </c>
       <c r="H48" s="2" t="inlineStr">
         <is>
-          <t>1. POST /picture/search/picture text='StarPicture'</t>
+          <t>current=9999 pageSize=10</t>
         </is>
       </c>
       <c r="I48" s="2" t="inlineStr">
         <is>
-          <t>返回code=0 含结果</t>
-        </is>
-      </c>
-      <c r="J48" s="2" t="n"/>
-      <c r="K48" s="2" t="n"/>
+          <t>code=0, records=[]</t>
+        </is>
+      </c>
+      <c r="J48" s="2" t="inlineStr"/>
+      <c r="K48" s="2" t="inlineStr"/>
       <c r="L48" s="2" t="inlineStr">
         <is>
           <t>李冠燃</t>
         </is>
       </c>
-      <c r="M48" s="2" t="n"/>
+      <c r="M48" s="2" t="inlineStr"/>
     </row>
     <row r="49" ht="80" customHeight="1">
       <c r="A49" s="2" t="inlineStr">
         <is>
-          <t>TC-PX-007</t>
+          <t>TC-LV-001</t>
         </is>
       </c>
       <c r="B49" s="2" t="inlineStr">
@@ -3058,50 +3043,50 @@
       </c>
       <c r="C49" s="3" t="inlineStr">
         <is>
-          <t>/图片搜索</t>
+          <t>/图片VO分页</t>
         </is>
       </c>
       <c r="D49" s="3" t="inlineStr">
         <is>
-          <t>接口测试</t>
+          <t>功能测试</t>
         </is>
       </c>
       <c r="E49" s="3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F49" s="4" t="inlineStr">
         <is>
-          <t>搜图_缺text字段</t>
+          <t>VO分页_正常</t>
         </is>
       </c>
       <c r="G49" s="2" t="inlineStr">
         <is>
-          <t>testuser01 已登录</t>
+          <t>admin</t>
         </is>
       </c>
       <c r="H49" s="2" t="inlineStr">
         <is>
-          <t>1. body 为空</t>
+          <t>POST /picture/list/page/vo</t>
         </is>
       </c>
       <c r="I49" s="2" t="inlineStr">
         <is>
-          <t>返回code=40001</t>
-        </is>
-      </c>
-      <c r="J49" s="2" t="n"/>
-      <c r="K49" s="2" t="n"/>
+          <t>code=0, PictureVO列表</t>
+        </is>
+      </c>
+      <c r="J49" s="2" t="inlineStr"/>
+      <c r="K49" s="2" t="inlineStr"/>
       <c r="L49" s="2" t="inlineStr">
         <is>
           <t>李冠燃</t>
         </is>
       </c>
-      <c r="M49" s="2" t="n"/>
+      <c r="M49" s="2" t="inlineStr"/>
     </row>
     <row r="50" ht="80" customHeight="1">
       <c r="A50" s="2" t="inlineStr">
         <is>
-          <t>TC-PX-008</t>
+          <t>TC-LV-002</t>
         </is>
       </c>
       <c r="B50" s="2" t="inlineStr">
@@ -3111,12 +3096,12 @@
       </c>
       <c r="C50" s="3" t="inlineStr">
         <is>
-          <t>/图片搜索</t>
+          <t>/图片VO分页</t>
         </is>
       </c>
       <c r="D50" s="3" t="inlineStr">
         <is>
-          <t>安全测试</t>
+          <t>功能测试</t>
         </is>
       </c>
       <c r="E50" s="3" t="n">
@@ -3124,37 +3109,37 @@
       </c>
       <c r="F50" s="4" t="inlineStr">
         <is>
-          <t>搜图_SQL注入</t>
+          <t>VO分页_普通用户</t>
         </is>
       </c>
       <c r="G50" s="2" t="inlineStr">
         <is>
-          <t>testuser01 已登录</t>
+          <t>testuser01</t>
         </is>
       </c>
       <c r="H50" s="2" t="inlineStr">
         <is>
-          <t>1. text="' OR 1=1 --"</t>
+          <t>POST /picture/list/page/vo</t>
         </is>
       </c>
       <c r="I50" s="2" t="inlineStr">
         <is>
-          <t>返回code=40001 拒绝注入</t>
-        </is>
-      </c>
-      <c r="J50" s="2" t="n"/>
-      <c r="K50" s="2" t="n"/>
+          <t>code=40100或code=0</t>
+        </is>
+      </c>
+      <c r="J50" s="2" t="inlineStr"/>
+      <c r="K50" s="2" t="inlineStr"/>
       <c r="L50" s="2" t="inlineStr">
         <is>
           <t>李冠燃</t>
         </is>
       </c>
-      <c r="M50" s="2" t="n"/>
+      <c r="M50" s="2" t="inlineStr"/>
     </row>
     <row r="51" ht="80" customHeight="1">
       <c r="A51" s="2" t="inlineStr">
         <is>
-          <t>TC-PX-009</t>
+          <t>TC-VC-001</t>
         </is>
       </c>
       <c r="B51" s="2" t="inlineStr">
@@ -3164,12 +3149,12 @@
       </c>
       <c r="C51" s="3" t="inlineStr">
         <is>
-          <t>/图片搜索</t>
+          <t>/图片缓存分页</t>
         </is>
       </c>
       <c r="D51" s="3" t="inlineStr">
         <is>
-          <t>安全测试</t>
+          <t>功能测试</t>
         </is>
       </c>
       <c r="E51" s="3" t="n">
@@ -3177,37 +3162,37 @@
       </c>
       <c r="F51" s="4" t="inlineStr">
         <is>
-          <t>搜图_XSS注入</t>
+          <t>缓存分页_正常</t>
         </is>
       </c>
       <c r="G51" s="2" t="inlineStr">
         <is>
-          <t>testuser01 已登录</t>
+          <t>admin</t>
         </is>
       </c>
       <c r="H51" s="2" t="inlineStr">
         <is>
-          <t>1. text="&lt;script&gt;alert(1)&lt;/script&gt;"</t>
+          <t>POST /picture/list/page/vo/cache</t>
         </is>
       </c>
       <c r="I51" s="2" t="inlineStr">
         <is>
-          <t>返回code=0 渲染时被转义</t>
-        </is>
-      </c>
-      <c r="J51" s="2" t="n"/>
-      <c r="K51" s="2" t="n"/>
+          <t>code=0, 含缓存</t>
+        </is>
+      </c>
+      <c r="J51" s="2" t="inlineStr"/>
+      <c r="K51" s="2" t="inlineStr"/>
       <c r="L51" s="2" t="inlineStr">
         <is>
           <t>李冠燃</t>
         </is>
       </c>
-      <c r="M51" s="2" t="n"/>
+      <c r="M51" s="2" t="inlineStr"/>
     </row>
     <row r="52" ht="80" customHeight="1">
       <c r="A52" s="2" t="inlineStr">
         <is>
-          <t>TC-PX-010</t>
+          <t>TC-TG-001</t>
         </is>
       </c>
       <c r="B52" s="2" t="inlineStr">
@@ -3217,7 +3202,7 @@
       </c>
       <c r="C52" s="3" t="inlineStr">
         <is>
-          <t>/图片搜索</t>
+          <t>/图片标签分类</t>
         </is>
       </c>
       <c r="D52" s="3" t="inlineStr">
@@ -3226,11 +3211,11 @@
         </is>
       </c>
       <c r="E52" s="3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F52" s="4" t="inlineStr">
         <is>
-          <t>搜图_含Unicode字符</t>
+          <t>获取标签分类</t>
         </is>
       </c>
       <c r="G52" s="2" t="inlineStr">
@@ -3240,27 +3225,27 @@
       </c>
       <c r="H52" s="2" t="inlineStr">
         <is>
-          <t>1. text='测试中文搜索'</t>
+          <t>GET /picture/tag_category</t>
         </is>
       </c>
       <c r="I52" s="2" t="inlineStr">
         <is>
-          <t>返回code=0</t>
-        </is>
-      </c>
-      <c r="J52" s="2" t="n"/>
-      <c r="K52" s="2" t="n"/>
+          <t>code=0, tags+categories</t>
+        </is>
+      </c>
+      <c r="J52" s="2" t="inlineStr"/>
+      <c r="K52" s="2" t="inlineStr"/>
       <c r="L52" s="2" t="inlineStr">
         <is>
           <t>李冠燃</t>
         </is>
       </c>
-      <c r="M52" s="2" t="n"/>
+      <c r="M52" s="2" t="inlineStr"/>
     </row>
     <row r="53" ht="80" customHeight="1">
       <c r="A53" s="2" t="inlineStr">
         <is>
-          <t>TC-PG-001</t>
+          <t>TC-RV-001</t>
         </is>
       </c>
       <c r="B53" s="2" t="inlineStr">
@@ -3270,7 +3255,7 @@
       </c>
       <c r="C53" s="3" t="inlineStr">
         <is>
-          <t>/图片管理</t>
+          <t>/图片审核</t>
         </is>
       </c>
       <c r="D53" s="3" t="inlineStr">
@@ -3283,37 +3268,37 @@
       </c>
       <c r="F53" s="4" t="inlineStr">
         <is>
-          <t>按id查询图片</t>
+          <t>审核_通过</t>
         </is>
       </c>
       <c r="G53" s="2" t="inlineStr">
         <is>
-          <t>已有图片</t>
+          <t>admin,待审核图片</t>
         </is>
       </c>
       <c r="H53" s="2" t="inlineStr">
         <is>
-          <t>1. GET /picture/get/vo?id=1</t>
+          <t>POST /picture/review id=1 reviewStatus=1</t>
         </is>
       </c>
       <c r="I53" s="2" t="inlineStr">
         <is>
-          <t>返回code=0 含完整图片信息</t>
-        </is>
-      </c>
-      <c r="J53" s="2" t="n"/>
-      <c r="K53" s="2" t="n"/>
+          <t>code=0</t>
+        </is>
+      </c>
+      <c r="J53" s="2" t="inlineStr"/>
+      <c r="K53" s="2" t="inlineStr"/>
       <c r="L53" s="2" t="inlineStr">
         <is>
           <t>李冠燃</t>
         </is>
       </c>
-      <c r="M53" s="2" t="n"/>
+      <c r="M53" s="2" t="inlineStr"/>
     </row>
     <row r="54" ht="80" customHeight="1">
       <c r="A54" s="2" t="inlineStr">
         <is>
-          <t>TC-PG-002</t>
+          <t>TC-RV-002</t>
         </is>
       </c>
       <c r="B54" s="2" t="inlineStr">
@@ -3323,7 +3308,7 @@
       </c>
       <c r="C54" s="3" t="inlineStr">
         <is>
-          <t>/图片管理</t>
+          <t>/图片审核</t>
         </is>
       </c>
       <c r="D54" s="3" t="inlineStr">
@@ -3336,37 +3321,37 @@
       </c>
       <c r="F54" s="4" t="inlineStr">
         <is>
-          <t>分页查询所有图片</t>
+          <t>审核_拒绝</t>
         </is>
       </c>
       <c r="G54" s="2" t="inlineStr">
         <is>
-          <t>testuser01 已登录</t>
+          <t>admin</t>
         </is>
       </c>
       <c r="H54" s="2" t="inlineStr">
         <is>
-          <t>1. POST /picture/list/page/vo current=1 pageSize=10</t>
+          <t>POST /picture/review id=1 reviewStatus=2</t>
         </is>
       </c>
       <c r="I54" s="2" t="inlineStr">
         <is>
-          <t>返回code=0 records含图片列表</t>
-        </is>
-      </c>
-      <c r="J54" s="2" t="n"/>
-      <c r="K54" s="2" t="n"/>
+          <t>code=0</t>
+        </is>
+      </c>
+      <c r="J54" s="2" t="inlineStr"/>
+      <c r="K54" s="2" t="inlineStr"/>
       <c r="L54" s="2" t="inlineStr">
         <is>
           <t>李冠燃</t>
         </is>
       </c>
-      <c r="M54" s="2" t="n"/>
+      <c r="M54" s="2" t="inlineStr"/>
     </row>
     <row r="55" ht="80" customHeight="1">
       <c r="A55" s="2" t="inlineStr">
         <is>
-          <t>TC-PG-003</t>
+          <t>TC-RV-003</t>
         </is>
       </c>
       <c r="B55" s="2" t="inlineStr">
@@ -3376,50 +3361,50 @@
       </c>
       <c r="C55" s="3" t="inlineStr">
         <is>
-          <t>/图片管理</t>
+          <t>/图片审核</t>
         </is>
       </c>
       <c r="D55" s="3" t="inlineStr">
         <is>
-          <t>接口测试</t>
+          <t>功能测试</t>
         </is>
       </c>
       <c r="E55" s="3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F55" s="4" t="inlineStr">
         <is>
-          <t>查询_id类型错误</t>
+          <t>审核_普通用户越权</t>
         </is>
       </c>
       <c r="G55" s="2" t="inlineStr">
         <is>
-          <t>testuser01 已登录</t>
+          <t>testuser01</t>
         </is>
       </c>
       <c r="H55" s="2" t="inlineStr">
         <is>
-          <t>1. GET /picture/get/vo?id='abc'</t>
+          <t>POST /picture/review</t>
         </is>
       </c>
       <c r="I55" s="2" t="inlineStr">
         <is>
-          <t>返回code=40001</t>
-        </is>
-      </c>
-      <c r="J55" s="2" t="n"/>
-      <c r="K55" s="2" t="n"/>
+          <t>code=40300</t>
+        </is>
+      </c>
+      <c r="J55" s="2" t="inlineStr"/>
+      <c r="K55" s="2" t="inlineStr"/>
       <c r="L55" s="2" t="inlineStr">
         <is>
           <t>李冠燃</t>
         </is>
       </c>
-      <c r="M55" s="2" t="n"/>
+      <c r="M55" s="2" t="inlineStr"/>
     </row>
     <row r="56" ht="80" customHeight="1">
       <c r="A56" s="2" t="inlineStr">
         <is>
-          <t>TC-PERF-002</t>
+          <t>TC-UR-001</t>
         </is>
       </c>
       <c r="B56" s="2" t="inlineStr">
@@ -3429,50 +3414,50 @@
       </c>
       <c r="C56" s="3" t="inlineStr">
         <is>
-          <t>/图片搜索</t>
+          <t>/URL上传</t>
         </is>
       </c>
       <c r="D56" s="3" t="inlineStr">
         <is>
-          <t>性能测试</t>
+          <t>功能测试</t>
         </is>
       </c>
       <c r="E56" s="3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F56" s="4" t="inlineStr">
         <is>
-          <t>搜图_50并发</t>
+          <t>URL上传_正常</t>
         </is>
       </c>
       <c r="G56" s="2" t="inlineStr">
         <is>
-          <t>已安装 JMeter</t>
+          <t>testuser01</t>
         </is>
       </c>
       <c r="H56" s="2" t="inlineStr">
         <is>
-          <t>1. JMeter 50 线程 POST /picture/search/picture</t>
+          <t>POST /picture/upload/url fileUrl='https://example.com/1.jpg'</t>
         </is>
       </c>
       <c r="I56" s="2" t="inlineStr">
         <is>
-          <t>P95 &lt; 500ms, 错误率 &lt; 1%</t>
-        </is>
-      </c>
-      <c r="J56" s="2" t="n"/>
-      <c r="K56" s="2" t="n"/>
+          <t>code=0</t>
+        </is>
+      </c>
+      <c r="J56" s="2" t="inlineStr"/>
+      <c r="K56" s="2" t="inlineStr"/>
       <c r="L56" s="2" t="inlineStr">
         <is>
           <t>李冠燃</t>
         </is>
       </c>
-      <c r="M56" s="2" t="n"/>
+      <c r="M56" s="2" t="inlineStr"/>
     </row>
     <row r="57" ht="80" customHeight="1">
       <c r="A57" s="2" t="inlineStr">
         <is>
-          <t>TC-URL-001</t>
+          <t>TC-UR-002</t>
         </is>
       </c>
       <c r="B57" s="2" t="inlineStr">
@@ -3482,12 +3467,12 @@
       </c>
       <c r="C57" s="3" t="inlineStr">
         <is>
-          <t>/图片上传</t>
+          <t>/URL上传</t>
         </is>
       </c>
       <c r="D57" s="3" t="inlineStr">
         <is>
-          <t>安全测试</t>
+          <t>功能测试</t>
         </is>
       </c>
       <c r="E57" s="3" t="n">
@@ -3495,37 +3480,37 @@
       </c>
       <c r="F57" s="4" t="inlineStr">
         <is>
-          <t>URL上传_内网IP</t>
+          <t>URL上传_内网IP_拒绝</t>
         </is>
       </c>
       <c r="G57" s="2" t="inlineStr">
         <is>
-          <t>testuser01 已登录</t>
+          <t>testuser01</t>
         </is>
       </c>
       <c r="H57" s="2" t="inlineStr">
         <is>
-          <t>1. fileUrl='http://127.0.0.1/x.jpg'</t>
+          <t>fileUrl='http://127.0.0.1/x.jpg'</t>
         </is>
       </c>
       <c r="I57" s="2" t="inlineStr">
         <is>
-          <t>返回code=40001 拒绝内网</t>
-        </is>
-      </c>
-      <c r="J57" s="2" t="n"/>
-      <c r="K57" s="2" t="n"/>
+          <t>code=40001</t>
+        </is>
+      </c>
+      <c r="J57" s="2" t="inlineStr"/>
+      <c r="K57" s="2" t="inlineStr"/>
       <c r="L57" s="2" t="inlineStr">
         <is>
           <t>李冠燃</t>
         </is>
       </c>
-      <c r="M57" s="2" t="n"/>
+      <c r="M57" s="2" t="inlineStr"/>
     </row>
     <row r="58" ht="80" customHeight="1">
       <c r="A58" s="2" t="inlineStr">
         <is>
-          <t>TC-SP-001</t>
+          <t>TC-UR-003</t>
         </is>
       </c>
       <c r="B58" s="2" t="inlineStr">
@@ -3535,7 +3520,7 @@
       </c>
       <c r="C58" s="3" t="inlineStr">
         <is>
-          <t>/空间管理</t>
+          <t>/URL上传</t>
         </is>
       </c>
       <c r="D58" s="3" t="inlineStr">
@@ -3548,37 +3533,37 @@
       </c>
       <c r="F58" s="4" t="inlineStr">
         <is>
-          <t>获取空间等级列表</t>
+          <t>URL上传_404</t>
         </is>
       </c>
       <c r="G58" s="2" t="inlineStr">
         <is>
-          <t>无</t>
+          <t>testuser01</t>
         </is>
       </c>
       <c r="H58" s="2" t="inlineStr">
         <is>
-          <t>1. GET /space/list/level</t>
+          <t>fileUrl='https://example.com/404.jpg'</t>
         </is>
       </c>
       <c r="I58" s="2" t="inlineStr">
         <is>
-          <t>返回code=0, 含普通版/专业版/旗舰版</t>
-        </is>
-      </c>
-      <c r="J58" s="2" t="n"/>
-      <c r="K58" s="2" t="n"/>
+          <t>code=40001</t>
+        </is>
+      </c>
+      <c r="J58" s="2" t="inlineStr"/>
+      <c r="K58" s="2" t="inlineStr"/>
       <c r="L58" s="2" t="inlineStr">
         <is>
-          <t>李坤纬</t>
-        </is>
-      </c>
-      <c r="M58" s="2" t="n"/>
+          <t>李冠燃</t>
+        </is>
+      </c>
+      <c r="M58" s="2" t="inlineStr"/>
     </row>
     <row r="59" ht="80" customHeight="1">
       <c r="A59" s="2" t="inlineStr">
         <is>
-          <t>TC-SP-002</t>
+          <t>TC-UB-001</t>
         </is>
       </c>
       <c r="B59" s="2" t="inlineStr">
@@ -3588,7 +3573,7 @@
       </c>
       <c r="C59" s="3" t="inlineStr">
         <is>
-          <t>/空间管理</t>
+          <t>/批量上传</t>
         </is>
       </c>
       <c r="D59" s="3" t="inlineStr">
@@ -3601,37 +3586,37 @@
       </c>
       <c r="F59" s="4" t="inlineStr">
         <is>
-          <t>创建空间_普通版</t>
+          <t>批量上传_5张</t>
         </is>
       </c>
       <c r="G59" s="2" t="inlineStr">
         <is>
-          <t>testuser01 已登录</t>
+          <t>testuser01</t>
         </is>
       </c>
       <c r="H59" s="2" t="inlineStr">
         <is>
-          <t>1. POST /space/add spaceName='我的空间' spaceLevel=0</t>
+          <t>POST /picture/upload/batch files=[5张jpg]</t>
         </is>
       </c>
       <c r="I59" s="2" t="inlineStr">
         <is>
-          <t>返回code=0, spaceId 存在</t>
-        </is>
-      </c>
-      <c r="J59" s="2" t="n"/>
-      <c r="K59" s="2" t="n"/>
+          <t>code=0, 5条记录</t>
+        </is>
+      </c>
+      <c r="J59" s="2" t="inlineStr"/>
+      <c r="K59" s="2" t="inlineStr"/>
       <c r="L59" s="2" t="inlineStr">
         <is>
-          <t>李坤纬</t>
-        </is>
-      </c>
-      <c r="M59" s="2" t="n"/>
+          <t>李冠燃</t>
+        </is>
+      </c>
+      <c r="M59" s="2" t="inlineStr"/>
     </row>
     <row r="60" ht="80" customHeight="1">
       <c r="A60" s="2" t="inlineStr">
         <is>
-          <t>TC-SP-003</t>
+          <t>TC-UB-002</t>
         </is>
       </c>
       <c r="B60" s="2" t="inlineStr">
@@ -3641,7 +3626,7 @@
       </c>
       <c r="C60" s="3" t="inlineStr">
         <is>
-          <t>/空间管理</t>
+          <t>/批量上传</t>
         </is>
       </c>
       <c r="D60" s="3" t="inlineStr">
@@ -3650,41 +3635,41 @@
         </is>
       </c>
       <c r="E60" s="3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F60" s="4" t="inlineStr">
         <is>
-          <t>创建空间_名称为空</t>
+          <t>批量上传_超20张</t>
         </is>
       </c>
       <c r="G60" s="2" t="inlineStr">
         <is>
-          <t>testuser01 已登录</t>
+          <t>testuser01</t>
         </is>
       </c>
       <c r="H60" s="2" t="inlineStr">
         <is>
-          <t>1. POST /space/add spaceName=''</t>
+          <t>POST /picture/upload/batch files=[30张]</t>
         </is>
       </c>
       <c r="I60" s="2" t="inlineStr">
         <is>
-          <t>返回code=40001</t>
-        </is>
-      </c>
-      <c r="J60" s="2" t="n"/>
-      <c r="K60" s="2" t="n"/>
+          <t>code=40001</t>
+        </is>
+      </c>
+      <c r="J60" s="2" t="inlineStr"/>
+      <c r="K60" s="2" t="inlineStr"/>
       <c r="L60" s="2" t="inlineStr">
         <is>
-          <t>李坤纬</t>
-        </is>
-      </c>
-      <c r="M60" s="2" t="n"/>
+          <t>李冠燃</t>
+        </is>
+      </c>
+      <c r="M60" s="2" t="inlineStr"/>
     </row>
     <row r="61" ht="80" customHeight="1">
       <c r="A61" s="2" t="inlineStr">
         <is>
-          <t>TC-SP-004</t>
+          <t>TC-SP-001</t>
         </is>
       </c>
       <c r="B61" s="2" t="inlineStr">
@@ -3694,7 +3679,7 @@
       </c>
       <c r="C61" s="3" t="inlineStr">
         <is>
-          <t>/空间管理</t>
+          <t>/关键字搜图</t>
         </is>
       </c>
       <c r="D61" s="3" t="inlineStr">
@@ -3703,41 +3688,41 @@
         </is>
       </c>
       <c r="E61" s="3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F61" s="4" t="inlineStr">
         <is>
-          <t>创建空间_名称超长</t>
+          <t>搜图_正常</t>
         </is>
       </c>
       <c r="G61" s="2" t="inlineStr">
         <is>
-          <t>testuser01 已登录</t>
+          <t>已有图片</t>
         </is>
       </c>
       <c r="H61" s="2" t="inlineStr">
         <is>
-          <t>1. POST /space/add spaceName=50+'x'</t>
+          <t>POST /picture/search/picture text='猫'</t>
         </is>
       </c>
       <c r="I61" s="2" t="inlineStr">
         <is>
-          <t>返回code=40001</t>
-        </is>
-      </c>
-      <c r="J61" s="2" t="n"/>
-      <c r="K61" s="2" t="n"/>
+          <t>code=0, 结果列表</t>
+        </is>
+      </c>
+      <c r="J61" s="2" t="inlineStr"/>
+      <c r="K61" s="2" t="inlineStr"/>
       <c r="L61" s="2" t="inlineStr">
         <is>
-          <t>李坤纬</t>
-        </is>
-      </c>
-      <c r="M61" s="2" t="n"/>
+          <t>李冠燃</t>
+        </is>
+      </c>
+      <c r="M61" s="2" t="inlineStr"/>
     </row>
     <row r="62" ht="80" customHeight="1">
       <c r="A62" s="2" t="inlineStr">
         <is>
-          <t>TC-SP-005</t>
+          <t>TC-SP-002</t>
         </is>
       </c>
       <c r="B62" s="2" t="inlineStr">
@@ -3747,7 +3732,7 @@
       </c>
       <c r="C62" s="3" t="inlineStr">
         <is>
-          <t>/空间管理</t>
+          <t>/关键字搜图</t>
         </is>
       </c>
       <c r="D62" s="3" t="inlineStr">
@@ -3756,11 +3741,11 @@
         </is>
       </c>
       <c r="E62" s="3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F62" s="4" t="inlineStr">
         <is>
-          <t>创建空间_未登录</t>
+          <t>搜图_无结果</t>
         </is>
       </c>
       <c r="G62" s="2" t="inlineStr">
@@ -3770,27 +3755,27 @@
       </c>
       <c r="H62" s="2" t="inlineStr">
         <is>
-          <t>1. POST /space/add</t>
+          <t>text='xyz999'</t>
         </is>
       </c>
       <c r="I62" s="2" t="inlineStr">
         <is>
-          <t>返回code=40100</t>
-        </is>
-      </c>
-      <c r="J62" s="2" t="n"/>
-      <c r="K62" s="2" t="n"/>
+          <t>code=0, []</t>
+        </is>
+      </c>
+      <c r="J62" s="2" t="inlineStr"/>
+      <c r="K62" s="2" t="inlineStr"/>
       <c r="L62" s="2" t="inlineStr">
         <is>
-          <t>李坤纬</t>
-        </is>
-      </c>
-      <c r="M62" s="2" t="n"/>
+          <t>李冠燃</t>
+        </is>
+      </c>
+      <c r="M62" s="2" t="inlineStr"/>
     </row>
     <row r="63" ht="80" customHeight="1">
       <c r="A63" s="2" t="inlineStr">
         <is>
-          <t>TC-SU-001</t>
+          <t>TC-SP-003</t>
         </is>
       </c>
       <c r="B63" s="2" t="inlineStr">
@@ -3800,7 +3785,7 @@
       </c>
       <c r="C63" s="3" t="inlineStr">
         <is>
-          <t>/空间成员</t>
+          <t>/关键字搜图</t>
         </is>
       </c>
       <c r="D63" s="3" t="inlineStr">
@@ -3813,37 +3798,37 @@
       </c>
       <c r="F63" s="4" t="inlineStr">
         <is>
-          <t>添加空间成员</t>
+          <t>搜图_SQL注入</t>
         </is>
       </c>
       <c r="G63" s="2" t="inlineStr">
         <is>
-          <t>admin 已登录, testuser01 有空间</t>
+          <t>testuser01</t>
         </is>
       </c>
       <c r="H63" s="2" t="inlineStr">
         <is>
-          <t>1. POST /spaceUser/add spaceId=1 userId=2 spaceRole='viewer'</t>
+          <t>text="' OR 1=1 --"</t>
         </is>
       </c>
       <c r="I63" s="2" t="inlineStr">
         <is>
-          <t>返回code=0</t>
-        </is>
-      </c>
-      <c r="J63" s="2" t="n"/>
-      <c r="K63" s="2" t="n"/>
+          <t>code=40001</t>
+        </is>
+      </c>
+      <c r="J63" s="2" t="inlineStr"/>
+      <c r="K63" s="2" t="inlineStr"/>
       <c r="L63" s="2" t="inlineStr">
         <is>
-          <t>李坤纬</t>
-        </is>
-      </c>
-      <c r="M63" s="2" t="n"/>
+          <t>李冠燃</t>
+        </is>
+      </c>
+      <c r="M63" s="2" t="inlineStr"/>
     </row>
     <row r="64" ht="80" customHeight="1">
       <c r="A64" s="2" t="inlineStr">
         <is>
-          <t>TC-SU-002</t>
+          <t>TC-SC-001</t>
         </is>
       </c>
       <c r="B64" s="2" t="inlineStr">
@@ -3853,7 +3838,7 @@
       </c>
       <c r="C64" s="3" t="inlineStr">
         <is>
-          <t>/空间成员</t>
+          <t>/颜色搜图</t>
         </is>
       </c>
       <c r="D64" s="3" t="inlineStr">
@@ -3866,37 +3851,37 @@
       </c>
       <c r="F64" s="4" t="inlineStr">
         <is>
-          <t>查询空间成员列表</t>
+          <t>搜图_蓝色</t>
         </is>
       </c>
       <c r="G64" s="2" t="inlineStr">
         <is>
-          <t>admin 已登录</t>
+          <t>已有图片</t>
         </is>
       </c>
       <c r="H64" s="2" t="inlineStr">
         <is>
-          <t>1. POST /spaceUser/list spaceId=1</t>
+          <t>POST /picture/search/color picColor='#0000FF'</t>
         </is>
       </c>
       <c r="I64" s="2" t="inlineStr">
         <is>
-          <t>返回成员列表</t>
-        </is>
-      </c>
-      <c r="J64" s="2" t="n"/>
-      <c r="K64" s="2" t="n"/>
+          <t>code=0</t>
+        </is>
+      </c>
+      <c r="J64" s="2" t="inlineStr"/>
+      <c r="K64" s="2" t="inlineStr"/>
       <c r="L64" s="2" t="inlineStr">
         <is>
-          <t>李坤纬</t>
-        </is>
-      </c>
-      <c r="M64" s="2" t="n"/>
+          <t>李冠燃</t>
+        </is>
+      </c>
+      <c r="M64" s="2" t="inlineStr"/>
     </row>
     <row r="65" ht="80" customHeight="1">
       <c r="A65" s="2" t="inlineStr">
         <is>
-          <t>TC-SU-003</t>
+          <t>TC-SC-002</t>
         </is>
       </c>
       <c r="B65" s="2" t="inlineStr">
@@ -3906,7 +3891,7 @@
       </c>
       <c r="C65" s="3" t="inlineStr">
         <is>
-          <t>/空间成员</t>
+          <t>/颜色搜图</t>
         </is>
       </c>
       <c r="D65" s="3" t="inlineStr">
@@ -3915,41 +3900,41 @@
         </is>
       </c>
       <c r="E65" s="3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F65" s="4" t="inlineStr">
         <is>
-          <t>添加成员_重复</t>
+          <t>搜图_无效颜色</t>
         </is>
       </c>
       <c r="G65" s="2" t="inlineStr">
         <is>
-          <t>成员已存在</t>
+          <t>testuser01</t>
         </is>
       </c>
       <c r="H65" s="2" t="inlineStr">
         <is>
-          <t>1. 重复 TC-SU-001</t>
+          <t>picColor='notacolor'</t>
         </is>
       </c>
       <c r="I65" s="2" t="inlineStr">
         <is>
-          <t>返回code=40001</t>
-        </is>
-      </c>
-      <c r="J65" s="2" t="n"/>
-      <c r="K65" s="2" t="n"/>
+          <t>code=40001</t>
+        </is>
+      </c>
+      <c r="J65" s="2" t="inlineStr"/>
+      <c r="K65" s="2" t="inlineStr"/>
       <c r="L65" s="2" t="inlineStr">
         <is>
-          <t>李坤纬</t>
-        </is>
-      </c>
-      <c r="M65" s="2" t="n"/>
+          <t>李冠燃</t>
+        </is>
+      </c>
+      <c r="M65" s="2" t="inlineStr"/>
     </row>
     <row r="66" ht="80" customHeight="1">
       <c r="A66" s="2" t="inlineStr">
         <is>
-          <t>TC-SU-004</t>
+          <t>TC-OC-001</t>
         </is>
       </c>
       <c r="B66" s="2" t="inlineStr">
@@ -3959,7 +3944,7 @@
       </c>
       <c r="C66" s="3" t="inlineStr">
         <is>
-          <t>/空间成员</t>
+          <t>/AI扩图</t>
         </is>
       </c>
       <c r="D66" s="3" t="inlineStr">
@@ -3968,41 +3953,41 @@
         </is>
       </c>
       <c r="E66" s="3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F66" s="4" t="inlineStr">
         <is>
-          <t>添加成员_未登录</t>
+          <t>创建扩图任务</t>
         </is>
       </c>
       <c r="G66" s="2" t="inlineStr">
         <is>
-          <t>无</t>
+          <t>testuser01有图片</t>
         </is>
       </c>
       <c r="H66" s="2" t="inlineStr">
         <is>
-          <t>1. POST /spaceUser/add</t>
+          <t>POST /picture/out_painting/create_task pictureId=1</t>
         </is>
       </c>
       <c r="I66" s="2" t="inlineStr">
         <is>
-          <t>返回code=40100</t>
-        </is>
-      </c>
-      <c r="J66" s="2" t="n"/>
-      <c r="K66" s="2" t="n"/>
+          <t>code=0, taskId</t>
+        </is>
+      </c>
+      <c r="J66" s="2" t="inlineStr"/>
+      <c r="K66" s="2" t="inlineStr"/>
       <c r="L66" s="2" t="inlineStr">
         <is>
-          <t>李坤纬</t>
-        </is>
-      </c>
-      <c r="M66" s="2" t="n"/>
+          <t>李冠燃</t>
+        </is>
+      </c>
+      <c r="M66" s="2" t="inlineStr"/>
     </row>
     <row r="67" ht="80" customHeight="1">
       <c r="A67" s="2" t="inlineStr">
         <is>
-          <t>TC-SU-005</t>
+          <t>TC-OC-002</t>
         </is>
       </c>
       <c r="B67" s="2" t="inlineStr">
@@ -4012,7 +3997,7 @@
       </c>
       <c r="C67" s="3" t="inlineStr">
         <is>
-          <t>/空间成员</t>
+          <t>/AI扩图</t>
         </is>
       </c>
       <c r="D67" s="3" t="inlineStr">
@@ -4021,41 +4006,41 @@
         </is>
       </c>
       <c r="E67" s="3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F67" s="4" t="inlineStr">
         <is>
-          <t>删除空间成员</t>
+          <t>任务_未登录</t>
         </is>
       </c>
       <c r="G67" s="2" t="inlineStr">
         <is>
-          <t>admin 已登录</t>
+          <t>无</t>
         </is>
       </c>
       <c r="H67" s="2" t="inlineStr">
         <is>
-          <t>1. POST /spaceUser/delete id=1</t>
+          <t>POST /picture/out_painting/create_task</t>
         </is>
       </c>
       <c r="I67" s="2" t="inlineStr">
         <is>
-          <t>返回code=0, isDelete=1</t>
-        </is>
-      </c>
-      <c r="J67" s="2" t="n"/>
-      <c r="K67" s="2" t="n"/>
+          <t>code=40100</t>
+        </is>
+      </c>
+      <c r="J67" s="2" t="inlineStr"/>
+      <c r="K67" s="2" t="inlineStr"/>
       <c r="L67" s="2" t="inlineStr">
         <is>
-          <t>李坤纬</t>
-        </is>
-      </c>
-      <c r="M67" s="2" t="n"/>
+          <t>李冠燃</t>
+        </is>
+      </c>
+      <c r="M67" s="2" t="inlineStr"/>
     </row>
     <row r="68" ht="80" customHeight="1">
       <c r="A68" s="2" t="inlineStr">
         <is>
-          <t>TC-PERF-001</t>
+          <t>TC-OG-001</t>
         </is>
       </c>
       <c r="B68" s="2" t="inlineStr">
@@ -4065,50 +4050,50 @@
       </c>
       <c r="C68" s="3" t="inlineStr">
         <is>
-          <t>/空间分析</t>
+          <t>/AI扩图查询</t>
         </is>
       </c>
       <c r="D68" s="3" t="inlineStr">
         <is>
-          <t>性能测试</t>
+          <t>功能测试</t>
         </is>
       </c>
       <c r="E68" s="3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F68" s="4" t="inlineStr">
         <is>
-          <t>空间分析_20并发</t>
+          <t>查询任务状态</t>
         </is>
       </c>
       <c r="G68" s="2" t="inlineStr">
         <is>
-          <t>已安装 JMeter</t>
+          <t>已创建任务</t>
         </is>
       </c>
       <c r="H68" s="2" t="inlineStr">
         <is>
-          <t>1. JMeter 20 线程 POST /space/analyze/usage</t>
+          <t>GET /picture/out_painting/get_task?taskId=xxx</t>
         </is>
       </c>
       <c r="I68" s="2" t="inlineStr">
         <is>
-          <t>P95 &lt; 1s, 错误率 &lt; 1%</t>
-        </is>
-      </c>
-      <c r="J68" s="2" t="n"/>
-      <c r="K68" s="2" t="n"/>
+          <t>code=0, status</t>
+        </is>
+      </c>
+      <c r="J68" s="2" t="inlineStr"/>
+      <c r="K68" s="2" t="inlineStr"/>
       <c r="L68" s="2" t="inlineStr">
         <is>
-          <t>李坤纬</t>
-        </is>
-      </c>
-      <c r="M68" s="2" t="n"/>
+          <t>李冠燃</t>
+        </is>
+      </c>
+      <c r="M68" s="2" t="inlineStr"/>
     </row>
     <row r="69" ht="80" customHeight="1">
       <c r="A69" s="2" t="inlineStr">
         <is>
-          <t>TC-API-001</t>
+          <t>TC-PE-001</t>
         </is>
       </c>
       <c r="B69" s="2" t="inlineStr">
@@ -4118,51 +4103,50 @@
       </c>
       <c r="C69" s="3" t="inlineStr">
         <is>
-          <t>/空间管理</t>
+          <t>/编辑代理</t>
         </is>
       </c>
       <c r="D69" s="3" t="inlineStr">
         <is>
-          <t>接口测试</t>
+          <t>功能测试</t>
         </is>
       </c>
       <c r="E69" s="3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F69" s="4" t="inlineStr">
         <is>
-          <t>创建空间_缺Content-Type</t>
+          <t>代理_正常URL</t>
         </is>
       </c>
       <c r="G69" s="2" t="inlineStr">
         <is>
-          <t>testuser01 已登录</t>
+          <t>testuser01</t>
         </is>
       </c>
       <c r="H69" s="2" t="inlineStr">
         <is>
-          <t>1. 不设置 Content-Type
-2. POST /space/add JSON body</t>
+          <t>GET /picture/proxy/editor?url=https://example.com/1.jpg</t>
         </is>
       </c>
       <c r="I69" s="2" t="inlineStr">
         <is>
-          <t>返回 415 或服务端能解析</t>
-        </is>
-      </c>
-      <c r="J69" s="2" t="n"/>
-      <c r="K69" s="2" t="n"/>
+          <t>返回图片</t>
+        </is>
+      </c>
+      <c r="J69" s="2" t="inlineStr"/>
+      <c r="K69" s="2" t="inlineStr"/>
       <c r="L69" s="2" t="inlineStr">
         <is>
-          <t>李坤纬</t>
-        </is>
-      </c>
-      <c r="M69" s="2" t="n"/>
+          <t>李冠燃</t>
+        </is>
+      </c>
+      <c r="M69" s="2" t="inlineStr"/>
     </row>
     <row r="70" ht="80" customHeight="1">
       <c r="A70" s="2" t="inlineStr">
         <is>
-          <t>TC-SEC-001</t>
+          <t>TC-PE-002</t>
         </is>
       </c>
       <c r="B70" s="2" t="inlineStr">
@@ -4172,12 +4156,12 @@
       </c>
       <c r="C70" s="3" t="inlineStr">
         <is>
-          <t>/空间管理</t>
+          <t>/编辑代理</t>
         </is>
       </c>
       <c r="D70" s="3" t="inlineStr">
         <is>
-          <t>安全测试</t>
+          <t>功能测试</t>
         </is>
       </c>
       <c r="E70" s="3" t="n">
@@ -4185,37 +4169,37 @@
       </c>
       <c r="F70" s="4" t="inlineStr">
         <is>
-          <t>空间名称XSS</t>
+          <t>代理_内网URL_拒绝</t>
         </is>
       </c>
       <c r="G70" s="2" t="inlineStr">
         <is>
-          <t>testuser01 已登录</t>
+          <t>testuser01</t>
         </is>
       </c>
       <c r="H70" s="2" t="inlineStr">
         <is>
-          <t>1. POST /space/add spaceName='&lt;script&gt;alert(1)&lt;/script&gt;'</t>
+          <t>url='http://192.168.1.1/admin'</t>
         </is>
       </c>
       <c r="I70" s="2" t="inlineStr">
         <is>
-          <t>返回code=0, 渲染时应被转义</t>
-        </is>
-      </c>
-      <c r="J70" s="2" t="n"/>
-      <c r="K70" s="2" t="n"/>
+          <t>code=40001</t>
+        </is>
+      </c>
+      <c r="J70" s="2" t="inlineStr"/>
+      <c r="K70" s="2" t="inlineStr"/>
       <c r="L70" s="2" t="inlineStr">
         <is>
-          <t>李坤纬</t>
-        </is>
-      </c>
-      <c r="M70" s="2" t="n"/>
+          <t>李冠燃</t>
+        </is>
+      </c>
+      <c r="M70" s="2" t="inlineStr"/>
     </row>
     <row r="71" ht="80" customHeight="1">
       <c r="A71" s="2" t="inlineStr">
         <is>
-          <t>TC-SP-006</t>
+          <t>TC-PERF-001</t>
         </is>
       </c>
       <c r="B71" s="2" t="inlineStr">
@@ -4225,12 +4209,12 @@
       </c>
       <c r="C71" s="3" t="inlineStr">
         <is>
-          <t>/空间管理</t>
+          <t>/图片上传</t>
         </is>
       </c>
       <c r="D71" s="3" t="inlineStr">
         <is>
-          <t>功能测试</t>
+          <t>性能测试</t>
         </is>
       </c>
       <c r="E71" s="3" t="n">
@@ -4238,37 +4222,37 @@
       </c>
       <c r="F71" s="4" t="inlineStr">
         <is>
-          <t>创建_重复同名空间</t>
+          <t>上传_20并发</t>
         </is>
       </c>
       <c r="G71" s="2" t="inlineStr">
         <is>
-          <t>testuser01 已登录</t>
+          <t>JMeter</t>
         </is>
       </c>
       <c r="H71" s="2" t="inlineStr">
         <is>
-          <t>1. 重复创建相同 spaceName</t>
+          <t>20线程 POST /file/upload</t>
         </is>
       </c>
       <c r="I71" s="2" t="inlineStr">
         <is>
-          <t>返回code=40001 或 code=0(允许同名)</t>
-        </is>
-      </c>
-      <c r="J71" s="2" t="n"/>
-      <c r="K71" s="2" t="n"/>
+          <t>P95&lt;3s</t>
+        </is>
+      </c>
+      <c r="J71" s="2" t="inlineStr"/>
+      <c r="K71" s="2" t="inlineStr"/>
       <c r="L71" s="2" t="inlineStr">
         <is>
-          <t>李坤纬</t>
-        </is>
-      </c>
-      <c r="M71" s="2" t="n"/>
+          <t>李冠燃</t>
+        </is>
+      </c>
+      <c r="M71" s="2" t="inlineStr"/>
     </row>
     <row r="72" ht="80" customHeight="1">
       <c r="A72" s="2" t="inlineStr">
         <is>
-          <t>TC-SP-007</t>
+          <t>TC-PERF-002</t>
         </is>
       </c>
       <c r="B72" s="2" t="inlineStr">
@@ -4278,12 +4262,12 @@
       </c>
       <c r="C72" s="3" t="inlineStr">
         <is>
-          <t>/空间管理</t>
+          <t>/图片分页</t>
         </is>
       </c>
       <c r="D72" s="3" t="inlineStr">
         <is>
-          <t>功能测试</t>
+          <t>性能测试</t>
         </is>
       </c>
       <c r="E72" s="3" t="n">
@@ -4291,37 +4275,37 @@
       </c>
       <c r="F72" s="4" t="inlineStr">
         <is>
-          <t>创建_名称50字符</t>
+          <t>分页查询_50并发</t>
         </is>
       </c>
       <c r="G72" s="2" t="inlineStr">
         <is>
-          <t>testuser01 已登录</t>
+          <t>JMeter</t>
         </is>
       </c>
       <c r="H72" s="2" t="inlineStr">
         <is>
-          <t>1. spaceName=50+'x'</t>
+          <t>50线程 POST /picture/list/page</t>
         </is>
       </c>
       <c r="I72" s="2" t="inlineStr">
         <is>
-          <t>返回code=40001 超长</t>
-        </is>
-      </c>
-      <c r="J72" s="2" t="n"/>
-      <c r="K72" s="2" t="n"/>
+          <t>P95&lt;300ms</t>
+        </is>
+      </c>
+      <c r="J72" s="2" t="inlineStr"/>
+      <c r="K72" s="2" t="inlineStr"/>
       <c r="L72" s="2" t="inlineStr">
         <is>
-          <t>李坤纬</t>
-        </is>
-      </c>
-      <c r="M72" s="2" t="n"/>
+          <t>李冠燃</t>
+        </is>
+      </c>
+      <c r="M72" s="2" t="inlineStr"/>
     </row>
     <row r="73" ht="80" customHeight="1">
       <c r="A73" s="2" t="inlineStr">
         <is>
-          <t>TC-SP-008</t>
+          <t>TC-API-001</t>
         </is>
       </c>
       <c r="B73" s="2" t="inlineStr">
@@ -4331,12 +4315,12 @@
       </c>
       <c r="C73" s="3" t="inlineStr">
         <is>
-          <t>/空间管理</t>
+          <t>/图片上传</t>
         </is>
       </c>
       <c r="D73" s="3" t="inlineStr">
         <is>
-          <t>功能测试</t>
+          <t>接口测试</t>
         </is>
       </c>
       <c r="E73" s="3" t="n">
@@ -4344,37 +4328,37 @@
       </c>
       <c r="F73" s="4" t="inlineStr">
         <is>
-          <t>创建_名称含特殊字符</t>
+          <t>上传_缺multipart边界</t>
         </is>
       </c>
       <c r="G73" s="2" t="inlineStr">
         <is>
-          <t>testuser01 已登录</t>
+          <t>testuser01</t>
         </is>
       </c>
       <c r="H73" s="2" t="inlineStr">
         <is>
-          <t>1. spaceName='my space!@#'</t>
+          <t>不完整multipart</t>
         </is>
       </c>
       <c r="I73" s="2" t="inlineStr">
         <is>
-          <t>返回code=40001</t>
-        </is>
-      </c>
-      <c r="J73" s="2" t="n"/>
-      <c r="K73" s="2" t="n"/>
+          <t>400/415</t>
+        </is>
+      </c>
+      <c r="J73" s="2" t="inlineStr"/>
+      <c r="K73" s="2" t="inlineStr"/>
       <c r="L73" s="2" t="inlineStr">
         <is>
-          <t>李坤纬</t>
-        </is>
-      </c>
-      <c r="M73" s="2" t="n"/>
+          <t>李冠燃</t>
+        </is>
+      </c>
+      <c r="M73" s="2" t="inlineStr"/>
     </row>
     <row r="74" ht="80" customHeight="1">
       <c r="A74" s="2" t="inlineStr">
         <is>
-          <t>TC-SP-009</t>
+          <t>TC-SEC-001</t>
         </is>
       </c>
       <c r="B74" s="2" t="inlineStr">
@@ -4384,50 +4368,50 @@
       </c>
       <c r="C74" s="3" t="inlineStr">
         <is>
-          <t>/空间管理</t>
+          <t>/图片上传</t>
         </is>
       </c>
       <c r="D74" s="3" t="inlineStr">
         <is>
-          <t>功能测试</t>
+          <t>安全测试</t>
         </is>
       </c>
       <c r="E74" s="3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F74" s="4" t="inlineStr">
         <is>
-          <t>创建_名称含中文</t>
+          <t>上传_伪PHP木马</t>
         </is>
       </c>
       <c r="G74" s="2" t="inlineStr">
         <is>
-          <t>testuser01 已登录</t>
+          <t>testuser01</t>
         </is>
       </c>
       <c r="H74" s="2" t="inlineStr">
         <is>
-          <t>1. spaceName='我的空间'</t>
+          <t>file=1.jpg内容为&lt;?php...?&gt;</t>
         </is>
       </c>
       <c r="I74" s="2" t="inlineStr">
         <is>
-          <t>返回code=0 支持中文</t>
-        </is>
-      </c>
-      <c r="J74" s="2" t="n"/>
-      <c r="K74" s="2" t="n"/>
+          <t>code=40001</t>
+        </is>
+      </c>
+      <c r="J74" s="2" t="inlineStr"/>
+      <c r="K74" s="2" t="inlineStr"/>
       <c r="L74" s="2" t="inlineStr">
         <is>
-          <t>李坤纬</t>
-        </is>
-      </c>
-      <c r="M74" s="2" t="n"/>
+          <t>李冠燃</t>
+        </is>
+      </c>
+      <c r="M74" s="2" t="inlineStr"/>
     </row>
     <row r="75" ht="80" customHeight="1">
       <c r="A75" s="2" t="inlineStr">
         <is>
-          <t>TC-SP-010</t>
+          <t>TC-SEC-002</t>
         </is>
       </c>
       <c r="B75" s="2" t="inlineStr">
@@ -4437,50 +4421,50 @@
       </c>
       <c r="C75" s="3" t="inlineStr">
         <is>
-          <t>/空间管理</t>
+          <t>/URL上传</t>
         </is>
       </c>
       <c r="D75" s="3" t="inlineStr">
         <is>
-          <t>功能测试</t>
+          <t>安全测试</t>
         </is>
       </c>
       <c r="E75" s="3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F75" s="4" t="inlineStr">
         <is>
-          <t>创建_旗舰版spaceLevel=3</t>
+          <t>URL上传_file协议</t>
         </is>
       </c>
       <c r="G75" s="2" t="inlineStr">
         <is>
-          <t>testuser01 已登录</t>
+          <t>testuser01</t>
         </is>
       </c>
       <c r="H75" s="2" t="inlineStr">
         <is>
-          <t>1. spaceName='旗舰' spaceLevel=3</t>
+          <t>fileUrl='file:///etc/passwd'</t>
         </is>
       </c>
       <c r="I75" s="2" t="inlineStr">
         <is>
-          <t>返回code=0</t>
-        </is>
-      </c>
-      <c r="J75" s="2" t="n"/>
-      <c r="K75" s="2" t="n"/>
+          <t>code=40001</t>
+        </is>
+      </c>
+      <c r="J75" s="2" t="inlineStr"/>
+      <c r="K75" s="2" t="inlineStr"/>
       <c r="L75" s="2" t="inlineStr">
         <is>
-          <t>李坤纬</t>
-        </is>
-      </c>
-      <c r="M75" s="2" t="n"/>
+          <t>李冠燃</t>
+        </is>
+      </c>
+      <c r="M75" s="2" t="inlineStr"/>
     </row>
     <row r="76" ht="80" customHeight="1">
       <c r="A76" s="2" t="inlineStr">
         <is>
-          <t>TC-SU-006</t>
+          <t>TC-SEC-003</t>
         </is>
       </c>
       <c r="B76" s="2" t="inlineStr">
@@ -4490,50 +4474,50 @@
       </c>
       <c r="C76" s="3" t="inlineStr">
         <is>
-          <t>/空间成员</t>
+          <t>/图片编辑</t>
         </is>
       </c>
       <c r="D76" s="3" t="inlineStr">
         <is>
-          <t>功能测试</t>
+          <t>安全测试</t>
         </is>
       </c>
       <c r="E76" s="3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F76" s="4" t="inlineStr">
         <is>
-          <t>成员_重复添加</t>
+          <t>编辑_name注入XSS</t>
         </is>
       </c>
       <c r="G76" s="2" t="inlineStr">
         <is>
-          <t>admin 已登录</t>
+          <t>testuser01</t>
         </is>
       </c>
       <c r="H76" s="2" t="inlineStr">
         <is>
-          <t>1. 重复添加同一成员</t>
+          <t>name='&lt;script&gt;alert(1)&lt;/script&gt;'</t>
         </is>
       </c>
       <c r="I76" s="2" t="inlineStr">
         <is>
-          <t>返回code=40001</t>
-        </is>
-      </c>
-      <c r="J76" s="2" t="n"/>
-      <c r="K76" s="2" t="n"/>
+          <t>code=0, 转义</t>
+        </is>
+      </c>
+      <c r="J76" s="2" t="inlineStr"/>
+      <c r="K76" s="2" t="inlineStr"/>
       <c r="L76" s="2" t="inlineStr">
         <is>
-          <t>李坤纬</t>
-        </is>
-      </c>
-      <c r="M76" s="2" t="n"/>
+          <t>李冠燃</t>
+        </is>
+      </c>
+      <c r="M76" s="2" t="inlineStr"/>
     </row>
     <row r="77" ht="80" customHeight="1">
       <c r="A77" s="2" t="inlineStr">
         <is>
-          <t>TC-SU-007</t>
+          <t>TC-SL-001</t>
         </is>
       </c>
       <c r="B77" s="2" t="inlineStr">
@@ -4543,7 +4527,7 @@
       </c>
       <c r="C77" s="3" t="inlineStr">
         <is>
-          <t>/空间成员</t>
+          <t>/空间等级</t>
         </is>
       </c>
       <c r="D77" s="3" t="inlineStr">
@@ -4552,41 +4536,41 @@
         </is>
       </c>
       <c r="E77" s="3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F77" s="4" t="inlineStr">
         <is>
-          <t>成员_添加自己</t>
+          <t>获取等级列表_正常</t>
         </is>
       </c>
       <c r="G77" s="2" t="inlineStr">
         <is>
-          <t>testuser01 已登录</t>
+          <t>无</t>
         </is>
       </c>
       <c r="H77" s="2" t="inlineStr">
         <is>
-          <t>1. userId=当前用户自己</t>
+          <t>GET /space/list/level</t>
         </is>
       </c>
       <c r="I77" s="2" t="inlineStr">
         <is>
-          <t>返回code=40001 不能加自己</t>
-        </is>
-      </c>
-      <c r="J77" s="2" t="n"/>
-      <c r="K77" s="2" t="n"/>
+          <t>code=0, 3个等级</t>
+        </is>
+      </c>
+      <c r="J77" s="2" t="inlineStr"/>
+      <c r="K77" s="2" t="inlineStr"/>
       <c r="L77" s="2" t="inlineStr">
         <is>
           <t>李坤纬</t>
         </is>
       </c>
-      <c r="M77" s="2" t="n"/>
+      <c r="M77" s="2" t="inlineStr"/>
     </row>
     <row r="78" ht="80" customHeight="1">
       <c r="A78" s="2" t="inlineStr">
         <is>
-          <t>TC-SU-008</t>
+          <t>TC-SL-002</t>
         </is>
       </c>
       <c r="B78" s="2" t="inlineStr">
@@ -4596,7 +4580,7 @@
       </c>
       <c r="C78" s="3" t="inlineStr">
         <is>
-          <t>/空间成员</t>
+          <t>/空间等级</t>
         </is>
       </c>
       <c r="D78" s="3" t="inlineStr">
@@ -4605,41 +4589,41 @@
         </is>
       </c>
       <c r="E78" s="3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F78" s="4" t="inlineStr">
         <is>
-          <t>成员_查询不存在的空间</t>
+          <t>获取等级列表_未登录</t>
         </is>
       </c>
       <c r="G78" s="2" t="inlineStr">
         <is>
-          <t>admin 已登录</t>
+          <t>无</t>
         </is>
       </c>
       <c r="H78" s="2" t="inlineStr">
         <is>
-          <t>1. POST /spaceUser/list spaceId=999999</t>
+          <t>GET /space/list/level 无Cookie</t>
         </is>
       </c>
       <c r="I78" s="2" t="inlineStr">
         <is>
-          <t>返回空列表</t>
-        </is>
-      </c>
-      <c r="J78" s="2" t="n"/>
-      <c r="K78" s="2" t="n"/>
+          <t>code=0, 不需要登录</t>
+        </is>
+      </c>
+      <c r="J78" s="2" t="inlineStr"/>
+      <c r="K78" s="2" t="inlineStr"/>
       <c r="L78" s="2" t="inlineStr">
         <is>
           <t>李坤纬</t>
         </is>
       </c>
-      <c r="M78" s="2" t="n"/>
+      <c r="M78" s="2" t="inlineStr"/>
     </row>
     <row r="79" ht="80" customHeight="1">
       <c r="A79" s="2" t="inlineStr">
         <is>
-          <t>TC-SU-009</t>
+          <t>TC-SS-001</t>
         </is>
       </c>
       <c r="B79" s="2" t="inlineStr">
@@ -4649,50 +4633,50 @@
       </c>
       <c r="C79" s="3" t="inlineStr">
         <is>
-          <t>/空间成员</t>
+          <t>/空间保存</t>
         </is>
       </c>
       <c r="D79" s="3" t="inlineStr">
         <is>
-          <t>接口测试</t>
+          <t>功能测试</t>
         </is>
       </c>
       <c r="E79" s="3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F79" s="4" t="inlineStr">
         <is>
-          <t>成员_缺spaceId</t>
+          <t>保存_正常</t>
         </is>
       </c>
       <c r="G79" s="2" t="inlineStr">
         <is>
-          <t>admin 已登录</t>
+          <t>testuser01</t>
         </is>
       </c>
       <c r="H79" s="2" t="inlineStr">
         <is>
-          <t>1. body 无 spaceId</t>
+          <t>POST /space/save spaceName='保存测试'</t>
         </is>
       </c>
       <c r="I79" s="2" t="inlineStr">
         <is>
-          <t>返回code=40001</t>
-        </is>
-      </c>
-      <c r="J79" s="2" t="n"/>
-      <c r="K79" s="2" t="n"/>
+          <t>code=0</t>
+        </is>
+      </c>
+      <c r="J79" s="2" t="inlineStr"/>
+      <c r="K79" s="2" t="inlineStr"/>
       <c r="L79" s="2" t="inlineStr">
         <is>
           <t>李坤纬</t>
         </is>
       </c>
-      <c r="M79" s="2" t="n"/>
+      <c r="M79" s="2" t="inlineStr"/>
     </row>
     <row r="80" ht="80" customHeight="1">
       <c r="A80" s="2" t="inlineStr">
         <is>
-          <t>TC-SU-010</t>
+          <t>TC-SS-002</t>
         </is>
       </c>
       <c r="B80" s="2" t="inlineStr">
@@ -4702,7 +4686,7 @@
       </c>
       <c r="C80" s="3" t="inlineStr">
         <is>
-          <t>/空间成员</t>
+          <t>/空间保存</t>
         </is>
       </c>
       <c r="D80" s="3" t="inlineStr">
@@ -4711,36 +4695,36 @@
         </is>
       </c>
       <c r="E80" s="3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F80" s="4" t="inlineStr">
         <is>
-          <t>成员_删除已删除的成员</t>
+          <t>保存_名称为空</t>
         </is>
       </c>
       <c r="G80" s="2" t="inlineStr">
         <is>
-          <t>admin 已登录</t>
+          <t>testuser01</t>
         </is>
       </c>
       <c r="H80" s="2" t="inlineStr">
         <is>
-          <t>1. 重复 delete 同一成员</t>
+          <t>spaceName=''</t>
         </is>
       </c>
       <c r="I80" s="2" t="inlineStr">
         <is>
-          <t>返回code=40001 第二次失败</t>
-        </is>
-      </c>
-      <c r="J80" s="2" t="n"/>
-      <c r="K80" s="2" t="n"/>
+          <t>code=40001</t>
+        </is>
+      </c>
+      <c r="J80" s="2" t="inlineStr"/>
+      <c r="K80" s="2" t="inlineStr"/>
       <c r="L80" s="2" t="inlineStr">
         <is>
           <t>李坤纬</t>
         </is>
       </c>
-      <c r="M80" s="2" t="n"/>
+      <c r="M80" s="2" t="inlineStr"/>
     </row>
     <row r="81" ht="80" customHeight="1">
       <c r="A81" s="2" t="inlineStr">
@@ -4755,7 +4739,7 @@
       </c>
       <c r="C81" s="3" t="inlineStr">
         <is>
-          <t>/空间分析</t>
+          <t>/空间新增</t>
         </is>
       </c>
       <c r="D81" s="3" t="inlineStr">
@@ -4768,32 +4752,32 @@
       </c>
       <c r="F81" s="4" t="inlineStr">
         <is>
-          <t>空间分类分析</t>
+          <t>新增_正常</t>
         </is>
       </c>
       <c r="G81" s="2" t="inlineStr">
         <is>
-          <t>testuser01 有空间</t>
+          <t>testuser01</t>
         </is>
       </c>
       <c r="H81" s="2" t="inlineStr">
         <is>
-          <t>1. POST /space/analyze/category spaceId=1</t>
+          <t>POST /space/add spaceName='新空间' spaceLevel=0</t>
         </is>
       </c>
       <c r="I81" s="2" t="inlineStr">
         <is>
-          <t>返回code=0 分类统计</t>
-        </is>
-      </c>
-      <c r="J81" s="2" t="n"/>
-      <c r="K81" s="2" t="n"/>
+          <t>code=0</t>
+        </is>
+      </c>
+      <c r="J81" s="2" t="inlineStr"/>
+      <c r="K81" s="2" t="inlineStr"/>
       <c r="L81" s="2" t="inlineStr">
         <is>
           <t>李坤纬</t>
         </is>
       </c>
-      <c r="M81" s="2" t="n"/>
+      <c r="M81" s="2" t="inlineStr"/>
     </row>
     <row r="82" ht="80" customHeight="1">
       <c r="A82" s="2" t="inlineStr">
@@ -4808,7 +4792,7 @@
       </c>
       <c r="C82" s="3" t="inlineStr">
         <is>
-          <t>/空间分析</t>
+          <t>/空间新增</t>
         </is>
       </c>
       <c r="D82" s="3" t="inlineStr">
@@ -4821,32 +4805,32 @@
       </c>
       <c r="F82" s="4" t="inlineStr">
         <is>
-          <t>空间标签分析</t>
+          <t>新增_名称超长50</t>
         </is>
       </c>
       <c r="G82" s="2" t="inlineStr">
         <is>
-          <t>testuser01 有空间</t>
+          <t>testuser01</t>
         </is>
       </c>
       <c r="H82" s="2" t="inlineStr">
         <is>
-          <t>1. POST /space/analyze/tag spaceId=1</t>
+          <t>spaceName=50+'x'</t>
         </is>
       </c>
       <c r="I82" s="2" t="inlineStr">
         <is>
-          <t>返回code=0 标签统计</t>
-        </is>
-      </c>
-      <c r="J82" s="2" t="n"/>
-      <c r="K82" s="2" t="n"/>
+          <t>code=40001</t>
+        </is>
+      </c>
+      <c r="J82" s="2" t="inlineStr"/>
+      <c r="K82" s="2" t="inlineStr"/>
       <c r="L82" s="2" t="inlineStr">
         <is>
           <t>李坤纬</t>
         </is>
       </c>
-      <c r="M82" s="2" t="n"/>
+      <c r="M82" s="2" t="inlineStr"/>
     </row>
     <row r="83" ht="80" customHeight="1">
       <c r="A83" s="2" t="inlineStr">
@@ -4861,7 +4845,7 @@
       </c>
       <c r="C83" s="3" t="inlineStr">
         <is>
-          <t>/空间分析</t>
+          <t>/空间新增</t>
         </is>
       </c>
       <c r="D83" s="3" t="inlineStr">
@@ -4874,37 +4858,37 @@
       </c>
       <c r="F83" s="4" t="inlineStr">
         <is>
-          <t>空间排行</t>
+          <t>新增_未登录</t>
         </is>
       </c>
       <c r="G83" s="2" t="inlineStr">
         <is>
-          <t>testuser01 已登录</t>
+          <t>无</t>
         </is>
       </c>
       <c r="H83" s="2" t="inlineStr">
         <is>
-          <t>1. POST /space/analyze/rank</t>
+          <t>POST /space/add</t>
         </is>
       </c>
       <c r="I83" s="2" t="inlineStr">
         <is>
-          <t>返回code=0 排行列表</t>
-        </is>
-      </c>
-      <c r="J83" s="2" t="n"/>
-      <c r="K83" s="2" t="n"/>
+          <t>code=40100</t>
+        </is>
+      </c>
+      <c r="J83" s="2" t="inlineStr"/>
+      <c r="K83" s="2" t="inlineStr"/>
       <c r="L83" s="2" t="inlineStr">
         <is>
           <t>李坤纬</t>
         </is>
       </c>
-      <c r="M83" s="2" t="n"/>
+      <c r="M83" s="2" t="inlineStr"/>
     </row>
     <row r="84" ht="80" customHeight="1">
       <c r="A84" s="2" t="inlineStr">
         <is>
-          <t>TC-SEC-002</t>
+          <t>TC-SG-001</t>
         </is>
       </c>
       <c r="B84" s="2" t="inlineStr">
@@ -4914,12 +4898,12 @@
       </c>
       <c r="C84" s="3" t="inlineStr">
         <is>
-          <t>/空间管理</t>
+          <t>/空间获取</t>
         </is>
       </c>
       <c r="D84" s="3" t="inlineStr">
         <is>
-          <t>安全测试</t>
+          <t>功能测试</t>
         </is>
       </c>
       <c r="E84" s="3" t="n">
@@ -4927,37 +4911,37 @@
       </c>
       <c r="F84" s="4" t="inlineStr">
         <is>
-          <t>跨用户删除空间</t>
+          <t>按id获取_正常</t>
         </is>
       </c>
       <c r="G84" s="2" t="inlineStr">
         <is>
-          <t>testuser02 已登录</t>
+          <t>testuser01</t>
         </is>
       </c>
       <c r="H84" s="2" t="inlineStr">
         <is>
-          <t>1. POST /space/delete id=testuser01的空间</t>
+          <t>GET /space/get?id=1</t>
         </is>
       </c>
       <c r="I84" s="2" t="inlineStr">
         <is>
-          <t>返回code=40300 越权失败</t>
-        </is>
-      </c>
-      <c r="J84" s="2" t="n"/>
-      <c r="K84" s="2" t="n"/>
+          <t>code=0</t>
+        </is>
+      </c>
+      <c r="J84" s="2" t="inlineStr"/>
+      <c r="K84" s="2" t="inlineStr"/>
       <c r="L84" s="2" t="inlineStr">
         <is>
           <t>李坤纬</t>
         </is>
       </c>
-      <c r="M84" s="2" t="n"/>
+      <c r="M84" s="2" t="inlineStr"/>
     </row>
     <row r="85" ht="80" customHeight="1">
       <c r="A85" s="2" t="inlineStr">
         <is>
-          <t>TC-PERF-002</t>
+          <t>TC-SG-002</t>
         </is>
       </c>
       <c r="B85" s="2" t="inlineStr">
@@ -4967,50 +4951,50 @@
       </c>
       <c r="C85" s="3" t="inlineStr">
         <is>
-          <t>/空间列表</t>
+          <t>/空间获取</t>
         </is>
       </c>
       <c r="D85" s="3" t="inlineStr">
         <is>
-          <t>性能测试</t>
+          <t>功能测试</t>
         </is>
       </c>
       <c r="E85" s="3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F85" s="4" t="inlineStr">
         <is>
-          <t>空间列表_50并发</t>
+          <t>按id获取_不存在</t>
         </is>
       </c>
       <c r="G85" s="2" t="inlineStr">
         <is>
-          <t>已安装 JMeter</t>
+          <t>无</t>
         </is>
       </c>
       <c r="H85" s="2" t="inlineStr">
         <is>
-          <t>1. JMeter 50 线程 POST /space/list/page/vo</t>
+          <t>GET /space/get?id=999999</t>
         </is>
       </c>
       <c r="I85" s="2" t="inlineStr">
         <is>
-          <t>P95 &lt; 500ms, 错误率 &lt; 1%</t>
-        </is>
-      </c>
-      <c r="J85" s="2" t="n"/>
-      <c r="K85" s="2" t="n"/>
+          <t>code=40001</t>
+        </is>
+      </c>
+      <c r="J85" s="2" t="inlineStr"/>
+      <c r="K85" s="2" t="inlineStr"/>
       <c r="L85" s="2" t="inlineStr">
         <is>
           <t>李坤纬</t>
         </is>
       </c>
-      <c r="M85" s="2" t="n"/>
+      <c r="M85" s="2" t="inlineStr"/>
     </row>
     <row r="86" ht="80" customHeight="1">
       <c r="A86" s="2" t="inlineStr">
         <is>
-          <t>TC-API-002</t>
+          <t>TC-SV-001</t>
         </is>
       </c>
       <c r="B86" s="2" t="inlineStr">
@@ -5020,50 +5004,50 @@
       </c>
       <c r="C86" s="3" t="inlineStr">
         <is>
-          <t>/空间成员</t>
+          <t>/空间VO</t>
         </is>
       </c>
       <c r="D86" s="3" t="inlineStr">
         <is>
-          <t>接口测试</t>
+          <t>功能测试</t>
         </is>
       </c>
       <c r="E86" s="3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F86" s="4" t="inlineStr">
         <is>
-          <t>添加成员_缺userId</t>
+          <t>获取VO_正常</t>
         </is>
       </c>
       <c r="G86" s="2" t="inlineStr">
         <is>
-          <t>admin 已登录</t>
+          <t>testuser01</t>
         </is>
       </c>
       <c r="H86" s="2" t="inlineStr">
         <is>
-          <t>1. body 只有 spaceId 和 spaceRole</t>
+          <t>GET /space/get/vo?id=1</t>
         </is>
       </c>
       <c r="I86" s="2" t="inlineStr">
         <is>
-          <t>返回code=40001</t>
-        </is>
-      </c>
-      <c r="J86" s="2" t="n"/>
-      <c r="K86" s="2" t="n"/>
+          <t>code=0</t>
+        </is>
+      </c>
+      <c r="J86" s="2" t="inlineStr"/>
+      <c r="K86" s="2" t="inlineStr"/>
       <c r="L86" s="2" t="inlineStr">
         <is>
           <t>李坤纬</t>
         </is>
       </c>
-      <c r="M86" s="2" t="n"/>
+      <c r="M86" s="2" t="inlineStr"/>
     </row>
     <row r="87" ht="80" customHeight="1">
       <c r="A87" s="2" t="inlineStr">
         <is>
-          <t>TC-FL-001</t>
+          <t>TC-SV-002</t>
         </is>
       </c>
       <c r="B87" s="2" t="inlineStr">
@@ -5073,7 +5057,7 @@
       </c>
       <c r="C87" s="3" t="inlineStr">
         <is>
-          <t>/文件上传</t>
+          <t>/空间VO</t>
         </is>
       </c>
       <c r="D87" s="3" t="inlineStr">
@@ -5086,37 +5070,37 @@
       </c>
       <c r="F87" s="4" t="inlineStr">
         <is>
-          <t>本地上传_jpg_2MB</t>
+          <t>获取VO_未登录</t>
         </is>
       </c>
       <c r="G87" s="2" t="inlineStr">
         <is>
-          <t>testuser01 已登录</t>
+          <t>无</t>
         </is>
       </c>
       <c r="H87" s="2" t="inlineStr">
         <is>
-          <t>1. POST /file/upload file=2MB_jpg</t>
+          <t>GET /space/get/vo?id=1</t>
         </is>
       </c>
       <c r="I87" s="2" t="inlineStr">
         <is>
-          <t>返回code=0, url 字段为可访问图片链接</t>
-        </is>
-      </c>
-      <c r="J87" s="2" t="n"/>
-      <c r="K87" s="2" t="n"/>
+          <t>code=40100</t>
+        </is>
+      </c>
+      <c r="J87" s="2" t="inlineStr"/>
+      <c r="K87" s="2" t="inlineStr"/>
       <c r="L87" s="2" t="inlineStr">
         <is>
-          <t>林景彬</t>
-        </is>
-      </c>
-      <c r="M87" s="2" t="n"/>
+          <t>李坤纬</t>
+        </is>
+      </c>
+      <c r="M87" s="2" t="inlineStr"/>
     </row>
     <row r="88" ht="80" customHeight="1">
       <c r="A88" s="2" t="inlineStr">
         <is>
-          <t>TC-FL-002</t>
+          <t>TC-SP-001</t>
         </is>
       </c>
       <c r="B88" s="2" t="inlineStr">
@@ -5126,7 +5110,7 @@
       </c>
       <c r="C88" s="3" t="inlineStr">
         <is>
-          <t>/文件上传</t>
+          <t>/空间分页</t>
         </is>
       </c>
       <c r="D88" s="3" t="inlineStr">
@@ -5139,37 +5123,37 @@
       </c>
       <c r="F88" s="4" t="inlineStr">
         <is>
-          <t>本地上传_png</t>
+          <t>分页查询_正常</t>
         </is>
       </c>
       <c r="G88" s="2" t="inlineStr">
         <is>
-          <t>testuser01 已登录</t>
+          <t>testuser01</t>
         </is>
       </c>
       <c r="H88" s="2" t="inlineStr">
         <is>
-          <t>1. POST /file/upload file=1MB_png</t>
+          <t>POST /space/list/page current=1 pageSize=10</t>
         </is>
       </c>
       <c r="I88" s="2" t="inlineStr">
         <is>
-          <t>返回code=0</t>
-        </is>
-      </c>
-      <c r="J88" s="2" t="n"/>
-      <c r="K88" s="2" t="n"/>
+          <t>code=0</t>
+        </is>
+      </c>
+      <c r="J88" s="2" t="inlineStr"/>
+      <c r="K88" s="2" t="inlineStr"/>
       <c r="L88" s="2" t="inlineStr">
         <is>
-          <t>林景彬</t>
-        </is>
-      </c>
-      <c r="M88" s="2" t="n"/>
+          <t>李坤纬</t>
+        </is>
+      </c>
+      <c r="M88" s="2" t="inlineStr"/>
     </row>
     <row r="89" ht="80" customHeight="1">
       <c r="A89" s="2" t="inlineStr">
         <is>
-          <t>TC-FL-003</t>
+          <t>TC-SP-002</t>
         </is>
       </c>
       <c r="B89" s="2" t="inlineStr">
@@ -5179,7 +5163,7 @@
       </c>
       <c r="C89" s="3" t="inlineStr">
         <is>
-          <t>/文件上传</t>
+          <t>/空间分页</t>
         </is>
       </c>
       <c r="D89" s="3" t="inlineStr">
@@ -5192,37 +5176,37 @@
       </c>
       <c r="F89" s="4" t="inlineStr">
         <is>
-          <t>本地上传_avatar_头像</t>
+          <t>分页查询_空页</t>
         </is>
       </c>
       <c r="G89" s="2" t="inlineStr">
         <is>
-          <t>testuser01 已登录</t>
+          <t>testuser01</t>
         </is>
       </c>
       <c r="H89" s="2" t="inlineStr">
         <is>
-          <t>1. POST /file/upload/avatar file=512KB_jpg</t>
+          <t>current=9999</t>
         </is>
       </c>
       <c r="I89" s="2" t="inlineStr">
         <is>
-          <t>返回code=0, userAvatar 已更新</t>
-        </is>
-      </c>
-      <c r="J89" s="2" t="n"/>
-      <c r="K89" s="2" t="n"/>
+          <t>code=0, []</t>
+        </is>
+      </c>
+      <c r="J89" s="2" t="inlineStr"/>
+      <c r="K89" s="2" t="inlineStr"/>
       <c r="L89" s="2" t="inlineStr">
         <is>
-          <t>林景彬</t>
-        </is>
-      </c>
-      <c r="M89" s="2" t="n"/>
+          <t>李坤纬</t>
+        </is>
+      </c>
+      <c r="M89" s="2" t="inlineStr"/>
     </row>
     <row r="90" ht="80" customHeight="1">
       <c r="A90" s="2" t="inlineStr">
         <is>
-          <t>TC-FL-004</t>
+          <t>TC-LV-001</t>
         </is>
       </c>
       <c r="B90" s="2" t="inlineStr">
@@ -5232,7 +5216,7 @@
       </c>
       <c r="C90" s="3" t="inlineStr">
         <is>
-          <t>/文件上传</t>
+          <t>/空间VO分页</t>
         </is>
       </c>
       <c r="D90" s="3" t="inlineStr">
@@ -5241,41 +5225,41 @@
         </is>
       </c>
       <c r="E90" s="3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F90" s="4" t="inlineStr">
         <is>
-          <t>本地上传_超过2MB_应失败</t>
+          <t>VO分页_正常</t>
         </is>
       </c>
       <c r="G90" s="2" t="inlineStr">
         <is>
-          <t>testuser01 已登录</t>
+          <t>testuser01</t>
         </is>
       </c>
       <c r="H90" s="2" t="inlineStr">
         <is>
-          <t>1. POST /file/upload file=5MB_jpg</t>
+          <t>POST /space/list/page/vo</t>
         </is>
       </c>
       <c r="I90" s="2" t="inlineStr">
         <is>
-          <t>返回code=40001</t>
-        </is>
-      </c>
-      <c r="J90" s="2" t="n"/>
-      <c r="K90" s="2" t="n"/>
+          <t>code=0</t>
+        </is>
+      </c>
+      <c r="J90" s="2" t="inlineStr"/>
+      <c r="K90" s="2" t="inlineStr"/>
       <c r="L90" s="2" t="inlineStr">
         <is>
-          <t>林景彬</t>
-        </is>
-      </c>
-      <c r="M90" s="2" t="n"/>
+          <t>李坤纬</t>
+        </is>
+      </c>
+      <c r="M90" s="2" t="inlineStr"/>
     </row>
     <row r="91" ht="80" customHeight="1">
       <c r="A91" s="2" t="inlineStr">
         <is>
-          <t>TC-FL-005</t>
+          <t>TC-LV-002</t>
         </is>
       </c>
       <c r="B91" s="2" t="inlineStr">
@@ -5285,7 +5269,7 @@
       </c>
       <c r="C91" s="3" t="inlineStr">
         <is>
-          <t>/文件上传</t>
+          <t>/空间VO分页</t>
         </is>
       </c>
       <c r="D91" s="3" t="inlineStr">
@@ -5294,11 +5278,11 @@
         </is>
       </c>
       <c r="E91" s="3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F91" s="4" t="inlineStr">
         <is>
-          <t>本地上传_未登录</t>
+          <t>VO分页_未登录</t>
         </is>
       </c>
       <c r="G91" s="2" t="inlineStr">
@@ -5308,27 +5292,27 @@
       </c>
       <c r="H91" s="2" t="inlineStr">
         <is>
-          <t>1. POST /file/upload</t>
+          <t>POST /space/list/page/vo</t>
         </is>
       </c>
       <c r="I91" s="2" t="inlineStr">
         <is>
-          <t>返回code=40100</t>
-        </is>
-      </c>
-      <c r="J91" s="2" t="n"/>
-      <c r="K91" s="2" t="n"/>
+          <t>code=40100</t>
+        </is>
+      </c>
+      <c r="J91" s="2" t="inlineStr"/>
+      <c r="K91" s="2" t="inlineStr"/>
       <c r="L91" s="2" t="inlineStr">
         <is>
-          <t>林景彬</t>
-        </is>
-      </c>
-      <c r="M91" s="2" t="n"/>
+          <t>李坤纬</t>
+        </is>
+      </c>
+      <c r="M91" s="2" t="inlineStr"/>
     </row>
     <row r="92" ht="80" customHeight="1">
       <c r="A92" s="2" t="inlineStr">
         <is>
-          <t>TC-WX-001</t>
+          <t>TC-SE-001</t>
         </is>
       </c>
       <c r="B92" s="2" t="inlineStr">
@@ -5338,7 +5322,7 @@
       </c>
       <c r="C92" s="3" t="inlineStr">
         <is>
-          <t>/微信公众号</t>
+          <t>/空间编辑</t>
         </is>
       </c>
       <c r="D92" s="3" t="inlineStr">
@@ -5351,37 +5335,37 @@
       </c>
       <c r="F92" s="4" t="inlineStr">
         <is>
-          <t>门户_GET_签名验证</t>
+          <t>编辑_正常</t>
         </is>
       </c>
       <c r="G92" s="2" t="inlineStr">
         <is>
-          <t>微信服务器 GET</t>
+          <t>testuser01是创建者</t>
         </is>
       </c>
       <c r="H92" s="2" t="inlineStr">
         <is>
-          <t>1. GET /wx/mp/portal signature=xxx timestamp=xxx nonce=xxx echostr=xxx</t>
+          <t>POST /space/edit id=1 spaceName='改名'</t>
         </is>
       </c>
       <c r="I92" s="2" t="inlineStr">
         <is>
-          <t>返回 echostr 明文（签名验证通过）</t>
-        </is>
-      </c>
-      <c r="J92" s="2" t="n"/>
-      <c r="K92" s="2" t="n"/>
+          <t>code=0</t>
+        </is>
+      </c>
+      <c r="J92" s="2" t="inlineStr"/>
+      <c r="K92" s="2" t="inlineStr"/>
       <c r="L92" s="2" t="inlineStr">
         <is>
-          <t>林景彬</t>
-        </is>
-      </c>
-      <c r="M92" s="2" t="n"/>
+          <t>李坤纬</t>
+        </is>
+      </c>
+      <c r="M92" s="2" t="inlineStr"/>
     </row>
     <row r="93" ht="80" customHeight="1">
       <c r="A93" s="2" t="inlineStr">
         <is>
-          <t>TC-WX-002</t>
+          <t>TC-SE-002</t>
         </is>
       </c>
       <c r="B93" s="2" t="inlineStr">
@@ -5391,7 +5375,7 @@
       </c>
       <c r="C93" s="3" t="inlineStr">
         <is>
-          <t>/微信公众号</t>
+          <t>/空间编辑</t>
         </is>
       </c>
       <c r="D93" s="3" t="inlineStr">
@@ -5404,38 +5388,37 @@
       </c>
       <c r="F93" s="4" t="inlineStr">
         <is>
-          <t>门户_POST_消息处理</t>
+          <t>编辑_越权</t>
         </is>
       </c>
       <c r="G93" s="2" t="inlineStr">
         <is>
-          <t>微信服务器 POST XML</t>
+          <t>testuser02</t>
         </is>
       </c>
       <c r="H93" s="2" t="inlineStr">
         <is>
-          <t>1. POST /wx/mp/portal Content-Type=application/xml
-2. body=&lt;xml&gt;...&lt;/xml&gt;</t>
+          <t>POST /space/edit id=别人空间</t>
         </is>
       </c>
       <c r="I93" s="2" t="inlineStr">
         <is>
-          <t>返回code=0, 响应 XML 包含正确结构</t>
-        </is>
-      </c>
-      <c r="J93" s="2" t="n"/>
-      <c r="K93" s="2" t="n"/>
+          <t>code=40300</t>
+        </is>
+      </c>
+      <c r="J93" s="2" t="inlineStr"/>
+      <c r="K93" s="2" t="inlineStr"/>
       <c r="L93" s="2" t="inlineStr">
         <is>
-          <t>林景彬</t>
-        </is>
-      </c>
-      <c r="M93" s="2" t="n"/>
+          <t>李坤纬</t>
+        </is>
+      </c>
+      <c r="M93" s="2" t="inlineStr"/>
     </row>
     <row r="94" ht="80" customHeight="1">
       <c r="A94" s="2" t="inlineStr">
         <is>
-          <t>TC-WX-003</t>
+          <t>TC-SD-001</t>
         </is>
       </c>
       <c r="B94" s="2" t="inlineStr">
@@ -5445,7 +5428,7 @@
       </c>
       <c r="C94" s="3" t="inlineStr">
         <is>
-          <t>/微信公众号</t>
+          <t>/空间删除</t>
         </is>
       </c>
       <c r="D94" s="3" t="inlineStr">
@@ -5454,41 +5437,41 @@
         </is>
       </c>
       <c r="E94" s="3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F94" s="4" t="inlineStr">
         <is>
-          <t>创建公众号菜单</t>
+          <t>删除_正常</t>
         </is>
       </c>
       <c r="G94" s="2" t="inlineStr">
         <is>
-          <t>admin 已登录</t>
+          <t>testuser01是创建者</t>
         </is>
       </c>
       <c r="H94" s="2" t="inlineStr">
         <is>
-          <t>1. POST /wx/mp/menu/create menu={"button":[...]}</t>
+          <t>POST /space/delete id=1</t>
         </is>
       </c>
       <c r="I94" s="2" t="inlineStr">
         <is>
-          <t>返回code=0</t>
-        </is>
-      </c>
-      <c r="J94" s="2" t="n"/>
-      <c r="K94" s="2" t="n"/>
+          <t>code=0, isDelete=1</t>
+        </is>
+      </c>
+      <c r="J94" s="2" t="inlineStr"/>
+      <c r="K94" s="2" t="inlineStr"/>
       <c r="L94" s="2" t="inlineStr">
         <is>
-          <t>林景彬</t>
-        </is>
-      </c>
-      <c r="M94" s="2" t="n"/>
+          <t>李坤纬</t>
+        </is>
+      </c>
+      <c r="M94" s="2" t="inlineStr"/>
     </row>
     <row r="95" ht="80" customHeight="1">
       <c r="A95" s="2" t="inlineStr">
         <is>
-          <t>TC-WX-004</t>
+          <t>TC-SD-002</t>
         </is>
       </c>
       <c r="B95" s="2" t="inlineStr">
@@ -5498,7 +5481,7 @@
       </c>
       <c r="C95" s="3" t="inlineStr">
         <is>
-          <t>/微信公众号</t>
+          <t>/空间删除</t>
         </is>
       </c>
       <c r="D95" s="3" t="inlineStr">
@@ -5507,41 +5490,41 @@
         </is>
       </c>
       <c r="E95" s="3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F95" s="4" t="inlineStr">
         <is>
-          <t>门户_GET_签名错误</t>
+          <t>删除_越权</t>
         </is>
       </c>
       <c r="G95" s="2" t="inlineStr">
         <is>
-          <t>伪造签名</t>
+          <t>testuser02</t>
         </is>
       </c>
       <c r="H95" s="2" t="inlineStr">
         <is>
-          <t>1. GET /wx/mp/portal signature=invalid</t>
+          <t>POST /space/delete id=别人空间</t>
         </is>
       </c>
       <c r="I95" s="2" t="inlineStr">
         <is>
-          <t>返回空或失败提示</t>
-        </is>
-      </c>
-      <c r="J95" s="2" t="n"/>
-      <c r="K95" s="2" t="n"/>
+          <t>code=40300</t>
+        </is>
+      </c>
+      <c r="J95" s="2" t="inlineStr"/>
+      <c r="K95" s="2" t="inlineStr"/>
       <c r="L95" s="2" t="inlineStr">
         <is>
-          <t>林景彬</t>
-        </is>
-      </c>
-      <c r="M95" s="2" t="n"/>
+          <t>李坤纬</t>
+        </is>
+      </c>
+      <c r="M95" s="2" t="inlineStr"/>
     </row>
     <row r="96" ht="80" customHeight="1">
       <c r="A96" s="2" t="inlineStr">
         <is>
-          <t>TC-WX-005</t>
+          <t>TC-SU-001</t>
         </is>
       </c>
       <c r="B96" s="2" t="inlineStr">
@@ -5551,7 +5534,7 @@
       </c>
       <c r="C96" s="3" t="inlineStr">
         <is>
-          <t>/微信公众号</t>
+          <t>/空间更新</t>
         </is>
       </c>
       <c r="D96" s="3" t="inlineStr">
@@ -5560,41 +5543,41 @@
         </is>
       </c>
       <c r="E96" s="3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F96" s="4" t="inlineStr">
         <is>
-          <t>门户_POST_未登录</t>
+          <t>更新_正常</t>
         </is>
       </c>
       <c r="G96" s="2" t="inlineStr">
         <is>
-          <t>无</t>
+          <t>testuser01是创建者</t>
         </is>
       </c>
       <c r="H96" s="2" t="inlineStr">
         <is>
-          <t>1. POST /wx/mp/portal</t>
+          <t>POST /space/update id=1 spaceName='更新'</t>
         </is>
       </c>
       <c r="I96" s="2" t="inlineStr">
         <is>
-          <t>返回code=40100 或 40300</t>
-        </is>
-      </c>
-      <c r="J96" s="2" t="n"/>
-      <c r="K96" s="2" t="n"/>
+          <t>code=0</t>
+        </is>
+      </c>
+      <c r="J96" s="2" t="inlineStr"/>
+      <c r="K96" s="2" t="inlineStr"/>
       <c r="L96" s="2" t="inlineStr">
         <is>
-          <t>林景彬</t>
-        </is>
-      </c>
-      <c r="M96" s="2" t="n"/>
+          <t>李坤纬</t>
+        </is>
+      </c>
+      <c r="M96" s="2" t="inlineStr"/>
     </row>
     <row r="97" ht="80" customHeight="1">
       <c r="A97" s="2" t="inlineStr">
         <is>
-          <t>TC-PERF-001</t>
+          <t>TC-SU-002</t>
         </is>
       </c>
       <c r="B97" s="2" t="inlineStr">
@@ -5604,50 +5587,50 @@
       </c>
       <c r="C97" s="3" t="inlineStr">
         <is>
-          <t>/文件上传</t>
+          <t>/空间更新</t>
         </is>
       </c>
       <c r="D97" s="3" t="inlineStr">
         <is>
-          <t>性能测试</t>
+          <t>功能测试</t>
         </is>
       </c>
       <c r="E97" s="3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F97" s="4" t="inlineStr">
         <is>
-          <t>上传_50并发_1MB</t>
+          <t>更新_越权</t>
         </is>
       </c>
       <c r="G97" s="2" t="inlineStr">
         <is>
-          <t>已安装 JMeter</t>
+          <t>testuser02</t>
         </is>
       </c>
       <c r="H97" s="2" t="inlineStr">
         <is>
-          <t>1. JMeter 50 线程上传 1MB jpg</t>
+          <t>POST /space/update</t>
         </is>
       </c>
       <c r="I97" s="2" t="inlineStr">
         <is>
-          <t>P95 &lt; 2s, 错误率 &lt; 5%</t>
-        </is>
-      </c>
-      <c r="J97" s="2" t="n"/>
-      <c r="K97" s="2" t="n"/>
+          <t>code=40300</t>
+        </is>
+      </c>
+      <c r="J97" s="2" t="inlineStr"/>
+      <c r="K97" s="2" t="inlineStr"/>
       <c r="L97" s="2" t="inlineStr">
         <is>
-          <t>林景彬</t>
-        </is>
-      </c>
-      <c r="M97" s="2" t="n"/>
+          <t>李坤纬</t>
+        </is>
+      </c>
+      <c r="M97" s="2" t="inlineStr"/>
     </row>
     <row r="98" ht="80" customHeight="1">
       <c r="A98" s="2" t="inlineStr">
         <is>
-          <t>TC-API-001</t>
+          <t>TC-MA-001</t>
         </is>
       </c>
       <c r="B98" s="2" t="inlineStr">
@@ -5657,50 +5640,50 @@
       </c>
       <c r="C98" s="3" t="inlineStr">
         <is>
-          <t>/文件上传</t>
+          <t>/成员添加</t>
         </is>
       </c>
       <c r="D98" s="3" t="inlineStr">
         <is>
-          <t>接口测试</t>
+          <t>功能测试</t>
         </is>
       </c>
       <c r="E98" s="3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F98" s="4" t="inlineStr">
         <is>
-          <t>upload_缺multipart边界</t>
+          <t>管理员添加_正常</t>
         </is>
       </c>
       <c r="G98" s="2" t="inlineStr">
         <is>
-          <t>testuser01 已登录</t>
+          <t>admin</t>
         </is>
       </c>
       <c r="H98" s="2" t="inlineStr">
         <is>
-          <t>1. 发送不完整 multipart 请求</t>
+          <t>POST /spaceUser/add spaceId=1 userId=2</t>
         </is>
       </c>
       <c r="I98" s="2" t="inlineStr">
         <is>
-          <t>返回 400 或 415</t>
-        </is>
-      </c>
-      <c r="J98" s="2" t="n"/>
-      <c r="K98" s="2" t="n"/>
+          <t>code=0</t>
+        </is>
+      </c>
+      <c r="J98" s="2" t="inlineStr"/>
+      <c r="K98" s="2" t="inlineStr"/>
       <c r="L98" s="2" t="inlineStr">
         <is>
-          <t>林景彬</t>
-        </is>
-      </c>
-      <c r="M98" s="2" t="n"/>
+          <t>李坤纬</t>
+        </is>
+      </c>
+      <c r="M98" s="2" t="inlineStr"/>
     </row>
     <row r="99" ht="80" customHeight="1">
       <c r="A99" s="2" t="inlineStr">
         <is>
-          <t>TC-SEC-001</t>
+          <t>TC-MA-002</t>
         </is>
       </c>
       <c r="B99" s="2" t="inlineStr">
@@ -5710,12 +5693,12 @@
       </c>
       <c r="C99" s="3" t="inlineStr">
         <is>
-          <t>/文件上传</t>
+          <t>/成员添加</t>
         </is>
       </c>
       <c r="D99" s="3" t="inlineStr">
         <is>
-          <t>安全测试</t>
+          <t>功能测试</t>
         </is>
       </c>
       <c r="E99" s="3" t="n">
@@ -5723,37 +5706,37 @@
       </c>
       <c r="F99" s="4" t="inlineStr">
         <is>
-          <t>上传_双扩展名</t>
+          <t>添加_重复</t>
         </is>
       </c>
       <c r="G99" s="2" t="inlineStr">
         <is>
-          <t>testuser01 已登录</t>
+          <t>admin</t>
         </is>
       </c>
       <c r="H99" s="2" t="inlineStr">
         <is>
-          <t>1. file=1.jpg.php</t>
+          <t>重复添加</t>
         </is>
       </c>
       <c r="I99" s="2" t="inlineStr">
         <is>
-          <t>返回code=40001</t>
-        </is>
-      </c>
-      <c r="J99" s="2" t="n"/>
-      <c r="K99" s="2" t="n"/>
+          <t>code=40001</t>
+        </is>
+      </c>
+      <c r="J99" s="2" t="inlineStr"/>
+      <c r="K99" s="2" t="inlineStr"/>
       <c r="L99" s="2" t="inlineStr">
         <is>
-          <t>林景彬</t>
-        </is>
-      </c>
-      <c r="M99" s="2" t="n"/>
+          <t>李坤纬</t>
+        </is>
+      </c>
+      <c r="M99" s="2" t="inlineStr"/>
     </row>
     <row r="100" ht="80" customHeight="1">
       <c r="A100" s="2" t="inlineStr">
         <is>
-          <t>TC-AT-006</t>
+          <t>TC-MA-003</t>
         </is>
       </c>
       <c r="B100" s="2" t="inlineStr">
@@ -5763,7 +5746,7 @@
       </c>
       <c r="C100" s="3" t="inlineStr">
         <is>
-          <t>/头像上传</t>
+          <t>/成员添加</t>
         </is>
       </c>
       <c r="D100" s="3" t="inlineStr">
@@ -5772,41 +5755,41 @@
         </is>
       </c>
       <c r="E100" s="3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F100" s="4" t="inlineStr">
         <is>
-          <t>头像_超过1MB_应失败</t>
+          <t>添加_普通用户越权</t>
         </is>
       </c>
       <c r="G100" s="2" t="inlineStr">
         <is>
-          <t>testuser01 已登录</t>
+          <t>testuser01</t>
         </is>
       </c>
       <c r="H100" s="2" t="inlineStr">
         <is>
-          <t>1. POST /file/upload/avatar file=1.5MB_jpg</t>
+          <t>POST /spaceUser/add</t>
         </is>
       </c>
       <c r="I100" s="2" t="inlineStr">
         <is>
-          <t>返回code=40001 超限</t>
-        </is>
-      </c>
-      <c r="J100" s="2" t="n"/>
-      <c r="K100" s="2" t="n"/>
+          <t>code=40300</t>
+        </is>
+      </c>
+      <c r="J100" s="2" t="inlineStr"/>
+      <c r="K100" s="2" t="inlineStr"/>
       <c r="L100" s="2" t="inlineStr">
         <is>
-          <t>林景彬</t>
-        </is>
-      </c>
-      <c r="M100" s="2" t="n"/>
+          <t>李坤纬</t>
+        </is>
+      </c>
+      <c r="M100" s="2" t="inlineStr"/>
     </row>
     <row r="101" ht="80" customHeight="1">
       <c r="A101" s="2" t="inlineStr">
         <is>
-          <t>TC-AT-007</t>
+          <t>TC-MD-001</t>
         </is>
       </c>
       <c r="B101" s="2" t="inlineStr">
@@ -5816,7 +5799,7 @@
       </c>
       <c r="C101" s="3" t="inlineStr">
         <is>
-          <t>/头像上传</t>
+          <t>/成员删除</t>
         </is>
       </c>
       <c r="D101" s="3" t="inlineStr">
@@ -5825,41 +5808,41 @@
         </is>
       </c>
       <c r="E101" s="3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F101" s="4" t="inlineStr">
         <is>
-          <t>头像_非图片文件_应失败</t>
+          <t>删除_正常</t>
         </is>
       </c>
       <c r="G101" s="2" t="inlineStr">
         <is>
-          <t>testuser01 已登录</t>
+          <t>admin</t>
         </is>
       </c>
       <c r="H101" s="2" t="inlineStr">
         <is>
-          <t>1. POST /file/upload/avatar file=test.pdf</t>
+          <t>POST /spaceUser/delete id=1</t>
         </is>
       </c>
       <c r="I101" s="2" t="inlineStr">
         <is>
-          <t>返回code=40001</t>
-        </is>
-      </c>
-      <c r="J101" s="2" t="n"/>
-      <c r="K101" s="2" t="n"/>
+          <t>code=0</t>
+        </is>
+      </c>
+      <c r="J101" s="2" t="inlineStr"/>
+      <c r="K101" s="2" t="inlineStr"/>
       <c r="L101" s="2" t="inlineStr">
         <is>
-          <t>林景彬</t>
-        </is>
-      </c>
-      <c r="M101" s="2" t="n"/>
+          <t>李坤纬</t>
+        </is>
+      </c>
+      <c r="M101" s="2" t="inlineStr"/>
     </row>
     <row r="102" ht="80" customHeight="1">
       <c r="A102" s="2" t="inlineStr">
         <is>
-          <t>TC-AT-008</t>
+          <t>TC-MD-002</t>
         </is>
       </c>
       <c r="B102" s="2" t="inlineStr">
@@ -5869,7 +5852,7 @@
       </c>
       <c r="C102" s="3" t="inlineStr">
         <is>
-          <t>/头像上传</t>
+          <t>/成员删除</t>
         </is>
       </c>
       <c r="D102" s="3" t="inlineStr">
@@ -5878,41 +5861,41 @@
         </is>
       </c>
       <c r="E102" s="3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F102" s="4" t="inlineStr">
         <is>
-          <t>头像_webp格式</t>
+          <t>删除_越权</t>
         </is>
       </c>
       <c r="G102" s="2" t="inlineStr">
         <is>
-          <t>testuser01 已登录</t>
+          <t>testuser02</t>
         </is>
       </c>
       <c r="H102" s="2" t="inlineStr">
         <is>
-          <t>1. POST /file/upload/avatar file=300KB_webp</t>
+          <t>POST /spaceUser/delete</t>
         </is>
       </c>
       <c r="I102" s="2" t="inlineStr">
         <is>
-          <t>返回code=0 picFormat=webp</t>
-        </is>
-      </c>
-      <c r="J102" s="2" t="n"/>
-      <c r="K102" s="2" t="n"/>
+          <t>code=40300</t>
+        </is>
+      </c>
+      <c r="J102" s="2" t="inlineStr"/>
+      <c r="K102" s="2" t="inlineStr"/>
       <c r="L102" s="2" t="inlineStr">
         <is>
-          <t>林景彬</t>
-        </is>
-      </c>
-      <c r="M102" s="2" t="n"/>
+          <t>李坤纬</t>
+        </is>
+      </c>
+      <c r="M102" s="2" t="inlineStr"/>
     </row>
     <row r="103" ht="80" customHeight="1">
       <c r="A103" s="2" t="inlineStr">
         <is>
-          <t>TC-AT-009</t>
+          <t>TC-MG-001</t>
         </is>
       </c>
       <c r="B103" s="2" t="inlineStr">
@@ -5922,7 +5905,7 @@
       </c>
       <c r="C103" s="3" t="inlineStr">
         <is>
-          <t>/头像上传</t>
+          <t>/成员查询</t>
         </is>
       </c>
       <c r="D103" s="3" t="inlineStr">
@@ -5931,41 +5914,41 @@
         </is>
       </c>
       <c r="E103" s="3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F103" s="4" t="inlineStr">
         <is>
-          <t>头像_空文件_应失败</t>
+          <t>查询_正常</t>
         </is>
       </c>
       <c r="G103" s="2" t="inlineStr">
         <is>
-          <t>testuser01 已登录</t>
+          <t>admin</t>
         </is>
       </c>
       <c r="H103" s="2" t="inlineStr">
         <is>
-          <t>1. POST /file/upload/avatar file=0byte</t>
+          <t>POST /spaceUser/get spaceId=1 userId=2</t>
         </is>
       </c>
       <c r="I103" s="2" t="inlineStr">
         <is>
-          <t>返回code=40001</t>
-        </is>
-      </c>
-      <c r="J103" s="2" t="n"/>
-      <c r="K103" s="2" t="n"/>
+          <t>code=0</t>
+        </is>
+      </c>
+      <c r="J103" s="2" t="inlineStr"/>
+      <c r="K103" s="2" t="inlineStr"/>
       <c r="L103" s="2" t="inlineStr">
         <is>
-          <t>林景彬</t>
-        </is>
-      </c>
-      <c r="M103" s="2" t="n"/>
+          <t>李坤纬</t>
+        </is>
+      </c>
+      <c r="M103" s="2" t="inlineStr"/>
     </row>
     <row r="104" ht="80" customHeight="1">
       <c r="A104" s="2" t="inlineStr">
         <is>
-          <t>TC-AT-010</t>
+          <t>TC-MG-002</t>
         </is>
       </c>
       <c r="B104" s="2" t="inlineStr">
@@ -5975,7 +5958,7 @@
       </c>
       <c r="C104" s="3" t="inlineStr">
         <is>
-          <t>/头像上传</t>
+          <t>/成员查询</t>
         </is>
       </c>
       <c r="D104" s="3" t="inlineStr">
@@ -5984,42 +5967,41 @@
         </is>
       </c>
       <c r="E104" s="3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F104" s="4" t="inlineStr">
         <is>
-          <t>头像_重复上传覆盖旧头像</t>
+          <t>查询_普通用户</t>
         </is>
       </c>
       <c r="G104" s="2" t="inlineStr">
         <is>
-          <t>testuser01 已登录</t>
+          <t>testuser01</t>
         </is>
       </c>
       <c r="H104" s="2" t="inlineStr">
         <is>
-          <t>1. 先上传头像A
-2. 再上传头像B</t>
+          <t>POST /spaceUser/get</t>
         </is>
       </c>
       <c r="I104" s="2" t="inlineStr">
         <is>
-          <t>返回code=0 userAvatar 改为新URL</t>
-        </is>
-      </c>
-      <c r="J104" s="2" t="n"/>
-      <c r="K104" s="2" t="n"/>
+          <t>code=40100或code=0</t>
+        </is>
+      </c>
+      <c r="J104" s="2" t="inlineStr"/>
+      <c r="K104" s="2" t="inlineStr"/>
       <c r="L104" s="2" t="inlineStr">
         <is>
-          <t>林景彬</t>
-        </is>
-      </c>
-      <c r="M104" s="2" t="n"/>
+          <t>李坤纬</t>
+        </is>
+      </c>
+      <c r="M104" s="2" t="inlineStr"/>
     </row>
     <row r="105" ht="80" customHeight="1">
       <c r="A105" s="2" t="inlineStr">
         <is>
-          <t>TC-GC-006</t>
+          <t>TC-ML-001</t>
         </is>
       </c>
       <c r="B105" s="2" t="inlineStr">
@@ -6029,7 +6011,7 @@
       </c>
       <c r="C105" s="3" t="inlineStr">
         <is>
-          <t>/获取当前用户</t>
+          <t>/成员列表</t>
         </is>
       </c>
       <c r="D105" s="3" t="inlineStr">
@@ -6042,37 +6024,37 @@
       </c>
       <c r="F105" s="4" t="inlineStr">
         <is>
-          <t>获取_管理员视角</t>
+          <t>列表_正常</t>
         </is>
       </c>
       <c r="G105" s="2" t="inlineStr">
         <is>
-          <t>admin 已登录</t>
+          <t>admin</t>
         </is>
       </c>
       <c r="H105" s="2" t="inlineStr">
         <is>
-          <t>1. GET /user/get/login (admin Cookie)</t>
+          <t>POST /spaceUser/list spaceId=1</t>
         </is>
       </c>
       <c r="I105" s="2" t="inlineStr">
         <is>
-          <t>返回code=0 含 userRole=admin</t>
-        </is>
-      </c>
-      <c r="J105" s="2" t="n"/>
-      <c r="K105" s="2" t="n"/>
+          <t>code=0, 成员列表</t>
+        </is>
+      </c>
+      <c r="J105" s="2" t="inlineStr"/>
+      <c r="K105" s="2" t="inlineStr"/>
       <c r="L105" s="2" t="inlineStr">
         <is>
-          <t>林景彬</t>
-        </is>
-      </c>
-      <c r="M105" s="2" t="n"/>
+          <t>李坤纬</t>
+        </is>
+      </c>
+      <c r="M105" s="2" t="inlineStr"/>
     </row>
     <row r="106" ht="80" customHeight="1">
       <c r="A106" s="2" t="inlineStr">
         <is>
-          <t>TC-GC-007</t>
+          <t>TC-ML-002</t>
         </is>
       </c>
       <c r="B106" s="2" t="inlineStr">
@@ -6082,20 +6064,20 @@
       </c>
       <c r="C106" s="3" t="inlineStr">
         <is>
-          <t>/获取当前用户</t>
+          <t>/成员列表</t>
         </is>
       </c>
       <c r="D106" s="3" t="inlineStr">
         <is>
-          <t>接口测试</t>
+          <t>功能测试</t>
         </is>
       </c>
       <c r="E106" s="3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F106" s="4" t="inlineStr">
         <is>
-          <t>获取_id为字符串</t>
+          <t>列表_未登录</t>
         </is>
       </c>
       <c r="G106" s="2" t="inlineStr">
@@ -6105,27 +6087,27 @@
       </c>
       <c r="H106" s="2" t="inlineStr">
         <is>
-          <t>1. Cookie伪造 userId='abc'</t>
+          <t>POST /spaceUser/list</t>
         </is>
       </c>
       <c r="I106" s="2" t="inlineStr">
         <is>
-          <t>返回code=40100</t>
-        </is>
-      </c>
-      <c r="J106" s="2" t="n"/>
-      <c r="K106" s="2" t="n"/>
+          <t>code=40100</t>
+        </is>
+      </c>
+      <c r="J106" s="2" t="inlineStr"/>
+      <c r="K106" s="2" t="inlineStr"/>
       <c r="L106" s="2" t="inlineStr">
         <is>
-          <t>林景彬</t>
-        </is>
-      </c>
-      <c r="M106" s="2" t="n"/>
+          <t>李坤纬</t>
+        </is>
+      </c>
+      <c r="M106" s="2" t="inlineStr"/>
     </row>
     <row r="107" ht="80" customHeight="1">
       <c r="A107" s="2" t="inlineStr">
         <is>
-          <t>TC-GC-008</t>
+          <t>TC-ME-001</t>
         </is>
       </c>
       <c r="B107" s="2" t="inlineStr">
@@ -6135,7 +6117,7 @@
       </c>
       <c r="C107" s="3" t="inlineStr">
         <is>
-          <t>/获取当前用户</t>
+          <t>/成员编辑</t>
         </is>
       </c>
       <c r="D107" s="3" t="inlineStr">
@@ -6148,37 +6130,37 @@
       </c>
       <c r="F107" s="4" t="inlineStr">
         <is>
-          <t>获取_用户信息完整</t>
+          <t>编辑_正常</t>
         </is>
       </c>
       <c r="G107" s="2" t="inlineStr">
         <is>
-          <t>testuser01 已登录</t>
+          <t>admin</t>
         </is>
       </c>
       <c r="H107" s="2" t="inlineStr">
         <is>
-          <t>1. GET /user/get/login</t>
+          <t>POST /spaceUser/edit id=1 spaceRole='editor'</t>
         </is>
       </c>
       <c r="I107" s="2" t="inlineStr">
         <is>
-          <t>返回code=0 含 userAvatar/userName/userProfile</t>
-        </is>
-      </c>
-      <c r="J107" s="2" t="n"/>
-      <c r="K107" s="2" t="n"/>
+          <t>code=0</t>
+        </is>
+      </c>
+      <c r="J107" s="2" t="inlineStr"/>
+      <c r="K107" s="2" t="inlineStr"/>
       <c r="L107" s="2" t="inlineStr">
         <is>
-          <t>林景彬</t>
-        </is>
-      </c>
-      <c r="M107" s="2" t="n"/>
+          <t>李坤纬</t>
+        </is>
+      </c>
+      <c r="M107" s="2" t="inlineStr"/>
     </row>
     <row r="108" ht="80" customHeight="1">
       <c r="A108" s="2" t="inlineStr">
         <is>
-          <t>TC-GC-009</t>
+          <t>TC-ME-002</t>
         </is>
       </c>
       <c r="B108" s="2" t="inlineStr">
@@ -6188,12 +6170,12 @@
       </c>
       <c r="C108" s="3" t="inlineStr">
         <is>
-          <t>/获取当前用户</t>
+          <t>/成员编辑</t>
         </is>
       </c>
       <c r="D108" s="3" t="inlineStr">
         <is>
-          <t>安全测试</t>
+          <t>功能测试</t>
         </is>
       </c>
       <c r="E108" s="3" t="n">
@@ -6201,37 +6183,37 @@
       </c>
       <c r="F108" s="4" t="inlineStr">
         <is>
-          <t>XSS_用户简介</t>
+          <t>编辑_越权</t>
         </is>
       </c>
       <c r="G108" s="2" t="inlineStr">
         <is>
-          <t>testuser01 已登录</t>
+          <t>testuser02</t>
         </is>
       </c>
       <c r="H108" s="2" t="inlineStr">
         <is>
-          <t>1. POST /user/update/my userProfile='&lt;script&gt;alert(1)&lt;/script&gt;'</t>
+          <t>POST /spaceUser/edit</t>
         </is>
       </c>
       <c r="I108" s="2" t="inlineStr">
         <is>
-          <t>返回code=0 渲染时被转义</t>
-        </is>
-      </c>
-      <c r="J108" s="2" t="n"/>
-      <c r="K108" s="2" t="n"/>
+          <t>code=40300</t>
+        </is>
+      </c>
+      <c r="J108" s="2" t="inlineStr"/>
+      <c r="K108" s="2" t="inlineStr"/>
       <c r="L108" s="2" t="inlineStr">
         <is>
-          <t>林景彬</t>
-        </is>
-      </c>
-      <c r="M108" s="2" t="n"/>
+          <t>李坤纬</t>
+        </is>
+      </c>
+      <c r="M108" s="2" t="inlineStr"/>
     </row>
     <row r="109" ht="80" customHeight="1">
       <c r="A109" s="2" t="inlineStr">
         <is>
-          <t>TC-GC-010</t>
+          <t>TC-LM-001</t>
         </is>
       </c>
       <c r="B109" s="2" t="inlineStr">
@@ -6241,7 +6223,7 @@
       </c>
       <c r="C109" s="3" t="inlineStr">
         <is>
-          <t>/获取当前用户</t>
+          <t>/我的空间</t>
         </is>
       </c>
       <c r="D109" s="3" t="inlineStr">
@@ -6254,37 +6236,37 @@
       </c>
       <c r="F109" s="4" t="inlineStr">
         <is>
-          <t>获取_用户简介含emoji</t>
+          <t>我的空间列表</t>
         </is>
       </c>
       <c r="G109" s="2" t="inlineStr">
         <is>
-          <t>testuser01 已登录</t>
+          <t>testuser01</t>
         </is>
       </c>
       <c r="H109" s="2" t="inlineStr">
         <is>
-          <t>1. POST /user/update/my userProfile='😀 用户'</t>
+          <t>POST /spaceUser/list/my</t>
         </is>
       </c>
       <c r="I109" s="2" t="inlineStr">
         <is>
-          <t>返回code=0</t>
-        </is>
-      </c>
-      <c r="J109" s="2" t="n"/>
-      <c r="K109" s="2" t="n"/>
+          <t>code=0, 我加入的空间</t>
+        </is>
+      </c>
+      <c r="J109" s="2" t="inlineStr"/>
+      <c r="K109" s="2" t="inlineStr"/>
       <c r="L109" s="2" t="inlineStr">
         <is>
-          <t>林景彬</t>
-        </is>
-      </c>
-      <c r="M109" s="2" t="n"/>
+          <t>李坤纬</t>
+        </is>
+      </c>
+      <c r="M109" s="2" t="inlineStr"/>
     </row>
     <row r="110" ht="80" customHeight="1">
       <c r="A110" s="2" t="inlineStr">
         <is>
-          <t>TC-UU-001</t>
+          <t>TC-LM-002</t>
         </is>
       </c>
       <c r="B110" s="2" t="inlineStr">
@@ -6294,7 +6276,7 @@
       </c>
       <c r="C110" s="3" t="inlineStr">
         <is>
-          <t>/用户更新</t>
+          <t>/我的空间</t>
         </is>
       </c>
       <c r="D110" s="3" t="inlineStr">
@@ -6307,37 +6289,37 @@
       </c>
       <c r="F110" s="4" t="inlineStr">
         <is>
-          <t>更新_昵称</t>
+          <t>我的空间_未登录</t>
         </is>
       </c>
       <c r="G110" s="2" t="inlineStr">
         <is>
-          <t>testuser01 已登录</t>
+          <t>无</t>
         </is>
       </c>
       <c r="H110" s="2" t="inlineStr">
         <is>
-          <t>1. POST /user/update/my userName='新名字'</t>
+          <t>POST /spaceUser/list/my</t>
         </is>
       </c>
       <c r="I110" s="2" t="inlineStr">
         <is>
-          <t>返回code=0</t>
-        </is>
-      </c>
-      <c r="J110" s="2" t="n"/>
-      <c r="K110" s="2" t="n"/>
+          <t>code=40100</t>
+        </is>
+      </c>
+      <c r="J110" s="2" t="inlineStr"/>
+      <c r="K110" s="2" t="inlineStr"/>
       <c r="L110" s="2" t="inlineStr">
         <is>
-          <t>林景彬</t>
-        </is>
-      </c>
-      <c r="M110" s="2" t="n"/>
+          <t>李坤纬</t>
+        </is>
+      </c>
+      <c r="M110" s="2" t="inlineStr"/>
     </row>
     <row r="111" ht="80" customHeight="1">
       <c r="A111" s="2" t="inlineStr">
         <is>
-          <t>TC-UU-002</t>
+          <t>TC-AU-001</t>
         </is>
       </c>
       <c r="B111" s="2" t="inlineStr">
@@ -6347,7 +6329,7 @@
       </c>
       <c r="C111" s="3" t="inlineStr">
         <is>
-          <t>/用户更新</t>
+          <t>/空间用量分析</t>
         </is>
       </c>
       <c r="D111" s="3" t="inlineStr">
@@ -6356,41 +6338,41 @@
         </is>
       </c>
       <c r="E111" s="3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F111" s="4" t="inlineStr">
         <is>
-          <t>更新_昵称为空</t>
+          <t>用量分析_正常</t>
         </is>
       </c>
       <c r="G111" s="2" t="inlineStr">
         <is>
-          <t>testuser01 已登录</t>
+          <t>testuser01有空间</t>
         </is>
       </c>
       <c r="H111" s="2" t="inlineStr">
         <is>
-          <t>1. POST /user/update/my userName=''</t>
+          <t>POST /space/analyze/usage spaceId=1</t>
         </is>
       </c>
       <c r="I111" s="2" t="inlineStr">
         <is>
-          <t>返回code=40001</t>
-        </is>
-      </c>
-      <c r="J111" s="2" t="n"/>
-      <c r="K111" s="2" t="n"/>
+          <t>code=0</t>
+        </is>
+      </c>
+      <c r="J111" s="2" t="inlineStr"/>
+      <c r="K111" s="2" t="inlineStr"/>
       <c r="L111" s="2" t="inlineStr">
         <is>
-          <t>林景彬</t>
-        </is>
-      </c>
-      <c r="M111" s="2" t="n"/>
+          <t>李坤纬</t>
+        </is>
+      </c>
+      <c r="M111" s="2" t="inlineStr"/>
     </row>
     <row r="112" ht="80" customHeight="1">
       <c r="A112" s="2" t="inlineStr">
         <is>
-          <t>TC-UU-003</t>
+          <t>TC-AC-001</t>
         </is>
       </c>
       <c r="B112" s="2" t="inlineStr">
@@ -6400,50 +6382,50 @@
       </c>
       <c r="C112" s="3" t="inlineStr">
         <is>
-          <t>/用户更新</t>
+          <t>/空间分类分析</t>
         </is>
       </c>
       <c r="D112" s="3" t="inlineStr">
         <is>
-          <t>接口测试</t>
+          <t>功能测试</t>
         </is>
       </c>
       <c r="E112" s="3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F112" s="4" t="inlineStr">
         <is>
-          <t>更新_缺userName</t>
+          <t>分类分析_正常</t>
         </is>
       </c>
       <c r="G112" s="2" t="inlineStr">
         <is>
-          <t>testuser01 已登录</t>
+          <t>testuser01有空间</t>
         </is>
       </c>
       <c r="H112" s="2" t="inlineStr">
         <is>
-          <t>1. body 无 userName</t>
+          <t>POST /space/analyze/category spaceId=1</t>
         </is>
       </c>
       <c r="I112" s="2" t="inlineStr">
         <is>
-          <t>返回code=40001</t>
-        </is>
-      </c>
-      <c r="J112" s="2" t="n"/>
-      <c r="K112" s="2" t="n"/>
+          <t>code=0</t>
+        </is>
+      </c>
+      <c r="J112" s="2" t="inlineStr"/>
+      <c r="K112" s="2" t="inlineStr"/>
       <c r="L112" s="2" t="inlineStr">
         <is>
-          <t>林景彬</t>
-        </is>
-      </c>
-      <c r="M112" s="2" t="n"/>
+          <t>李坤纬</t>
+        </is>
+      </c>
+      <c r="M112" s="2" t="inlineStr"/>
     </row>
     <row r="113" ht="80" customHeight="1">
       <c r="A113" s="2" t="inlineStr">
         <is>
-          <t>TC-PERF-002</t>
+          <t>TC-AT-001</t>
         </is>
       </c>
       <c r="B113" s="2" t="inlineStr">
@@ -6453,253 +6435,1850 @@
       </c>
       <c r="C113" s="3" t="inlineStr">
         <is>
-          <t>/头像上传</t>
+          <t>/空间标签分析</t>
         </is>
       </c>
       <c r="D113" s="3" t="inlineStr">
         <is>
-          <t>性能测试</t>
+          <t>功能测试</t>
         </is>
       </c>
       <c r="E113" s="3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F113" s="4" t="inlineStr">
         <is>
-          <t>头像上传_100并发</t>
+          <t>标签分析_正常</t>
         </is>
       </c>
       <c r="G113" s="2" t="inlineStr">
         <is>
-          <t>已安装 JMeter</t>
+          <t>testuser01有空间</t>
         </is>
       </c>
       <c r="H113" s="2" t="inlineStr">
         <is>
-          <t>1. JMeter 100 线程 POST /file/upload/avatar</t>
+          <t>POST /space/analyze/tag spaceId=1</t>
         </is>
       </c>
       <c r="I113" s="2" t="inlineStr">
         <is>
-          <t>P95 &lt; 3s, 错误率 &lt; 5%</t>
-        </is>
-      </c>
-      <c r="J113" s="2" t="n"/>
-      <c r="K113" s="2" t="n"/>
+          <t>code=0</t>
+        </is>
+      </c>
+      <c r="J113" s="2" t="inlineStr"/>
+      <c r="K113" s="2" t="inlineStr"/>
       <c r="L113" s="2" t="inlineStr">
         <is>
-          <t>林景彬</t>
-        </is>
-      </c>
-      <c r="M113" s="2" t="n"/>
+          <t>李坤纬</t>
+        </is>
+      </c>
+      <c r="M113" s="2" t="inlineStr"/>
     </row>
     <row r="114" ht="80" customHeight="1">
       <c r="A114" s="2" t="inlineStr">
         <is>
+          <t>TC-AZ-001</t>
+        </is>
+      </c>
+      <c r="B114" s="2" t="inlineStr">
+        <is>
+          <t>内娱图库StarPicture</t>
+        </is>
+      </c>
+      <c r="C114" s="3" t="inlineStr">
+        <is>
+          <t>/空间大小分析</t>
+        </is>
+      </c>
+      <c r="D114" s="3" t="inlineStr">
+        <is>
+          <t>功能测试</t>
+        </is>
+      </c>
+      <c r="E114" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="F114" s="4" t="inlineStr">
+        <is>
+          <t>大小分析_正常</t>
+        </is>
+      </c>
+      <c r="G114" s="2" t="inlineStr">
+        <is>
+          <t>testuser01有空间</t>
+        </is>
+      </c>
+      <c r="H114" s="2" t="inlineStr">
+        <is>
+          <t>POST /space/analyze/size spaceId=1</t>
+        </is>
+      </c>
+      <c r="I114" s="2" t="inlineStr">
+        <is>
+          <t>code=0</t>
+        </is>
+      </c>
+      <c r="J114" s="2" t="inlineStr"/>
+      <c r="K114" s="2" t="inlineStr"/>
+      <c r="L114" s="2" t="inlineStr">
+        <is>
+          <t>李坤纬</t>
+        </is>
+      </c>
+      <c r="M114" s="2" t="inlineStr"/>
+    </row>
+    <row r="115" ht="80" customHeight="1">
+      <c r="A115" s="2" t="inlineStr">
+        <is>
+          <t>TC-AP-001</t>
+        </is>
+      </c>
+      <c r="B115" s="2" t="inlineStr">
+        <is>
+          <t>内娱图库StarPicture</t>
+        </is>
+      </c>
+      <c r="C115" s="3" t="inlineStr">
+        <is>
+          <t>/空间用户分析</t>
+        </is>
+      </c>
+      <c r="D115" s="3" t="inlineStr">
+        <is>
+          <t>功能测试</t>
+        </is>
+      </c>
+      <c r="E115" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="F115" s="4" t="inlineStr">
+        <is>
+          <t>用户分析_正常</t>
+        </is>
+      </c>
+      <c r="G115" s="2" t="inlineStr">
+        <is>
+          <t>testuser01有空间</t>
+        </is>
+      </c>
+      <c r="H115" s="2" t="inlineStr">
+        <is>
+          <t>POST /space/analyze/user spaceId=1</t>
+        </is>
+      </c>
+      <c r="I115" s="2" t="inlineStr">
+        <is>
+          <t>code=0</t>
+        </is>
+      </c>
+      <c r="J115" s="2" t="inlineStr"/>
+      <c r="K115" s="2" t="inlineStr"/>
+      <c r="L115" s="2" t="inlineStr">
+        <is>
+          <t>李坤纬</t>
+        </is>
+      </c>
+      <c r="M115" s="2" t="inlineStr"/>
+    </row>
+    <row r="116" ht="80" customHeight="1">
+      <c r="A116" s="2" t="inlineStr">
+        <is>
+          <t>TC-AR-001</t>
+        </is>
+      </c>
+      <c r="B116" s="2" t="inlineStr">
+        <is>
+          <t>内娱图库StarPicture</t>
+        </is>
+      </c>
+      <c r="C116" s="3" t="inlineStr">
+        <is>
+          <t>/空间排行</t>
+        </is>
+      </c>
+      <c r="D116" s="3" t="inlineStr">
+        <is>
+          <t>功能测试</t>
+        </is>
+      </c>
+      <c r="E116" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="F116" s="4" t="inlineStr">
+        <is>
+          <t>排行_正常</t>
+        </is>
+      </c>
+      <c r="G116" s="2" t="inlineStr">
+        <is>
+          <t>testuser01</t>
+        </is>
+      </c>
+      <c r="H116" s="2" t="inlineStr">
+        <is>
+          <t>POST /space/analyze/rank</t>
+        </is>
+      </c>
+      <c r="I116" s="2" t="inlineStr">
+        <is>
+          <t>code=0</t>
+        </is>
+      </c>
+      <c r="J116" s="2" t="inlineStr"/>
+      <c r="K116" s="2" t="inlineStr"/>
+      <c r="L116" s="2" t="inlineStr">
+        <is>
+          <t>李坤纬</t>
+        </is>
+      </c>
+      <c r="M116" s="2" t="inlineStr"/>
+    </row>
+    <row r="117" ht="80" customHeight="1">
+      <c r="A117" s="2" t="inlineStr">
+        <is>
+          <t>TC-AR-002</t>
+        </is>
+      </c>
+      <c r="B117" s="2" t="inlineStr">
+        <is>
+          <t>内娱图库StarPicture</t>
+        </is>
+      </c>
+      <c r="C117" s="3" t="inlineStr">
+        <is>
+          <t>/空间排行</t>
+        </is>
+      </c>
+      <c r="D117" s="3" t="inlineStr">
+        <is>
+          <t>功能测试</t>
+        </is>
+      </c>
+      <c r="E117" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="F117" s="4" t="inlineStr">
+        <is>
+          <t>排行_未登录</t>
+        </is>
+      </c>
+      <c r="G117" s="2" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="H117" s="2" t="inlineStr">
+        <is>
+          <t>POST /space/analyze/rank</t>
+        </is>
+      </c>
+      <c r="I117" s="2" t="inlineStr">
+        <is>
+          <t>code=40100</t>
+        </is>
+      </c>
+      <c r="J117" s="2" t="inlineStr"/>
+      <c r="K117" s="2" t="inlineStr"/>
+      <c r="L117" s="2" t="inlineStr">
+        <is>
+          <t>李坤纬</t>
+        </is>
+      </c>
+      <c r="M117" s="2" t="inlineStr"/>
+    </row>
+    <row r="118" ht="80" customHeight="1">
+      <c r="A118" s="2" t="inlineStr">
+        <is>
+          <t>TC-PERF-001</t>
+        </is>
+      </c>
+      <c r="B118" s="2" t="inlineStr">
+        <is>
+          <t>内娱图库StarPicture</t>
+        </is>
+      </c>
+      <c r="C118" s="3" t="inlineStr">
+        <is>
+          <t>/空间分析</t>
+        </is>
+      </c>
+      <c r="D118" s="3" t="inlineStr">
+        <is>
+          <t>性能测试</t>
+        </is>
+      </c>
+      <c r="E118" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="F118" s="4" t="inlineStr">
+        <is>
+          <t>用量分析_20并发</t>
+        </is>
+      </c>
+      <c r="G118" s="2" t="inlineStr">
+        <is>
+          <t>JMeter</t>
+        </is>
+      </c>
+      <c r="H118" s="2" t="inlineStr">
+        <is>
+          <t>20线程 POST /space/analyze/usage</t>
+        </is>
+      </c>
+      <c r="I118" s="2" t="inlineStr">
+        <is>
+          <t>P95&lt;1s</t>
+        </is>
+      </c>
+      <c r="J118" s="2" t="inlineStr"/>
+      <c r="K118" s="2" t="inlineStr"/>
+      <c r="L118" s="2" t="inlineStr">
+        <is>
+          <t>李坤纬</t>
+        </is>
+      </c>
+      <c r="M118" s="2" t="inlineStr"/>
+    </row>
+    <row r="119" ht="80" customHeight="1">
+      <c r="A119" s="2" t="inlineStr">
+        <is>
+          <t>TC-PERF-002</t>
+        </is>
+      </c>
+      <c r="B119" s="2" t="inlineStr">
+        <is>
+          <t>内娱图库StarPicture</t>
+        </is>
+      </c>
+      <c r="C119" s="3" t="inlineStr">
+        <is>
+          <t>/空间列表</t>
+        </is>
+      </c>
+      <c r="D119" s="3" t="inlineStr">
+        <is>
+          <t>性能测试</t>
+        </is>
+      </c>
+      <c r="E119" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="F119" s="4" t="inlineStr">
+        <is>
+          <t>空间列表_50并发</t>
+        </is>
+      </c>
+      <c r="G119" s="2" t="inlineStr">
+        <is>
+          <t>JMeter</t>
+        </is>
+      </c>
+      <c r="H119" s="2" t="inlineStr">
+        <is>
+          <t>50线程 POST /space/list/page/vo</t>
+        </is>
+      </c>
+      <c r="I119" s="2" t="inlineStr">
+        <is>
+          <t>P95&lt;500ms</t>
+        </is>
+      </c>
+      <c r="J119" s="2" t="inlineStr"/>
+      <c r="K119" s="2" t="inlineStr"/>
+      <c r="L119" s="2" t="inlineStr">
+        <is>
+          <t>李坤纬</t>
+        </is>
+      </c>
+      <c r="M119" s="2" t="inlineStr"/>
+    </row>
+    <row r="120" ht="80" customHeight="1">
+      <c r="A120" s="2" t="inlineStr">
+        <is>
+          <t>TC-API-001</t>
+        </is>
+      </c>
+      <c r="B120" s="2" t="inlineStr">
+        <is>
+          <t>内娱图库StarPicture</t>
+        </is>
+      </c>
+      <c r="C120" s="3" t="inlineStr">
+        <is>
+          <t>/空间新增</t>
+        </is>
+      </c>
+      <c r="D120" s="3" t="inlineStr">
+        <is>
+          <t>接口测试</t>
+        </is>
+      </c>
+      <c r="E120" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="F120" s="4" t="inlineStr">
+        <is>
+          <t>新增_缺Content-Type</t>
+        </is>
+      </c>
+      <c r="G120" s="2" t="inlineStr">
+        <is>
+          <t>testuser01</t>
+        </is>
+      </c>
+      <c r="H120" s="2" t="inlineStr">
+        <is>
+          <t>不设置Content-Type</t>
+        </is>
+      </c>
+      <c r="I120" s="2" t="inlineStr">
+        <is>
+          <t>415</t>
+        </is>
+      </c>
+      <c r="J120" s="2" t="inlineStr"/>
+      <c r="K120" s="2" t="inlineStr"/>
+      <c r="L120" s="2" t="inlineStr">
+        <is>
+          <t>李坤纬</t>
+        </is>
+      </c>
+      <c r="M120" s="2" t="inlineStr"/>
+    </row>
+    <row r="121" ht="80" customHeight="1">
+      <c r="A121" s="2" t="inlineStr">
+        <is>
+          <t>TC-API-002</t>
+        </is>
+      </c>
+      <c r="B121" s="2" t="inlineStr">
+        <is>
+          <t>内娱图库StarPicture</t>
+        </is>
+      </c>
+      <c r="C121" s="3" t="inlineStr">
+        <is>
+          <t>/成员添加</t>
+        </is>
+      </c>
+      <c r="D121" s="3" t="inlineStr">
+        <is>
+          <t>接口测试</t>
+        </is>
+      </c>
+      <c r="E121" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="F121" s="4" t="inlineStr">
+        <is>
+          <t>添加_缺userId</t>
+        </is>
+      </c>
+      <c r="G121" s="2" t="inlineStr">
+        <is>
+          <t>admin</t>
+        </is>
+      </c>
+      <c r="H121" s="2" t="inlineStr">
+        <is>
+          <t>无userId字段</t>
+        </is>
+      </c>
+      <c r="I121" s="2" t="inlineStr">
+        <is>
+          <t>40001</t>
+        </is>
+      </c>
+      <c r="J121" s="2" t="inlineStr"/>
+      <c r="K121" s="2" t="inlineStr"/>
+      <c r="L121" s="2" t="inlineStr">
+        <is>
+          <t>李坤纬</t>
+        </is>
+      </c>
+      <c r="M121" s="2" t="inlineStr"/>
+    </row>
+    <row r="122" ht="80" customHeight="1">
+      <c r="A122" s="2" t="inlineStr">
+        <is>
+          <t>TC-SEC-001</t>
+        </is>
+      </c>
+      <c r="B122" s="2" t="inlineStr">
+        <is>
+          <t>内娱图库StarPicture</t>
+        </is>
+      </c>
+      <c r="C122" s="3" t="inlineStr">
+        <is>
+          <t>/空间管理</t>
+        </is>
+      </c>
+      <c r="D122" s="3" t="inlineStr">
+        <is>
+          <t>安全测试</t>
+        </is>
+      </c>
+      <c r="E122" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="F122" s="4" t="inlineStr">
+        <is>
+          <t>空间名称XSS</t>
+        </is>
+      </c>
+      <c r="G122" s="2" t="inlineStr">
+        <is>
+          <t>testuser01</t>
+        </is>
+      </c>
+      <c r="H122" s="2" t="inlineStr">
+        <is>
+          <t>spaceName='&lt;script&gt;alert(1)&lt;/script&gt;'</t>
+        </is>
+      </c>
+      <c r="I122" s="2" t="inlineStr">
+        <is>
+          <t>code=0, 转义</t>
+        </is>
+      </c>
+      <c r="J122" s="2" t="inlineStr"/>
+      <c r="K122" s="2" t="inlineStr"/>
+      <c r="L122" s="2" t="inlineStr">
+        <is>
+          <t>李坤纬</t>
+        </is>
+      </c>
+      <c r="M122" s="2" t="inlineStr"/>
+    </row>
+    <row r="123" ht="80" customHeight="1">
+      <c r="A123" s="2" t="inlineStr">
+        <is>
           <t>TC-SEC-002</t>
         </is>
       </c>
-      <c r="B114" s="2" t="inlineStr">
-        <is>
-          <t>内娱图库StarPicture</t>
-        </is>
-      </c>
-      <c r="C114" s="3" t="inlineStr">
+      <c r="B123" s="2" t="inlineStr">
+        <is>
+          <t>内娱图库StarPicture</t>
+        </is>
+      </c>
+      <c r="C123" s="3" t="inlineStr">
+        <is>
+          <t>/成员管理</t>
+        </is>
+      </c>
+      <c r="D123" s="3" t="inlineStr">
+        <is>
+          <t>安全测试</t>
+        </is>
+      </c>
+      <c r="E123" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="F123" s="4" t="inlineStr">
+        <is>
+          <t>跨用户添加成员</t>
+        </is>
+      </c>
+      <c r="G123" s="2" t="inlineStr">
+        <is>
+          <t>testuser02</t>
+        </is>
+      </c>
+      <c r="H123" s="2" t="inlineStr">
+        <is>
+          <t>POST /spaceUser/add spaceId=别人空间</t>
+        </is>
+      </c>
+      <c r="I123" s="2" t="inlineStr">
+        <is>
+          <t>code=40300</t>
+        </is>
+      </c>
+      <c r="J123" s="2" t="inlineStr"/>
+      <c r="K123" s="2" t="inlineStr"/>
+      <c r="L123" s="2" t="inlineStr">
+        <is>
+          <t>李坤纬</t>
+        </is>
+      </c>
+      <c r="M123" s="2" t="inlineStr"/>
+    </row>
+    <row r="124" ht="80" customHeight="1">
+      <c r="A124" s="2" t="inlineStr">
+        <is>
+          <t>TC-TU-001</t>
+        </is>
+      </c>
+      <c r="B124" s="2" t="inlineStr">
+        <is>
+          <t>内娱图库StarPicture</t>
+        </is>
+      </c>
+      <c r="C124" s="3" t="inlineStr">
+        <is>
+          <t>/文件上传</t>
+        </is>
+      </c>
+      <c r="D124" s="3" t="inlineStr">
+        <is>
+          <t>功能测试</t>
+        </is>
+      </c>
+      <c r="E124" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="F124" s="4" t="inlineStr">
+        <is>
+          <t>测试上传_正常jpg</t>
+        </is>
+      </c>
+      <c r="G124" s="2" t="inlineStr">
+        <is>
+          <t>testuser01</t>
+        </is>
+      </c>
+      <c r="H124" s="2" t="inlineStr">
+        <is>
+          <t>POST /file/test/upload file=1MB_jpg</t>
+        </is>
+      </c>
+      <c r="I124" s="2" t="inlineStr">
+        <is>
+          <t>code=0</t>
+        </is>
+      </c>
+      <c r="J124" s="2" t="inlineStr"/>
+      <c r="K124" s="2" t="inlineStr"/>
+      <c r="L124" s="2" t="inlineStr">
+        <is>
+          <t>林景彬</t>
+        </is>
+      </c>
+      <c r="M124" s="2" t="inlineStr"/>
+    </row>
+    <row r="125" ht="80" customHeight="1">
+      <c r="A125" s="2" t="inlineStr">
+        <is>
+          <t>TC-TU-002</t>
+        </is>
+      </c>
+      <c r="B125" s="2" t="inlineStr">
+        <is>
+          <t>内娱图库StarPicture</t>
+        </is>
+      </c>
+      <c r="C125" s="3" t="inlineStr">
+        <is>
+          <t>/文件上传</t>
+        </is>
+      </c>
+      <c r="D125" s="3" t="inlineStr">
+        <is>
+          <t>功能测试</t>
+        </is>
+      </c>
+      <c r="E125" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="F125" s="4" t="inlineStr">
+        <is>
+          <t>测试上传_空文件</t>
+        </is>
+      </c>
+      <c r="G125" s="2" t="inlineStr">
+        <is>
+          <t>testuser01</t>
+        </is>
+      </c>
+      <c r="H125" s="2" t="inlineStr">
+        <is>
+          <t>file=0byte</t>
+        </is>
+      </c>
+      <c r="I125" s="2" t="inlineStr">
+        <is>
+          <t>code=40001</t>
+        </is>
+      </c>
+      <c r="J125" s="2" t="inlineStr"/>
+      <c r="K125" s="2" t="inlineStr"/>
+      <c r="L125" s="2" t="inlineStr">
+        <is>
+          <t>林景彬</t>
+        </is>
+      </c>
+      <c r="M125" s="2" t="inlineStr"/>
+    </row>
+    <row r="126" ht="80" customHeight="1">
+      <c r="A126" s="2" t="inlineStr">
+        <is>
+          <t>TC-TU-003</t>
+        </is>
+      </c>
+      <c r="B126" s="2" t="inlineStr">
+        <is>
+          <t>内娱图库StarPicture</t>
+        </is>
+      </c>
+      <c r="C126" s="3" t="inlineStr">
+        <is>
+          <t>/文件上传</t>
+        </is>
+      </c>
+      <c r="D126" s="3" t="inlineStr">
+        <is>
+          <t>功能测试</t>
+        </is>
+      </c>
+      <c r="E126" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="F126" s="4" t="inlineStr">
+        <is>
+          <t>测试上传_非图片</t>
+        </is>
+      </c>
+      <c r="G126" s="2" t="inlineStr">
+        <is>
+          <t>testuser01</t>
+        </is>
+      </c>
+      <c r="H126" s="2" t="inlineStr">
+        <is>
+          <t>file=test.pdf</t>
+        </is>
+      </c>
+      <c r="I126" s="2" t="inlineStr">
+        <is>
+          <t>code=40001</t>
+        </is>
+      </c>
+      <c r="J126" s="2" t="inlineStr"/>
+      <c r="K126" s="2" t="inlineStr"/>
+      <c r="L126" s="2" t="inlineStr">
+        <is>
+          <t>林景彬</t>
+        </is>
+      </c>
+      <c r="M126" s="2" t="inlineStr"/>
+    </row>
+    <row r="127" ht="80" customHeight="1">
+      <c r="A127" s="2" t="inlineStr">
+        <is>
+          <t>TC-FU-001</t>
+        </is>
+      </c>
+      <c r="B127" s="2" t="inlineStr">
+        <is>
+          <t>内娱图库StarPicture</t>
+        </is>
+      </c>
+      <c r="C127" s="3" t="inlineStr">
+        <is>
+          <t>/文件上传</t>
+        </is>
+      </c>
+      <c r="D127" s="3" t="inlineStr">
+        <is>
+          <t>功能测试</t>
+        </is>
+      </c>
+      <c r="E127" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="F127" s="4" t="inlineStr">
+        <is>
+          <t>上传_正常png</t>
+        </is>
+      </c>
+      <c r="G127" s="2" t="inlineStr">
+        <is>
+          <t>testuser01</t>
+        </is>
+      </c>
+      <c r="H127" s="2" t="inlineStr">
+        <is>
+          <t>POST /file/upload file=1MB_png</t>
+        </is>
+      </c>
+      <c r="I127" s="2" t="inlineStr">
+        <is>
+          <t>code=0</t>
+        </is>
+      </c>
+      <c r="J127" s="2" t="inlineStr"/>
+      <c r="K127" s="2" t="inlineStr"/>
+      <c r="L127" s="2" t="inlineStr">
+        <is>
+          <t>林景彬</t>
+        </is>
+      </c>
+      <c r="M127" s="2" t="inlineStr"/>
+    </row>
+    <row r="128" ht="80" customHeight="1">
+      <c r="A128" s="2" t="inlineStr">
+        <is>
+          <t>TC-FU-002</t>
+        </is>
+      </c>
+      <c r="B128" s="2" t="inlineStr">
+        <is>
+          <t>内娱图库StarPicture</t>
+        </is>
+      </c>
+      <c r="C128" s="3" t="inlineStr">
+        <is>
+          <t>/文件上传</t>
+        </is>
+      </c>
+      <c r="D128" s="3" t="inlineStr">
+        <is>
+          <t>功能测试</t>
+        </is>
+      </c>
+      <c r="E128" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="F128" s="4" t="inlineStr">
+        <is>
+          <t>上传_超过2MB</t>
+        </is>
+      </c>
+      <c r="G128" s="2" t="inlineStr">
+        <is>
+          <t>testuser01</t>
+        </is>
+      </c>
+      <c r="H128" s="2" t="inlineStr">
+        <is>
+          <t>file=5MB_jpg</t>
+        </is>
+      </c>
+      <c r="I128" s="2" t="inlineStr">
+        <is>
+          <t>code=40001</t>
+        </is>
+      </c>
+      <c r="J128" s="2" t="inlineStr"/>
+      <c r="K128" s="2" t="inlineStr"/>
+      <c r="L128" s="2" t="inlineStr">
+        <is>
+          <t>林景彬</t>
+        </is>
+      </c>
+      <c r="M128" s="2" t="inlineStr"/>
+    </row>
+    <row r="129" ht="80" customHeight="1">
+      <c r="A129" s="2" t="inlineStr">
+        <is>
+          <t>TC-FU-003</t>
+        </is>
+      </c>
+      <c r="B129" s="2" t="inlineStr">
+        <is>
+          <t>内娱图库StarPicture</t>
+        </is>
+      </c>
+      <c r="C129" s="3" t="inlineStr">
+        <is>
+          <t>/文件上传</t>
+        </is>
+      </c>
+      <c r="D129" s="3" t="inlineStr">
+        <is>
+          <t>功能测试</t>
+        </is>
+      </c>
+      <c r="E129" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="F129" s="4" t="inlineStr">
+        <is>
+          <t>上传_未登录</t>
+        </is>
+      </c>
+      <c r="G129" s="2" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="H129" s="2" t="inlineStr">
+        <is>
+          <t>POST /file/upload</t>
+        </is>
+      </c>
+      <c r="I129" s="2" t="inlineStr">
+        <is>
+          <t>code=40100</t>
+        </is>
+      </c>
+      <c r="J129" s="2" t="inlineStr"/>
+      <c r="K129" s="2" t="inlineStr"/>
+      <c r="L129" s="2" t="inlineStr">
+        <is>
+          <t>林景彬</t>
+        </is>
+      </c>
+      <c r="M129" s="2" t="inlineStr"/>
+    </row>
+    <row r="130" ht="80" customHeight="1">
+      <c r="A130" s="2" t="inlineStr">
+        <is>
+          <t>TC-AU-001</t>
+        </is>
+      </c>
+      <c r="B130" s="2" t="inlineStr">
+        <is>
+          <t>内娱图库StarPicture</t>
+        </is>
+      </c>
+      <c r="C130" s="3" t="inlineStr">
         <is>
           <t>/头像上传</t>
         </is>
       </c>
-      <c r="D114" s="3" t="inlineStr">
+      <c r="D130" s="3" t="inlineStr">
+        <is>
+          <t>功能测试</t>
+        </is>
+      </c>
+      <c r="E130" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="F130" s="4" t="inlineStr">
+        <is>
+          <t>头像_正常</t>
+        </is>
+      </c>
+      <c r="G130" s="2" t="inlineStr">
+        <is>
+          <t>testuser01</t>
+        </is>
+      </c>
+      <c r="H130" s="2" t="inlineStr">
+        <is>
+          <t>POST /file/upload/avatar file=300KB_jpg</t>
+        </is>
+      </c>
+      <c r="I130" s="2" t="inlineStr">
+        <is>
+          <t>code=0, userAvatar更新</t>
+        </is>
+      </c>
+      <c r="J130" s="2" t="inlineStr"/>
+      <c r="K130" s="2" t="inlineStr"/>
+      <c r="L130" s="2" t="inlineStr">
+        <is>
+          <t>林景彬</t>
+        </is>
+      </c>
+      <c r="M130" s="2" t="inlineStr"/>
+    </row>
+    <row r="131" ht="80" customHeight="1">
+      <c r="A131" s="2" t="inlineStr">
+        <is>
+          <t>TC-AU-002</t>
+        </is>
+      </c>
+      <c r="B131" s="2" t="inlineStr">
+        <is>
+          <t>内娱图库StarPicture</t>
+        </is>
+      </c>
+      <c r="C131" s="3" t="inlineStr">
+        <is>
+          <t>/头像上传</t>
+        </is>
+      </c>
+      <c r="D131" s="3" t="inlineStr">
+        <is>
+          <t>功能测试</t>
+        </is>
+      </c>
+      <c r="E131" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="F131" s="4" t="inlineStr">
+        <is>
+          <t>头像_超过1MB</t>
+        </is>
+      </c>
+      <c r="G131" s="2" t="inlineStr">
+        <is>
+          <t>testuser01</t>
+        </is>
+      </c>
+      <c r="H131" s="2" t="inlineStr">
+        <is>
+          <t>file=1.5MB</t>
+        </is>
+      </c>
+      <c r="I131" s="2" t="inlineStr">
+        <is>
+          <t>code=40001</t>
+        </is>
+      </c>
+      <c r="J131" s="2" t="inlineStr"/>
+      <c r="K131" s="2" t="inlineStr"/>
+      <c r="L131" s="2" t="inlineStr">
+        <is>
+          <t>林景彬</t>
+        </is>
+      </c>
+      <c r="M131" s="2" t="inlineStr"/>
+    </row>
+    <row r="132" ht="80" customHeight="1">
+      <c r="A132" s="2" t="inlineStr">
+        <is>
+          <t>TC-AU-003</t>
+        </is>
+      </c>
+      <c r="B132" s="2" t="inlineStr">
+        <is>
+          <t>内娱图库StarPicture</t>
+        </is>
+      </c>
+      <c r="C132" s="3" t="inlineStr">
+        <is>
+          <t>/头像上传</t>
+        </is>
+      </c>
+      <c r="D132" s="3" t="inlineStr">
+        <is>
+          <t>功能测试</t>
+        </is>
+      </c>
+      <c r="E132" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="F132" s="4" t="inlineStr">
+        <is>
+          <t>头像_非图片</t>
+        </is>
+      </c>
+      <c r="G132" s="2" t="inlineStr">
+        <is>
+          <t>testuser01</t>
+        </is>
+      </c>
+      <c r="H132" s="2" t="inlineStr">
+        <is>
+          <t>file=test.pdf</t>
+        </is>
+      </c>
+      <c r="I132" s="2" t="inlineStr">
+        <is>
+          <t>code=40001</t>
+        </is>
+      </c>
+      <c r="J132" s="2" t="inlineStr"/>
+      <c r="K132" s="2" t="inlineStr"/>
+      <c r="L132" s="2" t="inlineStr">
+        <is>
+          <t>林景彬</t>
+        </is>
+      </c>
+      <c r="M132" s="2" t="inlineStr"/>
+    </row>
+    <row r="133" ht="80" customHeight="1">
+      <c r="A133" s="2" t="inlineStr">
+        <is>
+          <t>TC-WG-001</t>
+        </is>
+      </c>
+      <c r="B133" s="2" t="inlineStr">
+        <is>
+          <t>内娱图库StarPicture</t>
+        </is>
+      </c>
+      <c r="C133" s="3" t="inlineStr">
+        <is>
+          <t>/微信门户</t>
+        </is>
+      </c>
+      <c r="D133" s="3" t="inlineStr">
+        <is>
+          <t>功能测试</t>
+        </is>
+      </c>
+      <c r="E133" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="F133" s="4" t="inlineStr">
+        <is>
+          <t>门户_GET_签名验证</t>
+        </is>
+      </c>
+      <c r="G133" s="2" t="inlineStr">
+        <is>
+          <t>微信GET</t>
+        </is>
+      </c>
+      <c r="H133" s="2" t="inlineStr">
+        <is>
+          <t>GET /wx/mp/portal signature=xxx timestamp=xxx nonce=xxx echostr=test</t>
+        </is>
+      </c>
+      <c r="I133" s="2" t="inlineStr">
+        <is>
+          <t>返回echostr</t>
+        </is>
+      </c>
+      <c r="J133" s="2" t="inlineStr"/>
+      <c r="K133" s="2" t="inlineStr"/>
+      <c r="L133" s="2" t="inlineStr">
+        <is>
+          <t>林景彬</t>
+        </is>
+      </c>
+      <c r="M133" s="2" t="inlineStr"/>
+    </row>
+    <row r="134" ht="80" customHeight="1">
+      <c r="A134" s="2" t="inlineStr">
+        <is>
+          <t>TC-WG-002</t>
+        </is>
+      </c>
+      <c r="B134" s="2" t="inlineStr">
+        <is>
+          <t>内娱图库StarPicture</t>
+        </is>
+      </c>
+      <c r="C134" s="3" t="inlineStr">
+        <is>
+          <t>/微信门户</t>
+        </is>
+      </c>
+      <c r="D134" s="3" t="inlineStr">
+        <is>
+          <t>功能测试</t>
+        </is>
+      </c>
+      <c r="E134" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="F134" s="4" t="inlineStr">
+        <is>
+          <t>门户_GET_签名错误</t>
+        </is>
+      </c>
+      <c r="G134" s="2" t="inlineStr">
+        <is>
+          <t>微信GET</t>
+        </is>
+      </c>
+      <c r="H134" s="2" t="inlineStr">
+        <is>
+          <t>signature=invalid</t>
+        </is>
+      </c>
+      <c r="I134" s="2" t="inlineStr">
+        <is>
+          <t>返回空或错误</t>
+        </is>
+      </c>
+      <c r="J134" s="2" t="inlineStr"/>
+      <c r="K134" s="2" t="inlineStr"/>
+      <c r="L134" s="2" t="inlineStr">
+        <is>
+          <t>林景彬</t>
+        </is>
+      </c>
+      <c r="M134" s="2" t="inlineStr"/>
+    </row>
+    <row r="135" ht="80" customHeight="1">
+      <c r="A135" s="2" t="inlineStr">
+        <is>
+          <t>TC-WG-003</t>
+        </is>
+      </c>
+      <c r="B135" s="2" t="inlineStr">
+        <is>
+          <t>内娱图库StarPicture</t>
+        </is>
+      </c>
+      <c r="C135" s="3" t="inlineStr">
+        <is>
+          <t>/微信门户</t>
+        </is>
+      </c>
+      <c r="D135" s="3" t="inlineStr">
+        <is>
+          <t>功能测试</t>
+        </is>
+      </c>
+      <c r="E135" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="F135" s="4" t="inlineStr">
+        <is>
+          <t>门户_GET_缺参数</t>
+        </is>
+      </c>
+      <c r="G135" s="2" t="inlineStr">
+        <is>
+          <t>微信GET</t>
+        </is>
+      </c>
+      <c r="H135" s="2" t="inlineStr">
+        <is>
+          <t>无signature参数</t>
+        </is>
+      </c>
+      <c r="I135" s="2" t="inlineStr">
+        <is>
+          <t>返回错误</t>
+        </is>
+      </c>
+      <c r="J135" s="2" t="inlineStr"/>
+      <c r="K135" s="2" t="inlineStr"/>
+      <c r="L135" s="2" t="inlineStr">
+        <is>
+          <t>林景彬</t>
+        </is>
+      </c>
+      <c r="M135" s="2" t="inlineStr"/>
+    </row>
+    <row r="136" ht="80" customHeight="1">
+      <c r="A136" s="2" t="inlineStr">
+        <is>
+          <t>TC-WP-001</t>
+        </is>
+      </c>
+      <c r="B136" s="2" t="inlineStr">
+        <is>
+          <t>内娱图库StarPicture</t>
+        </is>
+      </c>
+      <c r="C136" s="3" t="inlineStr">
+        <is>
+          <t>/微信门户</t>
+        </is>
+      </c>
+      <c r="D136" s="3" t="inlineStr">
+        <is>
+          <t>功能测试</t>
+        </is>
+      </c>
+      <c r="E136" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="F136" s="4" t="inlineStr">
+        <is>
+          <t>门户_POST_正常文本</t>
+        </is>
+      </c>
+      <c r="G136" s="2" t="inlineStr">
+        <is>
+          <t>微信POST</t>
+        </is>
+      </c>
+      <c r="H136" s="2" t="inlineStr">
+        <is>
+          <t>POST /wx/mp/portal body=&lt;xml&gt;...</t>
+        </is>
+      </c>
+      <c r="I136" s="2" t="inlineStr">
+        <is>
+          <t>code=0, 响应XML</t>
+        </is>
+      </c>
+      <c r="J136" s="2" t="inlineStr"/>
+      <c r="K136" s="2" t="inlineStr"/>
+      <c r="L136" s="2" t="inlineStr">
+        <is>
+          <t>林景彬</t>
+        </is>
+      </c>
+      <c r="M136" s="2" t="inlineStr"/>
+    </row>
+    <row r="137" ht="80" customHeight="1">
+      <c r="A137" s="2" t="inlineStr">
+        <is>
+          <t>TC-WP-002</t>
+        </is>
+      </c>
+      <c r="B137" s="2" t="inlineStr">
+        <is>
+          <t>内娱图库StarPicture</t>
+        </is>
+      </c>
+      <c r="C137" s="3" t="inlineStr">
+        <is>
+          <t>/微信门户</t>
+        </is>
+      </c>
+      <c r="D137" s="3" t="inlineStr">
+        <is>
+          <t>功能测试</t>
+        </is>
+      </c>
+      <c r="E137" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="F137" s="4" t="inlineStr">
+        <is>
+          <t>门户_POST_空body</t>
+        </is>
+      </c>
+      <c r="G137" s="2" t="inlineStr">
+        <is>
+          <t>微信POST</t>
+        </is>
+      </c>
+      <c r="H137" s="2" t="inlineStr">
+        <is>
+          <t>body=空</t>
+        </is>
+      </c>
+      <c r="I137" s="2" t="inlineStr">
+        <is>
+          <t>返回错误XML</t>
+        </is>
+      </c>
+      <c r="J137" s="2" t="inlineStr"/>
+      <c r="K137" s="2" t="inlineStr"/>
+      <c r="L137" s="2" t="inlineStr">
+        <is>
+          <t>林景彬</t>
+        </is>
+      </c>
+      <c r="M137" s="2" t="inlineStr"/>
+    </row>
+    <row r="138" ht="80" customHeight="1">
+      <c r="A138" s="2" t="inlineStr">
+        <is>
+          <t>TC-WP-003</t>
+        </is>
+      </c>
+      <c r="B138" s="2" t="inlineStr">
+        <is>
+          <t>内娱图库StarPicture</t>
+        </is>
+      </c>
+      <c r="C138" s="3" t="inlineStr">
+        <is>
+          <t>/微信门户</t>
+        </is>
+      </c>
+      <c r="D138" s="3" t="inlineStr">
+        <is>
+          <t>功能测试</t>
+        </is>
+      </c>
+      <c r="E138" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="F138" s="4" t="inlineStr">
+        <is>
+          <t>门户_POST_格式错误</t>
+        </is>
+      </c>
+      <c r="G138" s="2" t="inlineStr">
+        <is>
+          <t>微信POST</t>
+        </is>
+      </c>
+      <c r="H138" s="2" t="inlineStr">
+        <is>
+          <t>body=非XML</t>
+        </is>
+      </c>
+      <c r="I138" s="2" t="inlineStr">
+        <is>
+          <t>返回错误</t>
+        </is>
+      </c>
+      <c r="J138" s="2" t="inlineStr"/>
+      <c r="K138" s="2" t="inlineStr"/>
+      <c r="L138" s="2" t="inlineStr">
+        <is>
+          <t>林景彬</t>
+        </is>
+      </c>
+      <c r="M138" s="2" t="inlineStr"/>
+    </row>
+    <row r="139" ht="80" customHeight="1">
+      <c r="A139" s="2" t="inlineStr">
+        <is>
+          <t>TC-MC-001</t>
+        </is>
+      </c>
+      <c r="B139" s="2" t="inlineStr">
+        <is>
+          <t>内娱图库StarPicture</t>
+        </is>
+      </c>
+      <c r="C139" s="3" t="inlineStr">
+        <is>
+          <t>/微信菜单</t>
+        </is>
+      </c>
+      <c r="D139" s="3" t="inlineStr">
+        <is>
+          <t>功能测试</t>
+        </is>
+      </c>
+      <c r="E139" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="F139" s="4" t="inlineStr">
+        <is>
+          <t>创建菜单_正常</t>
+        </is>
+      </c>
+      <c r="G139" s="2" t="inlineStr">
+        <is>
+          <t>admin</t>
+        </is>
+      </c>
+      <c r="H139" s="2" t="inlineStr">
+        <is>
+          <t>POST /wx/mp/menu/create menu={button:[...]}</t>
+        </is>
+      </c>
+      <c r="I139" s="2" t="inlineStr">
+        <is>
+          <t>code=0</t>
+        </is>
+      </c>
+      <c r="J139" s="2" t="inlineStr"/>
+      <c r="K139" s="2" t="inlineStr"/>
+      <c r="L139" s="2" t="inlineStr">
+        <is>
+          <t>林景彬</t>
+        </is>
+      </c>
+      <c r="M139" s="2" t="inlineStr"/>
+    </row>
+    <row r="140" ht="80" customHeight="1">
+      <c r="A140" s="2" t="inlineStr">
+        <is>
+          <t>TC-MC-002</t>
+        </is>
+      </c>
+      <c r="B140" s="2" t="inlineStr">
+        <is>
+          <t>内娱图库StarPicture</t>
+        </is>
+      </c>
+      <c r="C140" s="3" t="inlineStr">
+        <is>
+          <t>/微信菜单</t>
+        </is>
+      </c>
+      <c r="D140" s="3" t="inlineStr">
+        <is>
+          <t>功能测试</t>
+        </is>
+      </c>
+      <c r="E140" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="F140" s="4" t="inlineStr">
+        <is>
+          <t>创建菜单_空body</t>
+        </is>
+      </c>
+      <c r="G140" s="2" t="inlineStr">
+        <is>
+          <t>admin</t>
+        </is>
+      </c>
+      <c r="H140" s="2" t="inlineStr">
+        <is>
+          <t>body={}</t>
+        </is>
+      </c>
+      <c r="I140" s="2" t="inlineStr">
+        <is>
+          <t>code=40001</t>
+        </is>
+      </c>
+      <c r="J140" s="2" t="inlineStr"/>
+      <c r="K140" s="2" t="inlineStr"/>
+      <c r="L140" s="2" t="inlineStr">
+        <is>
+          <t>林景彬</t>
+        </is>
+      </c>
+      <c r="M140" s="2" t="inlineStr"/>
+    </row>
+    <row r="141" ht="80" customHeight="1">
+      <c r="A141" s="2" t="inlineStr">
+        <is>
+          <t>TC-MC-003</t>
+        </is>
+      </c>
+      <c r="B141" s="2" t="inlineStr">
+        <is>
+          <t>内娱图库StarPicture</t>
+        </is>
+      </c>
+      <c r="C141" s="3" t="inlineStr">
+        <is>
+          <t>/微信菜单</t>
+        </is>
+      </c>
+      <c r="D141" s="3" t="inlineStr">
+        <is>
+          <t>功能测试</t>
+        </is>
+      </c>
+      <c r="E141" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="F141" s="4" t="inlineStr">
+        <is>
+          <t>创建菜单_未登录</t>
+        </is>
+      </c>
+      <c r="G141" s="2" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="H141" s="2" t="inlineStr">
+        <is>
+          <t>POST /wx/mp/menu/create</t>
+        </is>
+      </c>
+      <c r="I141" s="2" t="inlineStr">
+        <is>
+          <t>code=40100</t>
+        </is>
+      </c>
+      <c r="J141" s="2" t="inlineStr"/>
+      <c r="K141" s="2" t="inlineStr"/>
+      <c r="L141" s="2" t="inlineStr">
+        <is>
+          <t>林景彬</t>
+        </is>
+      </c>
+      <c r="M141" s="2" t="inlineStr"/>
+    </row>
+    <row r="142" ht="80" customHeight="1">
+      <c r="A142" s="2" t="inlineStr">
+        <is>
+          <t>TC-PERF-001</t>
+        </is>
+      </c>
+      <c r="B142" s="2" t="inlineStr">
+        <is>
+          <t>内娱图库StarPicture</t>
+        </is>
+      </c>
+      <c r="C142" s="3" t="inlineStr">
+        <is>
+          <t>/文件上传</t>
+        </is>
+      </c>
+      <c r="D142" s="3" t="inlineStr">
+        <is>
+          <t>性能测试</t>
+        </is>
+      </c>
+      <c r="E142" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="F142" s="4" t="inlineStr">
+        <is>
+          <t>上传_50并发1MB</t>
+        </is>
+      </c>
+      <c r="G142" s="2" t="inlineStr">
+        <is>
+          <t>JMeter</t>
+        </is>
+      </c>
+      <c r="H142" s="2" t="inlineStr">
+        <is>
+          <t>50线程 POST /file/upload</t>
+        </is>
+      </c>
+      <c r="I142" s="2" t="inlineStr">
+        <is>
+          <t>P95&lt;2s</t>
+        </is>
+      </c>
+      <c r="J142" s="2" t="inlineStr"/>
+      <c r="K142" s="2" t="inlineStr"/>
+      <c r="L142" s="2" t="inlineStr">
+        <is>
+          <t>林景彬</t>
+        </is>
+      </c>
+      <c r="M142" s="2" t="inlineStr"/>
+    </row>
+    <row r="143" ht="80" customHeight="1">
+      <c r="A143" s="2" t="inlineStr">
+        <is>
+          <t>TC-PERF-002</t>
+        </is>
+      </c>
+      <c r="B143" s="2" t="inlineStr">
+        <is>
+          <t>内娱图库StarPicture</t>
+        </is>
+      </c>
+      <c r="C143" s="3" t="inlineStr">
+        <is>
+          <t>/头像上传</t>
+        </is>
+      </c>
+      <c r="D143" s="3" t="inlineStr">
+        <is>
+          <t>性能测试</t>
+        </is>
+      </c>
+      <c r="E143" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="F143" s="4" t="inlineStr">
+        <is>
+          <t>头像_100并发</t>
+        </is>
+      </c>
+      <c r="G143" s="2" t="inlineStr">
+        <is>
+          <t>JMeter</t>
+        </is>
+      </c>
+      <c r="H143" s="2" t="inlineStr">
+        <is>
+          <t>100线程 POST /file/upload/avatar</t>
+        </is>
+      </c>
+      <c r="I143" s="2" t="inlineStr">
+        <is>
+          <t>P95&lt;3s</t>
+        </is>
+      </c>
+      <c r="J143" s="2" t="inlineStr"/>
+      <c r="K143" s="2" t="inlineStr"/>
+      <c r="L143" s="2" t="inlineStr">
+        <is>
+          <t>林景彬</t>
+        </is>
+      </c>
+      <c r="M143" s="2" t="inlineStr"/>
+    </row>
+    <row r="144" ht="80" customHeight="1">
+      <c r="A144" s="2" t="inlineStr">
+        <is>
+          <t>TC-API-001</t>
+        </is>
+      </c>
+      <c r="B144" s="2" t="inlineStr">
+        <is>
+          <t>内娱图库StarPicture</t>
+        </is>
+      </c>
+      <c r="C144" s="3" t="inlineStr">
+        <is>
+          <t>/文件上传</t>
+        </is>
+      </c>
+      <c r="D144" s="3" t="inlineStr">
+        <is>
+          <t>接口测试</t>
+        </is>
+      </c>
+      <c r="E144" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="F144" s="4" t="inlineStr">
+        <is>
+          <t>上传_缺multipart边界</t>
+        </is>
+      </c>
+      <c r="G144" s="2" t="inlineStr">
+        <is>
+          <t>testuser01</t>
+        </is>
+      </c>
+      <c r="H144" s="2" t="inlineStr">
+        <is>
+          <t>不完整multipart</t>
+        </is>
+      </c>
+      <c r="I144" s="2" t="inlineStr">
+        <is>
+          <t>400/415</t>
+        </is>
+      </c>
+      <c r="J144" s="2" t="inlineStr"/>
+      <c r="K144" s="2" t="inlineStr"/>
+      <c r="L144" s="2" t="inlineStr">
+        <is>
+          <t>林景彬</t>
+        </is>
+      </c>
+      <c r="M144" s="2" t="inlineStr"/>
+    </row>
+    <row r="145" ht="80" customHeight="1">
+      <c r="A145" s="2" t="inlineStr">
+        <is>
+          <t>TC-SEC-001</t>
+        </is>
+      </c>
+      <c r="B145" s="2" t="inlineStr">
+        <is>
+          <t>内娱图库StarPicture</t>
+        </is>
+      </c>
+      <c r="C145" s="3" t="inlineStr">
+        <is>
+          <t>/文件上传</t>
+        </is>
+      </c>
+      <c r="D145" s="3" t="inlineStr">
         <is>
           <t>安全测试</t>
         </is>
       </c>
-      <c r="E114" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="F114" s="4" t="inlineStr">
-        <is>
-          <t>头像_伪SVG含JS</t>
-        </is>
-      </c>
-      <c r="G114" s="2" t="inlineStr">
-        <is>
-          <t>testuser01 已登录</t>
-        </is>
-      </c>
-      <c r="H114" s="2" t="inlineStr">
-        <is>
-          <t>1. file=avatar.svg 内容含 &lt;script&gt;alert(1)&lt;/script&gt;</t>
-        </is>
-      </c>
-      <c r="I114" s="2" t="inlineStr">
-        <is>
-          <t>返回code=40001 拒绝SVG</t>
-        </is>
-      </c>
-      <c r="J114" s="2" t="n"/>
-      <c r="K114" s="2" t="n"/>
-      <c r="L114" s="2" t="inlineStr">
+      <c r="E145" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="F145" s="4" t="inlineStr">
+        <is>
+          <t>上传_伪PHP木马</t>
+        </is>
+      </c>
+      <c r="G145" s="2" t="inlineStr">
+        <is>
+          <t>testuser01</t>
+        </is>
+      </c>
+      <c r="H145" s="2" t="inlineStr">
+        <is>
+          <t>file=1.jpg内容为&lt;?php...?&gt;</t>
+        </is>
+      </c>
+      <c r="I145" s="2" t="inlineStr">
+        <is>
+          <t>code=40001</t>
+        </is>
+      </c>
+      <c r="J145" s="2" t="inlineStr"/>
+      <c r="K145" s="2" t="inlineStr"/>
+      <c r="L145" s="2" t="inlineStr">
         <is>
           <t>林景彬</t>
         </is>
       </c>
-      <c r="M114" s="2" t="n"/>
+      <c r="M145" s="2" t="inlineStr"/>
+    </row>
+    <row r="146" ht="80" customHeight="1">
+      <c r="A146" s="2" t="inlineStr">
+        <is>
+          <t>TC-SEC-002</t>
+        </is>
+      </c>
+      <c r="B146" s="2" t="inlineStr">
+        <is>
+          <t>内娱图库StarPicture</t>
+        </is>
+      </c>
+      <c r="C146" s="3" t="inlineStr">
+        <is>
+          <t>/头像上传</t>
+        </is>
+      </c>
+      <c r="D146" s="3" t="inlineStr">
+        <is>
+          <t>安全测试</t>
+        </is>
+      </c>
+      <c r="E146" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="F146" s="4" t="inlineStr">
+        <is>
+          <t>头像_双扩展名绕过</t>
+        </is>
+      </c>
+      <c r="G146" s="2" t="inlineStr">
+        <is>
+          <t>testuser01</t>
+        </is>
+      </c>
+      <c r="H146" s="2" t="inlineStr">
+        <is>
+          <t>file=1.jpg.php</t>
+        </is>
+      </c>
+      <c r="I146" s="2" t="inlineStr">
+        <is>
+          <t>code=40001</t>
+        </is>
+      </c>
+      <c r="J146" s="2" t="inlineStr"/>
+      <c r="K146" s="2" t="inlineStr"/>
+      <c r="L146" s="2" t="inlineStr">
+        <is>
+          <t>林景彬</t>
+        </is>
+      </c>
+      <c r="M146" s="2" t="inlineStr"/>
+    </row>
+    <row r="147" ht="80" customHeight="1">
+      <c r="A147" s="2" t="inlineStr">
+        <is>
+          <t>TC-SEC-003</t>
+        </is>
+      </c>
+      <c r="B147" s="2" t="inlineStr">
+        <is>
+          <t>内娱图库StarPicture</t>
+        </is>
+      </c>
+      <c r="C147" s="3" t="inlineStr">
+        <is>
+          <t>/头像上传</t>
+        </is>
+      </c>
+      <c r="D147" s="3" t="inlineStr">
+        <is>
+          <t>安全测试</t>
+        </is>
+      </c>
+      <c r="E147" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="F147" s="4" t="inlineStr">
+        <is>
+          <t>头像_越权修改别人</t>
+        </is>
+      </c>
+      <c r="G147" s="2" t="inlineStr">
+        <is>
+          <t>testuser02</t>
+        </is>
+      </c>
+      <c r="H147" s="2" t="inlineStr">
+        <is>
+          <t>POST /file/upload/avatar userId=别人</t>
+        </is>
+      </c>
+      <c r="I147" s="2" t="inlineStr">
+        <is>
+          <t>只改本人</t>
+        </is>
+      </c>
+      <c r="J147" s="2" t="inlineStr"/>
+      <c r="K147" s="2" t="inlineStr"/>
+      <c r="L147" s="2" t="inlineStr">
+        <is>
+          <t>林景彬</t>
+        </is>
+      </c>
+      <c r="M147" s="2" t="inlineStr"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:M114"/>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:B14"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="20" customWidth="1" min="1" max="1"/>
-    <col width="12" customWidth="1" min="2" max="2"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="5" t="inlineStr">
-        <is>
-          <t>项目</t>
-        </is>
-      </c>
-      <c r="B1" s="5" t="inlineStr">
-        <is>
-          <t>数据</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="3" t="n"/>
-      <c r="B2" s="3" t="n"/>
-    </row>
-    <row r="3">
-      <c r="A3" s="3" t="inlineStr">
-        <is>
-          <t>按人员</t>
-        </is>
-      </c>
-      <c r="B3" s="3" t="inlineStr">
-        <is>
-          <t>用例数</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="3" t="inlineStr">
-        <is>
-          <t>朱远亮</t>
-        </is>
-      </c>
-      <c r="B4" s="3" t="n">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="3" t="inlineStr">
-        <is>
-          <t>李冠燃</t>
-        </is>
-      </c>
-      <c r="B5" s="3" t="n">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="3" t="inlineStr">
-        <is>
-          <t>李坤纬</t>
-        </is>
-      </c>
-      <c r="B6" s="3" t="n">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="3" t="inlineStr">
-        <is>
-          <t>林景彬</t>
-        </is>
-      </c>
-      <c r="B7" s="3" t="n">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="3" t="inlineStr">
-        <is>
-          <t>合计</t>
-        </is>
-      </c>
-      <c r="B8" s="3" t="n">
-        <v>113</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="3" t="n"/>
-      <c r="B9" s="3" t="n"/>
-    </row>
-    <row r="10">
-      <c r="A10" s="3" t="inlineStr">
-        <is>
-          <t>按测试类型</t>
-        </is>
-      </c>
-      <c r="B10" s="3" t="inlineStr">
-        <is>
-          <t>用例数</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="3" t="inlineStr">
-        <is>
-          <t>功能测试</t>
-        </is>
-      </c>
-      <c r="B11" s="3" t="n">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="3" t="inlineStr">
-        <is>
-          <t>接口测试</t>
-        </is>
-      </c>
-      <c r="B12" s="3" t="n">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="3" t="inlineStr">
-        <is>
-          <t>安全测试</t>
-        </is>
-      </c>
-      <c r="B13" s="3" t="n">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="3" t="inlineStr">
-        <is>
-          <t>性能测试</t>
-        </is>
-      </c>
-      <c r="B14" s="3" t="n">
-        <v>8</v>
-      </c>
-    </row>
-  </sheetData>
+  <autoFilter ref="A1:M147"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/docs/内娱图库_海蒂与爷爷_朱远亮_18144610287/StarPicture_测试用例.xlsx
+++ b/docs/内娱图库_海蒂与爷爷_朱远亮_18144610287/StarPicture_测试用例.xlsx
@@ -496,7 +496,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>StarPicture</t>
+          <t>功能测试</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -512,17 +512,11 @@
       <c r="F2" t="n">
         <v>1</v>
       </c>
-      <c r="G2" t="inlineStr"/>
-      <c r="H2" t="inlineStr"/>
-      <c r="I2" t="inlineStr"/>
-      <c r="J2" t="inlineStr"/>
-      <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr">
         <is>
           <t>朱远亮</t>
         </is>
       </c>
-      <c r="M2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -537,7 +531,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>StarPicture</t>
+          <t>功能测试</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -553,17 +547,11 @@
       <c r="F3" t="n">
         <v>1</v>
       </c>
-      <c r="G3" t="inlineStr"/>
-      <c r="H3" t="inlineStr"/>
-      <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr"/>
-      <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr">
         <is>
           <t>朱远亮</t>
         </is>
       </c>
-      <c r="M3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -578,7 +566,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>StarPicture</t>
+          <t>功能测试</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -594,17 +582,11 @@
       <c r="F4" t="n">
         <v>2</v>
       </c>
-      <c r="G4" t="inlineStr"/>
-      <c r="H4" t="inlineStr"/>
-      <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr"/>
-      <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr">
         <is>
           <t>朱远亮</t>
         </is>
       </c>
-      <c r="M4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -619,7 +601,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>StarPicture</t>
+          <t>功能测试</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -635,17 +617,11 @@
       <c r="F5" t="n">
         <v>2</v>
       </c>
-      <c r="G5" t="inlineStr"/>
-      <c r="H5" t="inlineStr"/>
-      <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr"/>
-      <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr">
         <is>
           <t>朱远亮</t>
         </is>
       </c>
-      <c r="M5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -660,7 +636,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>StarPicture</t>
+          <t>功能测试</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -676,17 +652,11 @@
       <c r="F6" t="n">
         <v>2</v>
       </c>
-      <c r="G6" t="inlineStr"/>
-      <c r="H6" t="inlineStr"/>
-      <c r="I6" t="inlineStr"/>
-      <c r="J6" t="inlineStr"/>
-      <c r="K6" t="inlineStr"/>
       <c r="L6" t="inlineStr">
         <is>
           <t>朱远亮</t>
         </is>
       </c>
-      <c r="M6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -701,7 +671,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>StarPicture</t>
+          <t>功能测试</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -717,17 +687,11 @@
       <c r="F7" t="n">
         <v>1</v>
       </c>
-      <c r="G7" t="inlineStr"/>
-      <c r="H7" t="inlineStr"/>
-      <c r="I7" t="inlineStr"/>
-      <c r="J7" t="inlineStr"/>
-      <c r="K7" t="inlineStr"/>
       <c r="L7" t="inlineStr">
         <is>
           <t>朱远亮</t>
         </is>
       </c>
-      <c r="M7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -742,7 +706,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>StarPicture</t>
+          <t>功能测试</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -758,17 +722,11 @@
       <c r="F8" t="n">
         <v>1</v>
       </c>
-      <c r="G8" t="inlineStr"/>
-      <c r="H8" t="inlineStr"/>
-      <c r="I8" t="inlineStr"/>
-      <c r="J8" t="inlineStr"/>
-      <c r="K8" t="inlineStr"/>
       <c r="L8" t="inlineStr">
         <is>
           <t>朱远亮</t>
         </is>
       </c>
-      <c r="M8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -783,7 +741,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>StarPicture</t>
+          <t>功能测试</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -799,17 +757,11 @@
       <c r="F9" t="n">
         <v>2</v>
       </c>
-      <c r="G9" t="inlineStr"/>
-      <c r="H9" t="inlineStr"/>
-      <c r="I9" t="inlineStr"/>
-      <c r="J9" t="inlineStr"/>
-      <c r="K9" t="inlineStr"/>
       <c r="L9" t="inlineStr">
         <is>
           <t>朱远亮</t>
         </is>
       </c>
-      <c r="M9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -824,7 +776,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>StarPicture</t>
+          <t>功能测试</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -840,17 +792,11 @@
       <c r="F10" t="n">
         <v>1</v>
       </c>
-      <c r="G10" t="inlineStr"/>
-      <c r="H10" t="inlineStr"/>
-      <c r="I10" t="inlineStr"/>
-      <c r="J10" t="inlineStr"/>
-      <c r="K10" t="inlineStr"/>
       <c r="L10" t="inlineStr">
         <is>
           <t>朱远亮</t>
         </is>
       </c>
-      <c r="M10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -865,7 +811,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>StarPicture</t>
+          <t>功能测试</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -881,17 +827,11 @@
       <c r="F11" t="n">
         <v>2</v>
       </c>
-      <c r="G11" t="inlineStr"/>
-      <c r="H11" t="inlineStr"/>
-      <c r="I11" t="inlineStr"/>
-      <c r="J11" t="inlineStr"/>
-      <c r="K11" t="inlineStr"/>
       <c r="L11" t="inlineStr">
         <is>
           <t>朱远亮</t>
         </is>
       </c>
-      <c r="M11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -906,7 +846,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>StarPicture</t>
+          <t>功能测试</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -922,17 +862,11 @@
       <c r="F12" t="n">
         <v>2</v>
       </c>
-      <c r="G12" t="inlineStr"/>
-      <c r="H12" t="inlineStr"/>
-      <c r="I12" t="inlineStr"/>
-      <c r="J12" t="inlineStr"/>
-      <c r="K12" t="inlineStr"/>
       <c r="L12" t="inlineStr">
         <is>
           <t>朱远亮</t>
         </is>
       </c>
-      <c r="M12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -947,7 +881,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>StarPicture</t>
+          <t>功能测试</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -963,17 +897,11 @@
       <c r="F13" t="n">
         <v>1</v>
       </c>
-      <c r="G13" t="inlineStr"/>
-      <c r="H13" t="inlineStr"/>
-      <c r="I13" t="inlineStr"/>
-      <c r="J13" t="inlineStr"/>
-      <c r="K13" t="inlineStr"/>
       <c r="L13" t="inlineStr">
         <is>
           <t>朱远亮</t>
         </is>
       </c>
-      <c r="M13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -988,7 +916,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>StarPicture</t>
+          <t>功能测试</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -1004,17 +932,11 @@
       <c r="F14" t="n">
         <v>1</v>
       </c>
-      <c r="G14" t="inlineStr"/>
-      <c r="H14" t="inlineStr"/>
-      <c r="I14" t="inlineStr"/>
-      <c r="J14" t="inlineStr"/>
-      <c r="K14" t="inlineStr"/>
       <c r="L14" t="inlineStr">
         <is>
           <t>朱远亮</t>
         </is>
       </c>
-      <c r="M14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -1029,7 +951,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>StarPicture</t>
+          <t>功能测试</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -1045,17 +967,11 @@
       <c r="F15" t="n">
         <v>1</v>
       </c>
-      <c r="G15" t="inlineStr"/>
-      <c r="H15" t="inlineStr"/>
-      <c r="I15" t="inlineStr"/>
-      <c r="J15" t="inlineStr"/>
-      <c r="K15" t="inlineStr"/>
       <c r="L15" t="inlineStr">
         <is>
           <t>朱远亮</t>
         </is>
       </c>
-      <c r="M15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -1070,7 +986,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>StarPicture</t>
+          <t>功能测试</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -1086,17 +1002,11 @@
       <c r="F16" t="n">
         <v>1</v>
       </c>
-      <c r="G16" t="inlineStr"/>
-      <c r="H16" t="inlineStr"/>
-      <c r="I16" t="inlineStr"/>
-      <c r="J16" t="inlineStr"/>
-      <c r="K16" t="inlineStr"/>
       <c r="L16" t="inlineStr">
         <is>
           <t>朱远亮</t>
         </is>
       </c>
-      <c r="M16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -1111,7 +1021,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>StarPicture</t>
+          <t>功能测试</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -1127,17 +1037,11 @@
       <c r="F17" t="n">
         <v>2</v>
       </c>
-      <c r="G17" t="inlineStr"/>
-      <c r="H17" t="inlineStr"/>
-      <c r="I17" t="inlineStr"/>
-      <c r="J17" t="inlineStr"/>
-      <c r="K17" t="inlineStr"/>
       <c r="L17" t="inlineStr">
         <is>
           <t>朱远亮</t>
         </is>
       </c>
-      <c r="M17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -1152,7 +1056,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>StarPicture</t>
+          <t>功能测试</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -1168,17 +1072,11 @@
       <c r="F18" t="n">
         <v>1</v>
       </c>
-      <c r="G18" t="inlineStr"/>
-      <c r="H18" t="inlineStr"/>
-      <c r="I18" t="inlineStr"/>
-      <c r="J18" t="inlineStr"/>
-      <c r="K18" t="inlineStr"/>
       <c r="L18" t="inlineStr">
         <is>
           <t>朱远亮</t>
         </is>
       </c>
-      <c r="M18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -1193,7 +1091,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>StarPicture</t>
+          <t>功能测试</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -1209,17 +1107,11 @@
       <c r="F19" t="n">
         <v>1</v>
       </c>
-      <c r="G19" t="inlineStr"/>
-      <c r="H19" t="inlineStr"/>
-      <c r="I19" t="inlineStr"/>
-      <c r="J19" t="inlineStr"/>
-      <c r="K19" t="inlineStr"/>
       <c r="L19" t="inlineStr">
         <is>
           <t>朱远亮</t>
         </is>
       </c>
-      <c r="M19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -1234,7 +1126,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>StarPicture</t>
+          <t>功能测试</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -1250,17 +1142,11 @@
       <c r="F20" t="n">
         <v>1</v>
       </c>
-      <c r="G20" t="inlineStr"/>
-      <c r="H20" t="inlineStr"/>
-      <c r="I20" t="inlineStr"/>
-      <c r="J20" t="inlineStr"/>
-      <c r="K20" t="inlineStr"/>
       <c r="L20" t="inlineStr">
         <is>
           <t>朱远亮</t>
         </is>
       </c>
-      <c r="M20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -1275,7 +1161,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>StarPicture</t>
+          <t>功能测试</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -1291,17 +1177,11 @@
       <c r="F21" t="n">
         <v>1</v>
       </c>
-      <c r="G21" t="inlineStr"/>
-      <c r="H21" t="inlineStr"/>
-      <c r="I21" t="inlineStr"/>
-      <c r="J21" t="inlineStr"/>
-      <c r="K21" t="inlineStr"/>
       <c r="L21" t="inlineStr">
         <is>
           <t>朱远亮</t>
         </is>
       </c>
-      <c r="M21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -1316,7 +1196,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>StarPicture</t>
+          <t>功能测试</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -1332,17 +1212,11 @@
       <c r="F22" t="n">
         <v>2</v>
       </c>
-      <c r="G22" t="inlineStr"/>
-      <c r="H22" t="inlineStr"/>
-      <c r="I22" t="inlineStr"/>
-      <c r="J22" t="inlineStr"/>
-      <c r="K22" t="inlineStr"/>
       <c r="L22" t="inlineStr">
         <is>
           <t>朱远亮</t>
         </is>
       </c>
-      <c r="M22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -1357,7 +1231,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>StarPicture</t>
+          <t>功能测试</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -1373,17 +1247,11 @@
       <c r="F23" t="n">
         <v>1</v>
       </c>
-      <c r="G23" t="inlineStr"/>
-      <c r="H23" t="inlineStr"/>
-      <c r="I23" t="inlineStr"/>
-      <c r="J23" t="inlineStr"/>
-      <c r="K23" t="inlineStr"/>
       <c r="L23" t="inlineStr">
         <is>
           <t>朱远亮</t>
         </is>
       </c>
-      <c r="M23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -1398,7 +1266,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>StarPicture</t>
+          <t>功能测试</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -1414,17 +1282,11 @@
       <c r="F24" t="n">
         <v>1</v>
       </c>
-      <c r="G24" t="inlineStr"/>
-      <c r="H24" t="inlineStr"/>
-      <c r="I24" t="inlineStr"/>
-      <c r="J24" t="inlineStr"/>
-      <c r="K24" t="inlineStr"/>
       <c r="L24" t="inlineStr">
         <is>
           <t>朱远亮</t>
         </is>
       </c>
-      <c r="M24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -1439,7 +1301,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>StarPicture</t>
+          <t>功能测试</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -1455,17 +1317,11 @@
       <c r="F25" t="n">
         <v>1</v>
       </c>
-      <c r="G25" t="inlineStr"/>
-      <c r="H25" t="inlineStr"/>
-      <c r="I25" t="inlineStr"/>
-      <c r="J25" t="inlineStr"/>
-      <c r="K25" t="inlineStr"/>
       <c r="L25" t="inlineStr">
         <is>
           <t>朱远亮</t>
         </is>
       </c>
-      <c r="M25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -1480,7 +1336,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>StarPicture</t>
+          <t>功能测试</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -1496,17 +1352,11 @@
       <c r="F26" t="n">
         <v>1</v>
       </c>
-      <c r="G26" t="inlineStr"/>
-      <c r="H26" t="inlineStr"/>
-      <c r="I26" t="inlineStr"/>
-      <c r="J26" t="inlineStr"/>
-      <c r="K26" t="inlineStr"/>
       <c r="L26" t="inlineStr">
         <is>
           <t>朱远亮</t>
         </is>
       </c>
-      <c r="M26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -1521,7 +1371,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>StarPicture</t>
+          <t>功能测试</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -1537,17 +1387,11 @@
       <c r="F27" t="n">
         <v>1</v>
       </c>
-      <c r="G27" t="inlineStr"/>
-      <c r="H27" t="inlineStr"/>
-      <c r="I27" t="inlineStr"/>
-      <c r="J27" t="inlineStr"/>
-      <c r="K27" t="inlineStr"/>
       <c r="L27" t="inlineStr">
         <is>
           <t>朱远亮</t>
         </is>
       </c>
-      <c r="M27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -1562,7 +1406,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>StarPicture</t>
+          <t>功能测试</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -1578,17 +1422,11 @@
       <c r="F28" t="n">
         <v>2</v>
       </c>
-      <c r="G28" t="inlineStr"/>
-      <c r="H28" t="inlineStr"/>
-      <c r="I28" t="inlineStr"/>
-      <c r="J28" t="inlineStr"/>
-      <c r="K28" t="inlineStr"/>
       <c r="L28" t="inlineStr">
         <is>
           <t>朱远亮</t>
         </is>
       </c>
-      <c r="M28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -1603,7 +1441,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>StarPicture</t>
+          <t>功能测试</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -1619,17 +1457,11 @@
       <c r="F29" t="n">
         <v>1</v>
       </c>
-      <c r="G29" t="inlineStr"/>
-      <c r="H29" t="inlineStr"/>
-      <c r="I29" t="inlineStr"/>
-      <c r="J29" t="inlineStr"/>
-      <c r="K29" t="inlineStr"/>
       <c r="L29" t="inlineStr">
         <is>
           <t>朱远亮</t>
         </is>
       </c>
-      <c r="M29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -1644,7 +1476,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>StarPicture</t>
+          <t>功能测试</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -1660,17 +1492,11 @@
       <c r="F30" t="n">
         <v>2</v>
       </c>
-      <c r="G30" t="inlineStr"/>
-      <c r="H30" t="inlineStr"/>
-      <c r="I30" t="inlineStr"/>
-      <c r="J30" t="inlineStr"/>
-      <c r="K30" t="inlineStr"/>
       <c r="L30" t="inlineStr">
         <is>
           <t>朱远亮</t>
         </is>
       </c>
-      <c r="M30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -1685,7 +1511,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>StarPicture</t>
+          <t>性能测试</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -1701,17 +1527,11 @@
       <c r="F31" t="n">
         <v>2</v>
       </c>
-      <c r="G31" t="inlineStr"/>
-      <c r="H31" t="inlineStr"/>
-      <c r="I31" t="inlineStr"/>
-      <c r="J31" t="inlineStr"/>
-      <c r="K31" t="inlineStr"/>
       <c r="L31" t="inlineStr">
         <is>
           <t>朱远亮</t>
         </is>
       </c>
-      <c r="M31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -1726,7 +1546,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>StarPicture</t>
+          <t>接口测试</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -1742,17 +1562,11 @@
       <c r="F32" t="n">
         <v>2</v>
       </c>
-      <c r="G32" t="inlineStr"/>
-      <c r="H32" t="inlineStr"/>
-      <c r="I32" t="inlineStr"/>
-      <c r="J32" t="inlineStr"/>
-      <c r="K32" t="inlineStr"/>
       <c r="L32" t="inlineStr">
         <is>
           <t>朱远亮</t>
         </is>
       </c>
-      <c r="M32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -1767,7 +1581,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>StarPicture</t>
+          <t>功能测试</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -1783,17 +1597,11 @@
       <c r="F33" t="n">
         <v>1</v>
       </c>
-      <c r="G33" t="inlineStr"/>
-      <c r="H33" t="inlineStr"/>
-      <c r="I33" t="inlineStr"/>
-      <c r="J33" t="inlineStr"/>
-      <c r="K33" t="inlineStr"/>
       <c r="L33" t="inlineStr">
         <is>
           <t>李冠燃</t>
         </is>
       </c>
-      <c r="M33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -1808,7 +1616,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>StarPicture</t>
+          <t>功能测试</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -1824,17 +1632,11 @@
       <c r="F34" t="n">
         <v>1</v>
       </c>
-      <c r="G34" t="inlineStr"/>
-      <c r="H34" t="inlineStr"/>
-      <c r="I34" t="inlineStr"/>
-      <c r="J34" t="inlineStr"/>
-      <c r="K34" t="inlineStr"/>
       <c r="L34" t="inlineStr">
         <is>
           <t>李冠燃</t>
         </is>
       </c>
-      <c r="M34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -1849,7 +1651,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>StarPicture</t>
+          <t>功能测试</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -1865,17 +1667,11 @@
       <c r="F35" t="n">
         <v>2</v>
       </c>
-      <c r="G35" t="inlineStr"/>
-      <c r="H35" t="inlineStr"/>
-      <c r="I35" t="inlineStr"/>
-      <c r="J35" t="inlineStr"/>
-      <c r="K35" t="inlineStr"/>
       <c r="L35" t="inlineStr">
         <is>
           <t>李冠燃</t>
         </is>
       </c>
-      <c r="M35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -1890,7 +1686,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>StarPicture</t>
+          <t>功能测试</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -1906,17 +1702,11 @@
       <c r="F36" t="n">
         <v>2</v>
       </c>
-      <c r="G36" t="inlineStr"/>
-      <c r="H36" t="inlineStr"/>
-      <c r="I36" t="inlineStr"/>
-      <c r="J36" t="inlineStr"/>
-      <c r="K36" t="inlineStr"/>
       <c r="L36" t="inlineStr">
         <is>
           <t>李冠燃</t>
         </is>
       </c>
-      <c r="M36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -1931,7 +1721,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>StarPicture</t>
+          <t>功能测试</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -1947,17 +1737,11 @@
       <c r="F37" t="n">
         <v>2</v>
       </c>
-      <c r="G37" t="inlineStr"/>
-      <c r="H37" t="inlineStr"/>
-      <c r="I37" t="inlineStr"/>
-      <c r="J37" t="inlineStr"/>
-      <c r="K37" t="inlineStr"/>
       <c r="L37" t="inlineStr">
         <is>
           <t>李冠燃</t>
         </is>
       </c>
-      <c r="M37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
@@ -1972,7 +1756,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>StarPicture</t>
+          <t>功能测试</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -1988,17 +1772,11 @@
       <c r="F38" t="n">
         <v>1</v>
       </c>
-      <c r="G38" t="inlineStr"/>
-      <c r="H38" t="inlineStr"/>
-      <c r="I38" t="inlineStr"/>
-      <c r="J38" t="inlineStr"/>
-      <c r="K38" t="inlineStr"/>
       <c r="L38" t="inlineStr">
         <is>
           <t>李冠燃</t>
         </is>
       </c>
-      <c r="M38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
@@ -2013,7 +1791,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>StarPicture</t>
+          <t>功能测试</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -2029,17 +1807,11 @@
       <c r="F39" t="n">
         <v>1</v>
       </c>
-      <c r="G39" t="inlineStr"/>
-      <c r="H39" t="inlineStr"/>
-      <c r="I39" t="inlineStr"/>
-      <c r="J39" t="inlineStr"/>
-      <c r="K39" t="inlineStr"/>
       <c r="L39" t="inlineStr">
         <is>
           <t>李冠燃</t>
         </is>
       </c>
-      <c r="M39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
@@ -2054,7 +1826,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>StarPicture</t>
+          <t>功能测试</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -2070,17 +1842,11 @@
       <c r="F40" t="n">
         <v>2</v>
       </c>
-      <c r="G40" t="inlineStr"/>
-      <c r="H40" t="inlineStr"/>
-      <c r="I40" t="inlineStr"/>
-      <c r="J40" t="inlineStr"/>
-      <c r="K40" t="inlineStr"/>
       <c r="L40" t="inlineStr">
         <is>
           <t>李冠燃</t>
         </is>
       </c>
-      <c r="M40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
@@ -2095,7 +1861,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>StarPicture</t>
+          <t>功能测试</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -2111,17 +1877,11 @@
       <c r="F41" t="n">
         <v>2</v>
       </c>
-      <c r="G41" t="inlineStr"/>
-      <c r="H41" t="inlineStr"/>
-      <c r="I41" t="inlineStr"/>
-      <c r="J41" t="inlineStr"/>
-      <c r="K41" t="inlineStr"/>
       <c r="L41" t="inlineStr">
         <is>
           <t>李冠燃</t>
         </is>
       </c>
-      <c r="M41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
@@ -2136,7 +1896,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>StarPicture</t>
+          <t>功能测试</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -2152,17 +1912,11 @@
       <c r="F42" t="n">
         <v>1</v>
       </c>
-      <c r="G42" t="inlineStr"/>
-      <c r="H42" t="inlineStr"/>
-      <c r="I42" t="inlineStr"/>
-      <c r="J42" t="inlineStr"/>
-      <c r="K42" t="inlineStr"/>
       <c r="L42" t="inlineStr">
         <is>
           <t>李冠燃</t>
         </is>
       </c>
-      <c r="M42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
@@ -2177,7 +1931,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>StarPicture</t>
+          <t>功能测试</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -2193,17 +1947,11 @@
       <c r="F43" t="n">
         <v>2</v>
       </c>
-      <c r="G43" t="inlineStr"/>
-      <c r="H43" t="inlineStr"/>
-      <c r="I43" t="inlineStr"/>
-      <c r="J43" t="inlineStr"/>
-      <c r="K43" t="inlineStr"/>
       <c r="L43" t="inlineStr">
         <is>
           <t>李冠燃</t>
         </is>
       </c>
-      <c r="M43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
@@ -2218,7 +1966,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>StarPicture</t>
+          <t>功能测试</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -2234,17 +1982,11 @@
       <c r="F44" t="n">
         <v>1</v>
       </c>
-      <c r="G44" t="inlineStr"/>
-      <c r="H44" t="inlineStr"/>
-      <c r="I44" t="inlineStr"/>
-      <c r="J44" t="inlineStr"/>
-      <c r="K44" t="inlineStr"/>
       <c r="L44" t="inlineStr">
         <is>
           <t>李冠燃</t>
         </is>
       </c>
-      <c r="M44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
@@ -2259,7 +2001,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>StarPicture</t>
+          <t>功能测试</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -2275,17 +2017,11 @@
       <c r="F45" t="n">
         <v>2</v>
       </c>
-      <c r="G45" t="inlineStr"/>
-      <c r="H45" t="inlineStr"/>
-      <c r="I45" t="inlineStr"/>
-      <c r="J45" t="inlineStr"/>
-      <c r="K45" t="inlineStr"/>
       <c r="L45" t="inlineStr">
         <is>
           <t>李冠燃</t>
         </is>
       </c>
-      <c r="M45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
@@ -2300,7 +2036,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>StarPicture</t>
+          <t>功能测试</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -2316,17 +2052,11 @@
       <c r="F46" t="n">
         <v>1</v>
       </c>
-      <c r="G46" t="inlineStr"/>
-      <c r="H46" t="inlineStr"/>
-      <c r="I46" t="inlineStr"/>
-      <c r="J46" t="inlineStr"/>
-      <c r="K46" t="inlineStr"/>
       <c r="L46" t="inlineStr">
         <is>
           <t>李冠燃</t>
         </is>
       </c>
-      <c r="M46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
@@ -2341,7 +2071,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>StarPicture</t>
+          <t>功能测试</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -2357,17 +2087,11 @@
       <c r="F47" t="n">
         <v>1</v>
       </c>
-      <c r="G47" t="inlineStr"/>
-      <c r="H47" t="inlineStr"/>
-      <c r="I47" t="inlineStr"/>
-      <c r="J47" t="inlineStr"/>
-      <c r="K47" t="inlineStr"/>
       <c r="L47" t="inlineStr">
         <is>
           <t>李冠燃</t>
         </is>
       </c>
-      <c r="M47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
@@ -2382,7 +2106,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>StarPicture</t>
+          <t>功能测试</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -2398,17 +2122,11 @@
       <c r="F48" t="n">
         <v>2</v>
       </c>
-      <c r="G48" t="inlineStr"/>
-      <c r="H48" t="inlineStr"/>
-      <c r="I48" t="inlineStr"/>
-      <c r="J48" t="inlineStr"/>
-      <c r="K48" t="inlineStr"/>
       <c r="L48" t="inlineStr">
         <is>
           <t>李冠燃</t>
         </is>
       </c>
-      <c r="M48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
@@ -2423,7 +2141,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>StarPicture</t>
+          <t>功能测试</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -2439,17 +2157,11 @@
       <c r="F49" t="n">
         <v>2</v>
       </c>
-      <c r="G49" t="inlineStr"/>
-      <c r="H49" t="inlineStr"/>
-      <c r="I49" t="inlineStr"/>
-      <c r="J49" t="inlineStr"/>
-      <c r="K49" t="inlineStr"/>
       <c r="L49" t="inlineStr">
         <is>
           <t>李冠燃</t>
         </is>
       </c>
-      <c r="M49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
@@ -2464,7 +2176,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>StarPicture</t>
+          <t>功能测试</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -2480,17 +2192,11 @@
       <c r="F50" t="n">
         <v>1</v>
       </c>
-      <c r="G50" t="inlineStr"/>
-      <c r="H50" t="inlineStr"/>
-      <c r="I50" t="inlineStr"/>
-      <c r="J50" t="inlineStr"/>
-      <c r="K50" t="inlineStr"/>
       <c r="L50" t="inlineStr">
         <is>
           <t>李冠燃</t>
         </is>
       </c>
-      <c r="M50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
@@ -2505,7 +2211,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>StarPicture</t>
+          <t>功能测试</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -2521,17 +2227,11 @@
       <c r="F51" t="n">
         <v>1</v>
       </c>
-      <c r="G51" t="inlineStr"/>
-      <c r="H51" t="inlineStr"/>
-      <c r="I51" t="inlineStr"/>
-      <c r="J51" t="inlineStr"/>
-      <c r="K51" t="inlineStr"/>
       <c r="L51" t="inlineStr">
         <is>
           <t>李冠燃</t>
         </is>
       </c>
-      <c r="M51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
@@ -2546,7 +2246,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>StarPicture</t>
+          <t>功能测试</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -2562,17 +2262,11 @@
       <c r="F52" t="n">
         <v>1</v>
       </c>
-      <c r="G52" t="inlineStr"/>
-      <c r="H52" t="inlineStr"/>
-      <c r="I52" t="inlineStr"/>
-      <c r="J52" t="inlineStr"/>
-      <c r="K52" t="inlineStr"/>
       <c r="L52" t="inlineStr">
         <is>
           <t>李冠燃</t>
         </is>
       </c>
-      <c r="M52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
@@ -2587,7 +2281,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>StarPicture</t>
+          <t>功能测试</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -2603,17 +2297,11 @@
       <c r="F53" t="n">
         <v>1</v>
       </c>
-      <c r="G53" t="inlineStr"/>
-      <c r="H53" t="inlineStr"/>
-      <c r="I53" t="inlineStr"/>
-      <c r="J53" t="inlineStr"/>
-      <c r="K53" t="inlineStr"/>
       <c r="L53" t="inlineStr">
         <is>
           <t>李冠燃</t>
         </is>
       </c>
-      <c r="M53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
@@ -2628,7 +2316,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>StarPicture</t>
+          <t>功能测试</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -2644,17 +2332,11 @@
       <c r="F54" t="n">
         <v>1</v>
       </c>
-      <c r="G54" t="inlineStr"/>
-      <c r="H54" t="inlineStr"/>
-      <c r="I54" t="inlineStr"/>
-      <c r="J54" t="inlineStr"/>
-      <c r="K54" t="inlineStr"/>
       <c r="L54" t="inlineStr">
         <is>
           <t>李冠燃</t>
         </is>
       </c>
-      <c r="M54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
@@ -2669,7 +2351,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>StarPicture</t>
+          <t>功能测试</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -2685,17 +2367,11 @@
       <c r="F55" t="n">
         <v>1</v>
       </c>
-      <c r="G55" t="inlineStr"/>
-      <c r="H55" t="inlineStr"/>
-      <c r="I55" t="inlineStr"/>
-      <c r="J55" t="inlineStr"/>
-      <c r="K55" t="inlineStr"/>
       <c r="L55" t="inlineStr">
         <is>
           <t>李冠燃</t>
         </is>
       </c>
-      <c r="M55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
@@ -2710,7 +2386,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>StarPicture</t>
+          <t>功能测试</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -2726,17 +2402,11 @@
       <c r="F56" t="n">
         <v>1</v>
       </c>
-      <c r="G56" t="inlineStr"/>
-      <c r="H56" t="inlineStr"/>
-      <c r="I56" t="inlineStr"/>
-      <c r="J56" t="inlineStr"/>
-      <c r="K56" t="inlineStr"/>
       <c r="L56" t="inlineStr">
         <is>
           <t>李冠燃</t>
         </is>
       </c>
-      <c r="M56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
@@ -2751,7 +2421,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>StarPicture</t>
+          <t>功能测试</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -2767,17 +2437,11 @@
       <c r="F57" t="n">
         <v>2</v>
       </c>
-      <c r="G57" t="inlineStr"/>
-      <c r="H57" t="inlineStr"/>
-      <c r="I57" t="inlineStr"/>
-      <c r="J57" t="inlineStr"/>
-      <c r="K57" t="inlineStr"/>
       <c r="L57" t="inlineStr">
         <is>
           <t>李冠燃</t>
         </is>
       </c>
-      <c r="M57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
@@ -2792,7 +2456,7 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>StarPicture</t>
+          <t>功能测试</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
@@ -2808,17 +2472,11 @@
       <c r="F58" t="n">
         <v>1</v>
       </c>
-      <c r="G58" t="inlineStr"/>
-      <c r="H58" t="inlineStr"/>
-      <c r="I58" t="inlineStr"/>
-      <c r="J58" t="inlineStr"/>
-      <c r="K58" t="inlineStr"/>
       <c r="L58" t="inlineStr">
         <is>
           <t>李冠燃</t>
         </is>
       </c>
-      <c r="M58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
@@ -2833,7 +2491,7 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>StarPicture</t>
+          <t>功能测试</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
@@ -2849,17 +2507,11 @@
       <c r="F59" t="n">
         <v>2</v>
       </c>
-      <c r="G59" t="inlineStr"/>
-      <c r="H59" t="inlineStr"/>
-      <c r="I59" t="inlineStr"/>
-      <c r="J59" t="inlineStr"/>
-      <c r="K59" t="inlineStr"/>
       <c r="L59" t="inlineStr">
         <is>
           <t>李冠燃</t>
         </is>
       </c>
-      <c r="M59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
@@ -2874,7 +2526,7 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>StarPicture</t>
+          <t>功能测试</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
@@ -2890,17 +2542,11 @@
       <c r="F60" t="n">
         <v>1</v>
       </c>
-      <c r="G60" t="inlineStr"/>
-      <c r="H60" t="inlineStr"/>
-      <c r="I60" t="inlineStr"/>
-      <c r="J60" t="inlineStr"/>
-      <c r="K60" t="inlineStr"/>
       <c r="L60" t="inlineStr">
         <is>
           <t>李冠燃</t>
         </is>
       </c>
-      <c r="M60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
@@ -2915,7 +2561,7 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>StarPicture</t>
+          <t>功能测试</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
@@ -2931,17 +2577,11 @@
       <c r="F61" t="n">
         <v>1</v>
       </c>
-      <c r="G61" t="inlineStr"/>
-      <c r="H61" t="inlineStr"/>
-      <c r="I61" t="inlineStr"/>
-      <c r="J61" t="inlineStr"/>
-      <c r="K61" t="inlineStr"/>
       <c r="L61" t="inlineStr">
         <is>
           <t>李冠燃</t>
         </is>
       </c>
-      <c r="M61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
@@ -2956,7 +2596,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>StarPicture</t>
+          <t>功能测试</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -2972,17 +2612,11 @@
       <c r="F62" t="n">
         <v>1</v>
       </c>
-      <c r="G62" t="inlineStr"/>
-      <c r="H62" t="inlineStr"/>
-      <c r="I62" t="inlineStr"/>
-      <c r="J62" t="inlineStr"/>
-      <c r="K62" t="inlineStr"/>
       <c r="L62" t="inlineStr">
         <is>
           <t>李冠燃</t>
         </is>
       </c>
-      <c r="M62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
@@ -2997,7 +2631,7 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>StarPicture</t>
+          <t>功能测试</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
@@ -3013,17 +2647,11 @@
       <c r="F63" t="n">
         <v>1</v>
       </c>
-      <c r="G63" t="inlineStr"/>
-      <c r="H63" t="inlineStr"/>
-      <c r="I63" t="inlineStr"/>
-      <c r="J63" t="inlineStr"/>
-      <c r="K63" t="inlineStr"/>
       <c r="L63" t="inlineStr">
         <is>
           <t>李冠燃</t>
         </is>
       </c>
-      <c r="M63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
@@ -3038,7 +2666,7 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>StarPicture</t>
+          <t>功能测试</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
@@ -3054,17 +2682,11 @@
       <c r="F64" t="n">
         <v>1</v>
       </c>
-      <c r="G64" t="inlineStr"/>
-      <c r="H64" t="inlineStr"/>
-      <c r="I64" t="inlineStr"/>
-      <c r="J64" t="inlineStr"/>
-      <c r="K64" t="inlineStr"/>
       <c r="L64" t="inlineStr">
         <is>
           <t>李冠燃</t>
         </is>
       </c>
-      <c r="M64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
@@ -3079,7 +2701,7 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>StarPicture</t>
+          <t>功能测试</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -3095,17 +2717,11 @@
       <c r="F65" t="n">
         <v>1</v>
       </c>
-      <c r="G65" t="inlineStr"/>
-      <c r="H65" t="inlineStr"/>
-      <c r="I65" t="inlineStr"/>
-      <c r="J65" t="inlineStr"/>
-      <c r="K65" t="inlineStr"/>
       <c r="L65" t="inlineStr">
         <is>
           <t>李冠燃</t>
         </is>
       </c>
-      <c r="M65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
@@ -3120,7 +2736,7 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>StarPicture</t>
+          <t>功能测试</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
@@ -3136,17 +2752,11 @@
       <c r="F66" t="n">
         <v>1</v>
       </c>
-      <c r="G66" t="inlineStr"/>
-      <c r="H66" t="inlineStr"/>
-      <c r="I66" t="inlineStr"/>
-      <c r="J66" t="inlineStr"/>
-      <c r="K66" t="inlineStr"/>
       <c r="L66" t="inlineStr">
         <is>
           <t>李冠燃</t>
         </is>
       </c>
-      <c r="M66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
@@ -3161,7 +2771,7 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>StarPicture</t>
+          <t>功能测试</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
@@ -3177,17 +2787,11 @@
       <c r="F67" t="n">
         <v>2</v>
       </c>
-      <c r="G67" t="inlineStr"/>
-      <c r="H67" t="inlineStr"/>
-      <c r="I67" t="inlineStr"/>
-      <c r="J67" t="inlineStr"/>
-      <c r="K67" t="inlineStr"/>
       <c r="L67" t="inlineStr">
         <is>
           <t>李冠燃</t>
         </is>
       </c>
-      <c r="M67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
@@ -3202,7 +2806,7 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>StarPicture</t>
+          <t>功能测试</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
@@ -3218,17 +2822,11 @@
       <c r="F68" t="n">
         <v>2</v>
       </c>
-      <c r="G68" t="inlineStr"/>
-      <c r="H68" t="inlineStr"/>
-      <c r="I68" t="inlineStr"/>
-      <c r="J68" t="inlineStr"/>
-      <c r="K68" t="inlineStr"/>
       <c r="L68" t="inlineStr">
         <is>
           <t>李冠燃</t>
         </is>
       </c>
-      <c r="M68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
@@ -3243,7 +2841,7 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>StarPicture</t>
+          <t>功能测试</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
@@ -3259,17 +2857,11 @@
       <c r="F69" t="n">
         <v>1</v>
       </c>
-      <c r="G69" t="inlineStr"/>
-      <c r="H69" t="inlineStr"/>
-      <c r="I69" t="inlineStr"/>
-      <c r="J69" t="inlineStr"/>
-      <c r="K69" t="inlineStr"/>
       <c r="L69" t="inlineStr">
         <is>
           <t>李冠燃</t>
         </is>
       </c>
-      <c r="M69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
@@ -3284,7 +2876,7 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>StarPicture</t>
+          <t>功能测试</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
@@ -3300,17 +2892,11 @@
       <c r="F70" t="n">
         <v>2</v>
       </c>
-      <c r="G70" t="inlineStr"/>
-      <c r="H70" t="inlineStr"/>
-      <c r="I70" t="inlineStr"/>
-      <c r="J70" t="inlineStr"/>
-      <c r="K70" t="inlineStr"/>
       <c r="L70" t="inlineStr">
         <is>
           <t>李冠燃</t>
         </is>
       </c>
-      <c r="M70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
@@ -3325,7 +2911,7 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>StarPicture</t>
+          <t>功能测试</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
@@ -3341,17 +2927,11 @@
       <c r="F71" t="n">
         <v>1</v>
       </c>
-      <c r="G71" t="inlineStr"/>
-      <c r="H71" t="inlineStr"/>
-      <c r="I71" t="inlineStr"/>
-      <c r="J71" t="inlineStr"/>
-      <c r="K71" t="inlineStr"/>
       <c r="L71" t="inlineStr">
         <is>
           <t>李冠燃</t>
         </is>
       </c>
-      <c r="M71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
@@ -3366,7 +2946,7 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>StarPicture</t>
+          <t>功能测试</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
@@ -3382,17 +2962,11 @@
       <c r="F72" t="n">
         <v>1</v>
       </c>
-      <c r="G72" t="inlineStr"/>
-      <c r="H72" t="inlineStr"/>
-      <c r="I72" t="inlineStr"/>
-      <c r="J72" t="inlineStr"/>
-      <c r="K72" t="inlineStr"/>
       <c r="L72" t="inlineStr">
         <is>
           <t>李冠燃</t>
         </is>
       </c>
-      <c r="M72" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
@@ -3407,7 +2981,7 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>StarPicture</t>
+          <t>功能测试</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
@@ -3423,17 +2997,11 @@
       <c r="F73" t="n">
         <v>1</v>
       </c>
-      <c r="G73" t="inlineStr"/>
-      <c r="H73" t="inlineStr"/>
-      <c r="I73" t="inlineStr"/>
-      <c r="J73" t="inlineStr"/>
-      <c r="K73" t="inlineStr"/>
       <c r="L73" t="inlineStr">
         <is>
           <t>李冠燃</t>
         </is>
       </c>
-      <c r="M73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
@@ -3448,7 +3016,7 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>StarPicture</t>
+          <t>功能测试</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
@@ -3464,17 +3032,11 @@
       <c r="F74" t="n">
         <v>1</v>
       </c>
-      <c r="G74" t="inlineStr"/>
-      <c r="H74" t="inlineStr"/>
-      <c r="I74" t="inlineStr"/>
-      <c r="J74" t="inlineStr"/>
-      <c r="K74" t="inlineStr"/>
       <c r="L74" t="inlineStr">
         <is>
           <t>李冠燃</t>
         </is>
       </c>
-      <c r="M74" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
@@ -3489,7 +3051,7 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>StarPicture</t>
+          <t>性能测试</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
@@ -3505,17 +3067,11 @@
       <c r="F75" t="n">
         <v>2</v>
       </c>
-      <c r="G75" t="inlineStr"/>
-      <c r="H75" t="inlineStr"/>
-      <c r="I75" t="inlineStr"/>
-      <c r="J75" t="inlineStr"/>
-      <c r="K75" t="inlineStr"/>
       <c r="L75" t="inlineStr">
         <is>
           <t>李冠燃</t>
         </is>
       </c>
-      <c r="M75" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
@@ -3530,7 +3086,7 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>StarPicture</t>
+          <t>接口测试</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
@@ -3546,17 +3102,11 @@
       <c r="F76" t="n">
         <v>2</v>
       </c>
-      <c r="G76" t="inlineStr"/>
-      <c r="H76" t="inlineStr"/>
-      <c r="I76" t="inlineStr"/>
-      <c r="J76" t="inlineStr"/>
-      <c r="K76" t="inlineStr"/>
       <c r="L76" t="inlineStr">
         <is>
           <t>李冠燃</t>
         </is>
       </c>
-      <c r="M76" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
@@ -3571,7 +3121,7 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>StarPicture</t>
+          <t>接口测试</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
@@ -3587,17 +3137,11 @@
       <c r="F77" t="n">
         <v>2</v>
       </c>
-      <c r="G77" t="inlineStr"/>
-      <c r="H77" t="inlineStr"/>
-      <c r="I77" t="inlineStr"/>
-      <c r="J77" t="inlineStr"/>
-      <c r="K77" t="inlineStr"/>
       <c r="L77" t="inlineStr">
         <is>
           <t>李冠燃</t>
         </is>
       </c>
-      <c r="M77" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
@@ -3612,7 +3156,7 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>StarPicture</t>
+          <t>功能测试</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
@@ -3628,17 +3172,11 @@
       <c r="F78" t="n">
         <v>1</v>
       </c>
-      <c r="G78" t="inlineStr"/>
-      <c r="H78" t="inlineStr"/>
-      <c r="I78" t="inlineStr"/>
-      <c r="J78" t="inlineStr"/>
-      <c r="K78" t="inlineStr"/>
       <c r="L78" t="inlineStr">
         <is>
           <t>李坤纬</t>
         </is>
       </c>
-      <c r="M78" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
@@ -3653,7 +3191,7 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>StarPicture</t>
+          <t>功能测试</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
@@ -3669,17 +3207,11 @@
       <c r="F79" t="n">
         <v>1</v>
       </c>
-      <c r="G79" t="inlineStr"/>
-      <c r="H79" t="inlineStr"/>
-      <c r="I79" t="inlineStr"/>
-      <c r="J79" t="inlineStr"/>
-      <c r="K79" t="inlineStr"/>
       <c r="L79" t="inlineStr">
         <is>
           <t>李坤纬</t>
         </is>
       </c>
-      <c r="M79" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
@@ -3694,7 +3226,7 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>StarPicture</t>
+          <t>功能测试</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
@@ -3710,17 +3242,11 @@
       <c r="F80" t="n">
         <v>2</v>
       </c>
-      <c r="G80" t="inlineStr"/>
-      <c r="H80" t="inlineStr"/>
-      <c r="I80" t="inlineStr"/>
-      <c r="J80" t="inlineStr"/>
-      <c r="K80" t="inlineStr"/>
       <c r="L80" t="inlineStr">
         <is>
           <t>李坤纬</t>
         </is>
       </c>
-      <c r="M80" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
@@ -3735,7 +3261,7 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>StarPicture</t>
+          <t>功能测试</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
@@ -3751,17 +3277,11 @@
       <c r="F81" t="n">
         <v>2</v>
       </c>
-      <c r="G81" t="inlineStr"/>
-      <c r="H81" t="inlineStr"/>
-      <c r="I81" t="inlineStr"/>
-      <c r="J81" t="inlineStr"/>
-      <c r="K81" t="inlineStr"/>
       <c r="L81" t="inlineStr">
         <is>
           <t>李坤纬</t>
         </is>
       </c>
-      <c r="M81" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
@@ -3776,7 +3296,7 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>StarPicture</t>
+          <t>功能测试</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
@@ -3792,17 +3312,11 @@
       <c r="F82" t="n">
         <v>1</v>
       </c>
-      <c r="G82" t="inlineStr"/>
-      <c r="H82" t="inlineStr"/>
-      <c r="I82" t="inlineStr"/>
-      <c r="J82" t="inlineStr"/>
-      <c r="K82" t="inlineStr"/>
       <c r="L82" t="inlineStr">
         <is>
           <t>李坤纬</t>
         </is>
       </c>
-      <c r="M82" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
@@ -3817,7 +3331,7 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>StarPicture</t>
+          <t>功能测试</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
@@ -3833,17 +3347,11 @@
       <c r="F83" t="n">
         <v>1</v>
       </c>
-      <c r="G83" t="inlineStr"/>
-      <c r="H83" t="inlineStr"/>
-      <c r="I83" t="inlineStr"/>
-      <c r="J83" t="inlineStr"/>
-      <c r="K83" t="inlineStr"/>
       <c r="L83" t="inlineStr">
         <is>
           <t>李坤纬</t>
         </is>
       </c>
-      <c r="M83" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
@@ -3858,7 +3366,7 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>StarPicture</t>
+          <t>功能测试</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
@@ -3874,17 +3382,11 @@
       <c r="F84" t="n">
         <v>1</v>
       </c>
-      <c r="G84" t="inlineStr"/>
-      <c r="H84" t="inlineStr"/>
-      <c r="I84" t="inlineStr"/>
-      <c r="J84" t="inlineStr"/>
-      <c r="K84" t="inlineStr"/>
       <c r="L84" t="inlineStr">
         <is>
           <t>李坤纬</t>
         </is>
       </c>
-      <c r="M84" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
@@ -3899,7 +3401,7 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>StarPicture</t>
+          <t>功能测试</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
@@ -3915,17 +3417,11 @@
       <c r="F85" t="n">
         <v>2</v>
       </c>
-      <c r="G85" t="inlineStr"/>
-      <c r="H85" t="inlineStr"/>
-      <c r="I85" t="inlineStr"/>
-      <c r="J85" t="inlineStr"/>
-      <c r="K85" t="inlineStr"/>
       <c r="L85" t="inlineStr">
         <is>
           <t>李坤纬</t>
         </is>
       </c>
-      <c r="M85" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
@@ -3940,7 +3436,7 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>StarPicture</t>
+          <t>功能测试</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
@@ -3956,17 +3452,11 @@
       <c r="F86" t="n">
         <v>1</v>
       </c>
-      <c r="G86" t="inlineStr"/>
-      <c r="H86" t="inlineStr"/>
-      <c r="I86" t="inlineStr"/>
-      <c r="J86" t="inlineStr"/>
-      <c r="K86" t="inlineStr"/>
       <c r="L86" t="inlineStr">
         <is>
           <t>李坤纬</t>
         </is>
       </c>
-      <c r="M86" t="inlineStr"/>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
@@ -3981,7 +3471,7 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>StarPicture</t>
+          <t>功能测试</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
@@ -3997,17 +3487,11 @@
       <c r="F87" t="n">
         <v>1</v>
       </c>
-      <c r="G87" t="inlineStr"/>
-      <c r="H87" t="inlineStr"/>
-      <c r="I87" t="inlineStr"/>
-      <c r="J87" t="inlineStr"/>
-      <c r="K87" t="inlineStr"/>
       <c r="L87" t="inlineStr">
         <is>
           <t>李坤纬</t>
         </is>
       </c>
-      <c r="M87" t="inlineStr"/>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
@@ -4022,7 +3506,7 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>StarPicture</t>
+          <t>功能测试</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
@@ -4038,17 +3522,11 @@
       <c r="F88" t="n">
         <v>2</v>
       </c>
-      <c r="G88" t="inlineStr"/>
-      <c r="H88" t="inlineStr"/>
-      <c r="I88" t="inlineStr"/>
-      <c r="J88" t="inlineStr"/>
-      <c r="K88" t="inlineStr"/>
       <c r="L88" t="inlineStr">
         <is>
           <t>李坤纬</t>
         </is>
       </c>
-      <c r="M88" t="inlineStr"/>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
@@ -4063,7 +3541,7 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>StarPicture</t>
+          <t>功能测试</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
@@ -4079,17 +3557,11 @@
       <c r="F89" t="n">
         <v>1</v>
       </c>
-      <c r="G89" t="inlineStr"/>
-      <c r="H89" t="inlineStr"/>
-      <c r="I89" t="inlineStr"/>
-      <c r="J89" t="inlineStr"/>
-      <c r="K89" t="inlineStr"/>
       <c r="L89" t="inlineStr">
         <is>
           <t>李坤纬</t>
         </is>
       </c>
-      <c r="M89" t="inlineStr"/>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
@@ -4104,7 +3576,7 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>StarPicture</t>
+          <t>功能测试</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
@@ -4120,17 +3592,11 @@
       <c r="F90" t="n">
         <v>1</v>
       </c>
-      <c r="G90" t="inlineStr"/>
-      <c r="H90" t="inlineStr"/>
-      <c r="I90" t="inlineStr"/>
-      <c r="J90" t="inlineStr"/>
-      <c r="K90" t="inlineStr"/>
       <c r="L90" t="inlineStr">
         <is>
           <t>李坤纬</t>
         </is>
       </c>
-      <c r="M90" t="inlineStr"/>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
@@ -4145,7 +3611,7 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>StarPicture</t>
+          <t>功能测试</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
@@ -4161,17 +3627,11 @@
       <c r="F91" t="n">
         <v>1</v>
       </c>
-      <c r="G91" t="inlineStr"/>
-      <c r="H91" t="inlineStr"/>
-      <c r="I91" t="inlineStr"/>
-      <c r="J91" t="inlineStr"/>
-      <c r="K91" t="inlineStr"/>
       <c r="L91" t="inlineStr">
         <is>
           <t>李坤纬</t>
         </is>
       </c>
-      <c r="M91" t="inlineStr"/>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
@@ -4186,7 +3646,7 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>StarPicture</t>
+          <t>功能测试</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
@@ -4202,17 +3662,11 @@
       <c r="F92" t="n">
         <v>1</v>
       </c>
-      <c r="G92" t="inlineStr"/>
-      <c r="H92" t="inlineStr"/>
-      <c r="I92" t="inlineStr"/>
-      <c r="J92" t="inlineStr"/>
-      <c r="K92" t="inlineStr"/>
       <c r="L92" t="inlineStr">
         <is>
           <t>李坤纬</t>
         </is>
       </c>
-      <c r="M92" t="inlineStr"/>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
@@ -4227,7 +3681,7 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>StarPicture</t>
+          <t>功能测试</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
@@ -4243,17 +3697,11 @@
       <c r="F93" t="n">
         <v>1</v>
       </c>
-      <c r="G93" t="inlineStr"/>
-      <c r="H93" t="inlineStr"/>
-      <c r="I93" t="inlineStr"/>
-      <c r="J93" t="inlineStr"/>
-      <c r="K93" t="inlineStr"/>
       <c r="L93" t="inlineStr">
         <is>
           <t>李坤纬</t>
         </is>
       </c>
-      <c r="M93" t="inlineStr"/>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
@@ -4268,7 +3716,7 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>StarPicture</t>
+          <t>功能测试</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
@@ -4284,17 +3732,11 @@
       <c r="F94" t="n">
         <v>1</v>
       </c>
-      <c r="G94" t="inlineStr"/>
-      <c r="H94" t="inlineStr"/>
-      <c r="I94" t="inlineStr"/>
-      <c r="J94" t="inlineStr"/>
-      <c r="K94" t="inlineStr"/>
       <c r="L94" t="inlineStr">
         <is>
           <t>李坤纬</t>
         </is>
       </c>
-      <c r="M94" t="inlineStr"/>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
@@ -4309,7 +3751,7 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>StarPicture</t>
+          <t>功能测试</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
@@ -4325,17 +3767,11 @@
       <c r="F95" t="n">
         <v>1</v>
       </c>
-      <c r="G95" t="inlineStr"/>
-      <c r="H95" t="inlineStr"/>
-      <c r="I95" t="inlineStr"/>
-      <c r="J95" t="inlineStr"/>
-      <c r="K95" t="inlineStr"/>
       <c r="L95" t="inlineStr">
         <is>
           <t>李坤纬</t>
         </is>
       </c>
-      <c r="M95" t="inlineStr"/>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
@@ -4350,7 +3786,7 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>StarPicture</t>
+          <t>功能测试</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
@@ -4366,17 +3802,11 @@
       <c r="F96" t="n">
         <v>2</v>
       </c>
-      <c r="G96" t="inlineStr"/>
-      <c r="H96" t="inlineStr"/>
-      <c r="I96" t="inlineStr"/>
-      <c r="J96" t="inlineStr"/>
-      <c r="K96" t="inlineStr"/>
       <c r="L96" t="inlineStr">
         <is>
           <t>李坤纬</t>
         </is>
       </c>
-      <c r="M96" t="inlineStr"/>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
@@ -4391,7 +3821,7 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>StarPicture</t>
+          <t>功能测试</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
@@ -4407,17 +3837,11 @@
       <c r="F97" t="n">
         <v>1</v>
       </c>
-      <c r="G97" t="inlineStr"/>
-      <c r="H97" t="inlineStr"/>
-      <c r="I97" t="inlineStr"/>
-      <c r="J97" t="inlineStr"/>
-      <c r="K97" t="inlineStr"/>
       <c r="L97" t="inlineStr">
         <is>
           <t>李坤纬</t>
         </is>
       </c>
-      <c r="M97" t="inlineStr"/>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
@@ -4432,7 +3856,7 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>StarPicture</t>
+          <t>功能测试</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
@@ -4448,17 +3872,11 @@
       <c r="F98" t="n">
         <v>1</v>
       </c>
-      <c r="G98" t="inlineStr"/>
-      <c r="H98" t="inlineStr"/>
-      <c r="I98" t="inlineStr"/>
-      <c r="J98" t="inlineStr"/>
-      <c r="K98" t="inlineStr"/>
       <c r="L98" t="inlineStr">
         <is>
           <t>李坤纬</t>
         </is>
       </c>
-      <c r="M98" t="inlineStr"/>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
@@ -4473,7 +3891,7 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>StarPicture</t>
+          <t>功能测试</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
@@ -4489,17 +3907,11 @@
       <c r="F99" t="n">
         <v>1</v>
       </c>
-      <c r="G99" t="inlineStr"/>
-      <c r="H99" t="inlineStr"/>
-      <c r="I99" t="inlineStr"/>
-      <c r="J99" t="inlineStr"/>
-      <c r="K99" t="inlineStr"/>
       <c r="L99" t="inlineStr">
         <is>
           <t>李坤纬</t>
         </is>
       </c>
-      <c r="M99" t="inlineStr"/>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
@@ -4514,7 +3926,7 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>StarPicture</t>
+          <t>功能测试</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
@@ -4530,17 +3942,11 @@
       <c r="F100" t="n">
         <v>1</v>
       </c>
-      <c r="G100" t="inlineStr"/>
-      <c r="H100" t="inlineStr"/>
-      <c r="I100" t="inlineStr"/>
-      <c r="J100" t="inlineStr"/>
-      <c r="K100" t="inlineStr"/>
       <c r="L100" t="inlineStr">
         <is>
           <t>李坤纬</t>
         </is>
       </c>
-      <c r="M100" t="inlineStr"/>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
@@ -4555,7 +3961,7 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>StarPicture</t>
+          <t>功能测试</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
@@ -4571,17 +3977,11 @@
       <c r="F101" t="n">
         <v>1</v>
       </c>
-      <c r="G101" t="inlineStr"/>
-      <c r="H101" t="inlineStr"/>
-      <c r="I101" t="inlineStr"/>
-      <c r="J101" t="inlineStr"/>
-      <c r="K101" t="inlineStr"/>
       <c r="L101" t="inlineStr">
         <is>
           <t>李坤纬</t>
         </is>
       </c>
-      <c r="M101" t="inlineStr"/>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
@@ -4596,7 +3996,7 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>StarPicture</t>
+          <t>功能测试</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
@@ -4612,17 +4012,11 @@
       <c r="F102" t="n">
         <v>1</v>
       </c>
-      <c r="G102" t="inlineStr"/>
-      <c r="H102" t="inlineStr"/>
-      <c r="I102" t="inlineStr"/>
-      <c r="J102" t="inlineStr"/>
-      <c r="K102" t="inlineStr"/>
       <c r="L102" t="inlineStr">
         <is>
           <t>李坤纬</t>
         </is>
       </c>
-      <c r="M102" t="inlineStr"/>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
@@ -4637,7 +4031,7 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>StarPicture</t>
+          <t>功能测试</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
@@ -4653,17 +4047,11 @@
       <c r="F103" t="n">
         <v>1</v>
       </c>
-      <c r="G103" t="inlineStr"/>
-      <c r="H103" t="inlineStr"/>
-      <c r="I103" t="inlineStr"/>
-      <c r="J103" t="inlineStr"/>
-      <c r="K103" t="inlineStr"/>
       <c r="L103" t="inlineStr">
         <is>
           <t>李坤纬</t>
         </is>
       </c>
-      <c r="M103" t="inlineStr"/>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
@@ -4678,7 +4066,7 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>StarPicture</t>
+          <t>功能测试</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
@@ -4694,17 +4082,11 @@
       <c r="F104" t="n">
         <v>1</v>
       </c>
-      <c r="G104" t="inlineStr"/>
-      <c r="H104" t="inlineStr"/>
-      <c r="I104" t="inlineStr"/>
-      <c r="J104" t="inlineStr"/>
-      <c r="K104" t="inlineStr"/>
       <c r="L104" t="inlineStr">
         <is>
           <t>李坤纬</t>
         </is>
       </c>
-      <c r="M104" t="inlineStr"/>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
@@ -4719,7 +4101,7 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>StarPicture</t>
+          <t>功能测试</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
@@ -4735,17 +4117,11 @@
       <c r="F105" t="n">
         <v>1</v>
       </c>
-      <c r="G105" t="inlineStr"/>
-      <c r="H105" t="inlineStr"/>
-      <c r="I105" t="inlineStr"/>
-      <c r="J105" t="inlineStr"/>
-      <c r="K105" t="inlineStr"/>
       <c r="L105" t="inlineStr">
         <is>
           <t>李坤纬</t>
         </is>
       </c>
-      <c r="M105" t="inlineStr"/>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
@@ -4760,7 +4136,7 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>StarPicture</t>
+          <t>功能测试</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
@@ -4776,17 +4152,11 @@
       <c r="F106" t="n">
         <v>1</v>
       </c>
-      <c r="G106" t="inlineStr"/>
-      <c r="H106" t="inlineStr"/>
-      <c r="I106" t="inlineStr"/>
-      <c r="J106" t="inlineStr"/>
-      <c r="K106" t="inlineStr"/>
       <c r="L106" t="inlineStr">
         <is>
           <t>李坤纬</t>
         </is>
       </c>
-      <c r="M106" t="inlineStr"/>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
@@ -4801,7 +4171,7 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>StarPicture</t>
+          <t>功能测试</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
@@ -4817,17 +4187,11 @@
       <c r="F107" t="n">
         <v>1</v>
       </c>
-      <c r="G107" t="inlineStr"/>
-      <c r="H107" t="inlineStr"/>
-      <c r="I107" t="inlineStr"/>
-      <c r="J107" t="inlineStr"/>
-      <c r="K107" t="inlineStr"/>
       <c r="L107" t="inlineStr">
         <is>
           <t>李坤纬</t>
         </is>
       </c>
-      <c r="M107" t="inlineStr"/>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
@@ -4842,7 +4206,7 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>StarPicture</t>
+          <t>功能测试</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
@@ -4858,17 +4222,11 @@
       <c r="F108" t="n">
         <v>1</v>
       </c>
-      <c r="G108" t="inlineStr"/>
-      <c r="H108" t="inlineStr"/>
-      <c r="I108" t="inlineStr"/>
-      <c r="J108" t="inlineStr"/>
-      <c r="K108" t="inlineStr"/>
       <c r="L108" t="inlineStr">
         <is>
           <t>李坤纬</t>
         </is>
       </c>
-      <c r="M108" t="inlineStr"/>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
@@ -4883,7 +4241,7 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>StarPicture</t>
+          <t>功能测试</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
@@ -4899,17 +4257,11 @@
       <c r="F109" t="n">
         <v>1</v>
       </c>
-      <c r="G109" t="inlineStr"/>
-      <c r="H109" t="inlineStr"/>
-      <c r="I109" t="inlineStr"/>
-      <c r="J109" t="inlineStr"/>
-      <c r="K109" t="inlineStr"/>
       <c r="L109" t="inlineStr">
         <is>
           <t>李坤纬</t>
         </is>
       </c>
-      <c r="M109" t="inlineStr"/>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
@@ -4924,7 +4276,7 @@
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>StarPicture</t>
+          <t>性能测试</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
@@ -4940,17 +4292,11 @@
       <c r="F110" t="n">
         <v>2</v>
       </c>
-      <c r="G110" t="inlineStr"/>
-      <c r="H110" t="inlineStr"/>
-      <c r="I110" t="inlineStr"/>
-      <c r="J110" t="inlineStr"/>
-      <c r="K110" t="inlineStr"/>
       <c r="L110" t="inlineStr">
         <is>
           <t>李坤纬</t>
         </is>
       </c>
-      <c r="M110" t="inlineStr"/>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
@@ -4965,7 +4311,7 @@
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>StarPicture</t>
+          <t>接口测试</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
@@ -4981,17 +4327,11 @@
       <c r="F111" t="n">
         <v>2</v>
       </c>
-      <c r="G111" t="inlineStr"/>
-      <c r="H111" t="inlineStr"/>
-      <c r="I111" t="inlineStr"/>
-      <c r="J111" t="inlineStr"/>
-      <c r="K111" t="inlineStr"/>
       <c r="L111" t="inlineStr">
         <is>
           <t>李坤纬</t>
         </is>
       </c>
-      <c r="M111" t="inlineStr"/>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
@@ -5006,7 +4346,7 @@
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>StarPicture</t>
+          <t>功能测试</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
@@ -5022,17 +4362,11 @@
       <c r="F112" t="n">
         <v>1</v>
       </c>
-      <c r="G112" t="inlineStr"/>
-      <c r="H112" t="inlineStr"/>
-      <c r="I112" t="inlineStr"/>
-      <c r="J112" t="inlineStr"/>
-      <c r="K112" t="inlineStr"/>
       <c r="L112" t="inlineStr">
         <is>
           <t>林景彬</t>
         </is>
       </c>
-      <c r="M112" t="inlineStr"/>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
@@ -5047,7 +4381,7 @@
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>StarPicture</t>
+          <t>功能测试</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
@@ -5063,17 +4397,11 @@
       <c r="F113" t="n">
         <v>1</v>
       </c>
-      <c r="G113" t="inlineStr"/>
-      <c r="H113" t="inlineStr"/>
-      <c r="I113" t="inlineStr"/>
-      <c r="J113" t="inlineStr"/>
-      <c r="K113" t="inlineStr"/>
       <c r="L113" t="inlineStr">
         <is>
           <t>林景彬</t>
         </is>
       </c>
-      <c r="M113" t="inlineStr"/>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
@@ -5088,7 +4416,7 @@
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>StarPicture</t>
+          <t>功能测试</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
@@ -5104,17 +4432,11 @@
       <c r="F114" t="n">
         <v>1</v>
       </c>
-      <c r="G114" t="inlineStr"/>
-      <c r="H114" t="inlineStr"/>
-      <c r="I114" t="inlineStr"/>
-      <c r="J114" t="inlineStr"/>
-      <c r="K114" t="inlineStr"/>
       <c r="L114" t="inlineStr">
         <is>
           <t>林景彬</t>
         </is>
       </c>
-      <c r="M114" t="inlineStr"/>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
@@ -5129,7 +4451,7 @@
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>StarPicture</t>
+          <t>功能测试</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
@@ -5145,17 +4467,11 @@
       <c r="F115" t="n">
         <v>2</v>
       </c>
-      <c r="G115" t="inlineStr"/>
-      <c r="H115" t="inlineStr"/>
-      <c r="I115" t="inlineStr"/>
-      <c r="J115" t="inlineStr"/>
-      <c r="K115" t="inlineStr"/>
       <c r="L115" t="inlineStr">
         <is>
           <t>林景彬</t>
         </is>
       </c>
-      <c r="M115" t="inlineStr"/>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
@@ -5170,7 +4486,7 @@
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>StarPicture</t>
+          <t>功能测试</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
@@ -5186,17 +4502,11 @@
       <c r="F116" t="n">
         <v>2</v>
       </c>
-      <c r="G116" t="inlineStr"/>
-      <c r="H116" t="inlineStr"/>
-      <c r="I116" t="inlineStr"/>
-      <c r="J116" t="inlineStr"/>
-      <c r="K116" t="inlineStr"/>
       <c r="L116" t="inlineStr">
         <is>
           <t>林景彬</t>
         </is>
       </c>
-      <c r="M116" t="inlineStr"/>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
@@ -5211,7 +4521,7 @@
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>StarPicture</t>
+          <t>功能测试</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
@@ -5227,17 +4537,11 @@
       <c r="F117" t="n">
         <v>2</v>
       </c>
-      <c r="G117" t="inlineStr"/>
-      <c r="H117" t="inlineStr"/>
-      <c r="I117" t="inlineStr"/>
-      <c r="J117" t="inlineStr"/>
-      <c r="K117" t="inlineStr"/>
       <c r="L117" t="inlineStr">
         <is>
           <t>林景彬</t>
         </is>
       </c>
-      <c r="M117" t="inlineStr"/>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
@@ -5252,7 +4556,7 @@
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>StarPicture</t>
+          <t>功能测试</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
@@ -5268,17 +4572,11 @@
       <c r="F118" t="n">
         <v>1</v>
       </c>
-      <c r="G118" t="inlineStr"/>
-      <c r="H118" t="inlineStr"/>
-      <c r="I118" t="inlineStr"/>
-      <c r="J118" t="inlineStr"/>
-      <c r="K118" t="inlineStr"/>
       <c r="L118" t="inlineStr">
         <is>
           <t>林景彬</t>
         </is>
       </c>
-      <c r="M118" t="inlineStr"/>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
@@ -5293,7 +4591,7 @@
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>StarPicture</t>
+          <t>功能测试</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
@@ -5309,17 +4607,11 @@
       <c r="F119" t="n">
         <v>1</v>
       </c>
-      <c r="G119" t="inlineStr"/>
-      <c r="H119" t="inlineStr"/>
-      <c r="I119" t="inlineStr"/>
-      <c r="J119" t="inlineStr"/>
-      <c r="K119" t="inlineStr"/>
       <c r="L119" t="inlineStr">
         <is>
           <t>林景彬</t>
         </is>
       </c>
-      <c r="M119" t="inlineStr"/>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
@@ -5334,7 +4626,7 @@
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>StarPicture</t>
+          <t>功能测试</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
@@ -5350,17 +4642,11 @@
       <c r="F120" t="n">
         <v>2</v>
       </c>
-      <c r="G120" t="inlineStr"/>
-      <c r="H120" t="inlineStr"/>
-      <c r="I120" t="inlineStr"/>
-      <c r="J120" t="inlineStr"/>
-      <c r="K120" t="inlineStr"/>
       <c r="L120" t="inlineStr">
         <is>
           <t>林景彬</t>
         </is>
       </c>
-      <c r="M120" t="inlineStr"/>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
@@ -5375,7 +4661,7 @@
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>StarPicture</t>
+          <t>功能测试</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
@@ -5391,17 +4677,11 @@
       <c r="F121" t="n">
         <v>1</v>
       </c>
-      <c r="G121" t="inlineStr"/>
-      <c r="H121" t="inlineStr"/>
-      <c r="I121" t="inlineStr"/>
-      <c r="J121" t="inlineStr"/>
-      <c r="K121" t="inlineStr"/>
       <c r="L121" t="inlineStr">
         <is>
           <t>林景彬</t>
         </is>
       </c>
-      <c r="M121" t="inlineStr"/>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
@@ -5416,7 +4696,7 @@
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>StarPicture</t>
+          <t>功能测试</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
@@ -5432,17 +4712,11 @@
       <c r="F122" t="n">
         <v>1</v>
       </c>
-      <c r="G122" t="inlineStr"/>
-      <c r="H122" t="inlineStr"/>
-      <c r="I122" t="inlineStr"/>
-      <c r="J122" t="inlineStr"/>
-      <c r="K122" t="inlineStr"/>
       <c r="L122" t="inlineStr">
         <is>
           <t>林景彬</t>
         </is>
       </c>
-      <c r="M122" t="inlineStr"/>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
@@ -5457,7 +4731,7 @@
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>StarPicture</t>
+          <t>功能测试</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
@@ -5473,17 +4747,11 @@
       <c r="F123" t="n">
         <v>2</v>
       </c>
-      <c r="G123" t="inlineStr"/>
-      <c r="H123" t="inlineStr"/>
-      <c r="I123" t="inlineStr"/>
-      <c r="J123" t="inlineStr"/>
-      <c r="K123" t="inlineStr"/>
       <c r="L123" t="inlineStr">
         <is>
           <t>林景彬</t>
         </is>
       </c>
-      <c r="M123" t="inlineStr"/>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
@@ -5498,7 +4766,7 @@
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>StarPicture</t>
+          <t>功能测试</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
@@ -5514,17 +4782,11 @@
       <c r="F124" t="n">
         <v>2</v>
       </c>
-      <c r="G124" t="inlineStr"/>
-      <c r="H124" t="inlineStr"/>
-      <c r="I124" t="inlineStr"/>
-      <c r="J124" t="inlineStr"/>
-      <c r="K124" t="inlineStr"/>
       <c r="L124" t="inlineStr">
         <is>
           <t>林景彬</t>
         </is>
       </c>
-      <c r="M124" t="inlineStr"/>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
@@ -5539,7 +4801,7 @@
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>StarPicture</t>
+          <t>功能测试</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
@@ -5555,17 +4817,11 @@
       <c r="F125" t="n">
         <v>2</v>
       </c>
-      <c r="G125" t="inlineStr"/>
-      <c r="H125" t="inlineStr"/>
-      <c r="I125" t="inlineStr"/>
-      <c r="J125" t="inlineStr"/>
-      <c r="K125" t="inlineStr"/>
       <c r="L125" t="inlineStr">
         <is>
           <t>林景彬</t>
         </is>
       </c>
-      <c r="M125" t="inlineStr"/>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
@@ -5580,7 +4836,7 @@
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>StarPicture</t>
+          <t>功能测试</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
@@ -5596,17 +4852,11 @@
       <c r="F126" t="n">
         <v>1</v>
       </c>
-      <c r="G126" t="inlineStr"/>
-      <c r="H126" t="inlineStr"/>
-      <c r="I126" t="inlineStr"/>
-      <c r="J126" t="inlineStr"/>
-      <c r="K126" t="inlineStr"/>
       <c r="L126" t="inlineStr">
         <is>
           <t>林景彬</t>
         </is>
       </c>
-      <c r="M126" t="inlineStr"/>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
@@ -5621,7 +4871,7 @@
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>StarPicture</t>
+          <t>功能测试</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
@@ -5637,17 +4887,11 @@
       <c r="F127" t="n">
         <v>1</v>
       </c>
-      <c r="G127" t="inlineStr"/>
-      <c r="H127" t="inlineStr"/>
-      <c r="I127" t="inlineStr"/>
-      <c r="J127" t="inlineStr"/>
-      <c r="K127" t="inlineStr"/>
       <c r="L127" t="inlineStr">
         <is>
           <t>林景彬</t>
         </is>
       </c>
-      <c r="M127" t="inlineStr"/>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
@@ -5662,7 +4906,7 @@
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>StarPicture</t>
+          <t>功能测试</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
@@ -5678,17 +4922,11 @@
       <c r="F128" t="n">
         <v>2</v>
       </c>
-      <c r="G128" t="inlineStr"/>
-      <c r="H128" t="inlineStr"/>
-      <c r="I128" t="inlineStr"/>
-      <c r="J128" t="inlineStr"/>
-      <c r="K128" t="inlineStr"/>
       <c r="L128" t="inlineStr">
         <is>
           <t>林景彬</t>
         </is>
       </c>
-      <c r="M128" t="inlineStr"/>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
@@ -5703,7 +4941,7 @@
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>StarPicture</t>
+          <t>功能测试</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
@@ -5719,17 +4957,11 @@
       <c r="F129" t="n">
         <v>1</v>
       </c>
-      <c r="G129" t="inlineStr"/>
-      <c r="H129" t="inlineStr"/>
-      <c r="I129" t="inlineStr"/>
-      <c r="J129" t="inlineStr"/>
-      <c r="K129" t="inlineStr"/>
       <c r="L129" t="inlineStr">
         <is>
           <t>林景彬</t>
         </is>
       </c>
-      <c r="M129" t="inlineStr"/>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
@@ -5744,7 +4976,7 @@
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>StarPicture</t>
+          <t>功能测试</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
@@ -5760,17 +4992,11 @@
       <c r="F130" t="n">
         <v>1</v>
       </c>
-      <c r="G130" t="inlineStr"/>
-      <c r="H130" t="inlineStr"/>
-      <c r="I130" t="inlineStr"/>
-      <c r="J130" t="inlineStr"/>
-      <c r="K130" t="inlineStr"/>
       <c r="L130" t="inlineStr">
         <is>
           <t>林景彬</t>
         </is>
       </c>
-      <c r="M130" t="inlineStr"/>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
@@ -5785,7 +5011,7 @@
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>StarPicture</t>
+          <t>功能测试</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
@@ -5801,17 +5027,11 @@
       <c r="F131" t="n">
         <v>1</v>
       </c>
-      <c r="G131" t="inlineStr"/>
-      <c r="H131" t="inlineStr"/>
-      <c r="I131" t="inlineStr"/>
-      <c r="J131" t="inlineStr"/>
-      <c r="K131" t="inlineStr"/>
       <c r="L131" t="inlineStr">
         <is>
           <t>林景彬</t>
         </is>
       </c>
-      <c r="M131" t="inlineStr"/>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
@@ -5826,7 +5046,7 @@
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>StarPicture</t>
+          <t>功能测试</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
@@ -5842,17 +5062,11 @@
       <c r="F132" t="n">
         <v>1</v>
       </c>
-      <c r="G132" t="inlineStr"/>
-      <c r="H132" t="inlineStr"/>
-      <c r="I132" t="inlineStr"/>
-      <c r="J132" t="inlineStr"/>
-      <c r="K132" t="inlineStr"/>
       <c r="L132" t="inlineStr">
         <is>
           <t>林景彬</t>
         </is>
       </c>
-      <c r="M132" t="inlineStr"/>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
@@ -5867,7 +5081,7 @@
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>StarPicture</t>
+          <t>功能测试</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
@@ -5883,17 +5097,11 @@
       <c r="F133" t="n">
         <v>2</v>
       </c>
-      <c r="G133" t="inlineStr"/>
-      <c r="H133" t="inlineStr"/>
-      <c r="I133" t="inlineStr"/>
-      <c r="J133" t="inlineStr"/>
-      <c r="K133" t="inlineStr"/>
       <c r="L133" t="inlineStr">
         <is>
           <t>林景彬</t>
         </is>
       </c>
-      <c r="M133" t="inlineStr"/>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
@@ -5908,7 +5116,7 @@
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>StarPicture</t>
+          <t>功能测试</t>
         </is>
       </c>
       <c r="D134" t="inlineStr">
@@ -5924,17 +5132,11 @@
       <c r="F134" t="n">
         <v>1</v>
       </c>
-      <c r="G134" t="inlineStr"/>
-      <c r="H134" t="inlineStr"/>
-      <c r="I134" t="inlineStr"/>
-      <c r="J134" t="inlineStr"/>
-      <c r="K134" t="inlineStr"/>
       <c r="L134" t="inlineStr">
         <is>
           <t>林景彬</t>
         </is>
       </c>
-      <c r="M134" t="inlineStr"/>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
@@ -5949,7 +5151,7 @@
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>StarPicture</t>
+          <t>性能测试</t>
         </is>
       </c>
       <c r="D135" t="inlineStr">
@@ -5965,17 +5167,11 @@
       <c r="F135" t="n">
         <v>2</v>
       </c>
-      <c r="G135" t="inlineStr"/>
-      <c r="H135" t="inlineStr"/>
-      <c r="I135" t="inlineStr"/>
-      <c r="J135" t="inlineStr"/>
-      <c r="K135" t="inlineStr"/>
       <c r="L135" t="inlineStr">
         <is>
           <t>林景彬</t>
         </is>
       </c>
-      <c r="M135" t="inlineStr"/>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
@@ -5990,7 +5186,7 @@
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>StarPicture</t>
+          <t>接口测试</t>
         </is>
       </c>
       <c r="D136" t="inlineStr">
@@ -6006,17 +5202,11 @@
       <c r="F136" t="n">
         <v>2</v>
       </c>
-      <c r="G136" t="inlineStr"/>
-      <c r="H136" t="inlineStr"/>
-      <c r="I136" t="inlineStr"/>
-      <c r="J136" t="inlineStr"/>
-      <c r="K136" t="inlineStr"/>
       <c r="L136" t="inlineStr">
         <is>
           <t>林景彬</t>
         </is>
       </c>
-      <c r="M136" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
